--- a/database/event/2187/event_2187_evp_summary.xlsx
+++ b/database/event/2187/event_2187_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.5194</v>
       </c>
       <c r="D2" t="n">
-        <v>2.879</v>
+        <v>2.8109</v>
       </c>
       <c r="E2" t="n">
         <v>8.169600000000001</v>
@@ -548,7 +548,7 @@
         <v>1.1062</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9815</v>
+        <v>1.9258</v>
       </c>
       <c r="E3" t="n">
         <v>5.9481</v>
@@ -594,7 +594,7 @@
         <v>1.0284</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8124</v>
+        <v>1.759</v>
       </c>
       <c r="E4" t="n">
         <v>5.5293</v>
@@ -640,7 +640,7 @@
         <v>0.9651999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6752</v>
+        <v>1.6237</v>
       </c>
       <c r="E5" t="n">
         <v>5.1897</v>
@@ -686,7 +686,7 @@
         <v>0.9596</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6631</v>
+        <v>1.6118</v>
       </c>
       <c r="E6" t="n">
         <v>5.1598</v>
@@ -732,7 +732,7 @@
         <v>0.9427</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6262</v>
+        <v>1.5754</v>
       </c>
       <c r="E7" t="n">
         <v>5.0686</v>
@@ -778,7 +778,7 @@
         <v>0.889</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5096</v>
+        <v>1.4604</v>
       </c>
       <c r="E8" t="n">
         <v>4.7798</v>
@@ -824,7 +824,7 @@
         <v>0.8166</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3524</v>
+        <v>1.3054</v>
       </c>
       <c r="E9" t="n">
         <v>4.3908</v>
@@ -870,7 +870,7 @@
         <v>0.7374000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1803</v>
+        <v>1.1356</v>
       </c>
       <c r="E10" t="n">
         <v>3.9647</v>
@@ -916,7 +916,7 @@
         <v>0.5985</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8786</v>
+        <v>0.8381</v>
       </c>
       <c r="E11" t="n">
         <v>3.2178</v>
@@ -962,7 +962,7 @@
         <v>0.5937</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8681</v>
+        <v>0.8278</v>
       </c>
       <c r="E12" t="n">
         <v>3.192</v>
@@ -1008,7 +1008,7 @@
         <v>0.5748</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.7873</v>
       </c>
       <c r="E13" t="n">
         <v>3.0904</v>
@@ -1054,7 +1054,7 @@
         <v>0.5085</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6831</v>
+        <v>0.6453</v>
       </c>
       <c r="E14" t="n">
         <v>2.734</v>
@@ -1100,7 +1100,7 @@
         <v>0.4815</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6244</v>
+        <v>0.5874</v>
       </c>
       <c r="E15" t="n">
         <v>2.5887</v>
@@ -1146,7 +1146,7 @@
         <v>0.4445</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5441</v>
+        <v>0.5083</v>
       </c>
       <c r="E16" t="n">
         <v>2.39</v>
@@ -1192,7 +1192,7 @@
         <v>0.4371</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5281</v>
+        <v>0.4924</v>
       </c>
       <c r="E17" t="n">
         <v>2.3503</v>
@@ -1238,7 +1238,7 @@
         <v>0.2575</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1379</v>
+        <v>0.1076</v>
       </c>
       <c r="E18" t="n">
         <v>1.3843</v>
@@ -1284,7 +1284,7 @@
         <v>0.1857</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0181</v>
+        <v>-0.0462</v>
       </c>
       <c r="E19" t="n">
         <v>0.9983</v>
@@ -1330,7 +1330,7 @@
         <v>0.1847</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0201</v>
+        <v>-0.0482</v>
       </c>
       <c r="E20" t="n">
         <v>0.9932</v>
@@ -1376,7 +1376,7 @@
         <v>0.1838</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0221</v>
+        <v>-0.0502</v>
       </c>
       <c r="E21" t="n">
         <v>0.9883</v>
@@ -1422,7 +1422,7 @@
         <v>0.1401</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.117</v>
+        <v>-0.1438</v>
       </c>
       <c r="E22" t="n">
         <v>0.7534</v>
@@ -1468,7 +1468,7 @@
         <v>0.1179</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1654</v>
+        <v>-0.1914</v>
       </c>
       <c r="E23" t="n">
         <v>0.6337</v>
@@ -1514,7 +1514,7 @@
         <v>0.0796</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2485</v>
+        <v>-0.2734</v>
       </c>
       <c r="E24" t="n">
         <v>0.4279</v>
@@ -1560,7 +1560,7 @@
         <v>0.0617</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2874</v>
+        <v>-0.3118</v>
       </c>
       <c r="E25" t="n">
         <v>0.3315</v>
@@ -1606,7 +1606,7 @@
         <v>0.0178</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3826</v>
+        <v>-0.4057</v>
       </c>
       <c r="E26" t="n">
         <v>0.0959</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0484</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5264</v>
+        <v>-0.5475</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2601</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0509</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5319</v>
+        <v>-0.553</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2737</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0547</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5403</v>
+        <v>-0.5612</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2943</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0805</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5962</v>
+        <v>-0.6163</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4327</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1264</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.696</v>
+        <v>-0.7147</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6798</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1513</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.75</v>
+        <v>-0.768</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8135</v>
@@ -1928,7 +1928,7 @@
         <v>-0.157</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7623</v>
+        <v>-0.7802</v>
       </c>
       <c r="E33" t="n">
         <v>-0.844</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1819</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8165</v>
+        <v>-0.8335</v>
       </c>
       <c r="E34" t="n">
         <v>-0.978</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1936</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8419</v>
+        <v>-0.8586</v>
       </c>
       <c r="E35" t="n">
         <v>-1.041</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1986</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8529</v>
+        <v>-0.8694</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0681</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2631</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.993</v>
+        <v>-1.0076</v>
       </c>
       <c r="E37" t="n">
         <v>-1.4149</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3181</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1122</v>
+        <v>-1.1253</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7102</v>
@@ -2204,7 +2204,7 @@
         <v>-0.334</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1469</v>
+        <v>-1.1594</v>
       </c>
       <c r="E39" t="n">
         <v>-1.796</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3421</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1644</v>
+        <v>-1.1767</v>
       </c>
       <c r="E40" t="n">
         <v>-1.8393</v>
@@ -2296,7 +2296,7 @@
         <v>-0.3677</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2201</v>
+        <v>-1.2316</v>
       </c>
       <c r="E41" t="n">
         <v>-1.9772</v>

--- a/database/event/2187/event_2187_evp_summary.xlsx
+++ b/database/event/2187/event_2187_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.169600000000001</v>
+        <v>7.012</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5194</v>
+        <v>1.3041</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8109</v>
+        <v>2.5276</v>
       </c>
       <c r="E2" t="n">
-        <v>8.169600000000001</v>
+        <v>7.012</v>
       </c>
       <c r="F2" t="n">
-        <v>3.876</v>
+        <v>3.4058</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2936</v>
+        <v>3.6062</v>
       </c>
       <c r="H2" t="n">
-        <v>3.876</v>
+        <v>6.5137</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1416</v>
+        <v>3.3868</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2936</v>
+        <v>3.6062</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>127</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4352</v>
+        <v>6.993</v>
       </c>
       <c r="N2" t="n">
         <v>268</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9481</v>
+        <v>5.1951</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1062</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9258</v>
+        <v>1.7073</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9481</v>
+        <v>5.1951</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5838</v>
+        <v>3.3329</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3643</v>
+        <v>1.8622</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5838</v>
+        <v>6.2567</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9048</v>
+        <v>3.2532</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3643</v>
+        <v>1.8622</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2691</v>
+        <v>5.1154</v>
       </c>
       <c r="N3" t="n">
         <v>223</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5293</v>
+        <v>5.077</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0284</v>
+        <v>0.9442</v>
       </c>
       <c r="D4" t="n">
-        <v>1.759</v>
+        <v>1.654</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5293</v>
+        <v>5.077</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5941</v>
+        <v>3.4487</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9352</v>
+        <v>1.6283</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5941</v>
+        <v>6.6648</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9131</v>
+        <v>3.4654</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9352</v>
+        <v>1.6283</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.8483</v>
+        <v>5.0937</v>
       </c>
       <c r="N4" t="n">
         <v>213</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1897</v>
+        <v>5.0399</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.9373</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6237</v>
+        <v>1.6372</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1897</v>
+        <v>5.0399</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3122</v>
+        <v>3.042</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8774999999999999</v>
+        <v>1.9979</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7885</v>
+        <v>5.2318</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8812</v>
+        <v>2.7203</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8774999999999999</v>
+        <v>1.9979</v>
       </c>
       <c r="K5" t="n">
         <v>274</v>
@@ -667,7 +667,7 @@
         <v>130</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7587</v>
+        <v>4.7182</v>
       </c>
       <c r="N5" t="n">
         <v>404</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.1598</v>
+        <v>4.8915</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9596</v>
+        <v>0.9097</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6118</v>
+        <v>1.5703</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1598</v>
+        <v>4.8915</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0991</v>
+        <v>3.1377</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0607</v>
+        <v>1.7538</v>
       </c>
       <c r="H6" t="n">
-        <v>3.0991</v>
+        <v>5.569</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5119</v>
+        <v>2.8956</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0607</v>
+        <v>1.7538</v>
       </c>
       <c r="K6" t="n">
         <v>274</v>
@@ -713,7 +713,7 @@
         <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5726</v>
+        <v>4.6494</v>
       </c>
       <c r="N6" t="n">
         <v>404</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0686</v>
+        <v>4.8912</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9427</v>
+        <v>0.9097</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5754</v>
+        <v>1.5701</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0686</v>
+        <v>4.8912</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9703</v>
+        <v>2.7484</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0983</v>
+        <v>2.1428</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9703</v>
+        <v>4.1973</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4075</v>
+        <v>2.1824</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0983</v>
+        <v>2.1428</v>
       </c>
       <c r="K7" t="n">
-        <v>274</v>
+        <v>196</v>
       </c>
       <c r="L7" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="M7" t="n">
-        <v>4.505800000000001</v>
+        <v>4.3252</v>
       </c>
       <c r="N7" t="n">
-        <v>404</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7798</v>
+        <v>4.651</v>
       </c>
       <c r="C8" t="n">
-        <v>0.889</v>
+        <v>0.865</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4604</v>
+        <v>1.4617</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7798</v>
+        <v>4.651</v>
       </c>
       <c r="F8" t="n">
-        <v>2.119</v>
+        <v>3.6743</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6608</v>
+        <v>0.9767</v>
       </c>
       <c r="H8" t="n">
-        <v>2.119</v>
+        <v>7.4595</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7175</v>
+        <v>3.8786</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6608</v>
+        <v>0.9767</v>
       </c>
       <c r="K8" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="L8" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>4.3783</v>
+        <v>4.8553</v>
       </c>
       <c r="N8" t="n">
-        <v>234</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3908</v>
+        <v>4.5532</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8166</v>
+        <v>0.8468</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3054</v>
+        <v>1.4175</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3908</v>
+        <v>4.5532</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5613</v>
+        <v>2.7453</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8295</v>
+        <v>1.8079</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5613</v>
+        <v>4.1865</v>
       </c>
       <c r="I9" t="n">
-        <v>2.076</v>
+        <v>2.1768</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8295</v>
+        <v>1.8079</v>
       </c>
       <c r="K9" t="n">
         <v>141</v>
@@ -851,7 +851,7 @@
         <v>127</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9055</v>
+        <v>3.9847</v>
       </c>
       <c r="N9" t="n">
         <v>268</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9647</v>
+        <v>4.2713</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7944</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1356</v>
+        <v>1.2903</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9647</v>
+        <v>4.2713</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2351</v>
+        <v>3.1383</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7296</v>
+        <v>1.133</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2351</v>
+        <v>5.5711</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6221</v>
+        <v>2.8967</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7296</v>
+        <v>1.133</v>
       </c>
       <c r="K10" t="n">
         <v>141</v>
@@ -897,7 +897,7 @@
         <v>127</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3517</v>
+        <v>4.0297</v>
       </c>
       <c r="N10" t="n">
         <v>268</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2178</v>
+        <v>3.7926</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5985</v>
+        <v>0.7054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8381</v>
+        <v>1.0742</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2178</v>
+        <v>3.7926</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3389</v>
+        <v>2.2989</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8789</v>
+        <v>1.4937</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3389</v>
+        <v>2.6135</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0852</v>
+        <v>1.3589</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8789</v>
+        <v>1.4937</v>
       </c>
       <c r="K11" t="n">
         <v>106</v>
@@ -943,7 +943,7 @@
         <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9641</v>
+        <v>2.8526</v>
       </c>
       <c r="N11" t="n">
         <v>223</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.192</v>
+        <v>3.5871</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5937</v>
+        <v>0.6671</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8278</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.192</v>
+        <v>3.5871</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0129</v>
+        <v>3.1348</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1791</v>
+        <v>0.4523</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0129</v>
+        <v>5.5588</v>
       </c>
       <c r="I12" t="n">
-        <v>2.442</v>
+        <v>2.8903</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1791</v>
+        <v>0.4523</v>
       </c>
       <c r="K12" t="n">
         <v>42</v>
@@ -989,7 +989,7 @@
         <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6211</v>
+        <v>3.3426</v>
       </c>
       <c r="N12" t="n">
         <v>145</v>
@@ -998,219 +998,219 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0904</v>
+        <v>3.2725</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5748</v>
+        <v>0.6086</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7873</v>
+        <v>0.8394</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0904</v>
+        <v>3.2725</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8788</v>
+        <v>2.7735</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2116</v>
+        <v>0.499</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8788</v>
+        <v>4.2858</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3333</v>
+        <v>2.2284</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2116</v>
+        <v>0.499</v>
       </c>
       <c r="K13" t="n">
-        <v>141</v>
+        <v>274</v>
       </c>
       <c r="L13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5449</v>
+        <v>2.7274</v>
       </c>
       <c r="N13" t="n">
-        <v>268</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.734</v>
+        <v>3.2576</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5085</v>
+        <v>0.6059</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6453</v>
+        <v>0.8326</v>
       </c>
       <c r="E14" t="n">
-        <v>2.734</v>
+        <v>3.2576</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0823</v>
+        <v>3.0691</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3483</v>
+        <v>0.1885</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0823</v>
+        <v>5.3272</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4983</v>
+        <v>2.7699</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3483</v>
+        <v>0.1885</v>
       </c>
       <c r="K14" t="n">
-        <v>42</v>
+        <v>141</v>
       </c>
       <c r="L14" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="M14" t="n">
-        <v>2.15</v>
+        <v>2.9584</v>
       </c>
       <c r="N14" t="n">
-        <v>145</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.5887</v>
+        <v>3.0411</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4815</v>
+        <v>0.5656</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5874</v>
+        <v>0.7349</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5887</v>
+        <v>3.0411</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3512</v>
+        <v>3.1039</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2375</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3512</v>
+        <v>5.4499</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9057</v>
+        <v>2.8337</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2375</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1432</v>
+        <v>2.7709</v>
       </c>
       <c r="N15" t="n">
-        <v>223</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.39</v>
+        <v>2.6884</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4445</v>
+        <v>0.5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5083</v>
+        <v>0.5757</v>
       </c>
       <c r="E16" t="n">
-        <v>2.39</v>
+        <v>2.6884</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0294</v>
+        <v>2.6435</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4193</v>
+        <v>0.0449</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0294</v>
+        <v>3.8276</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0238</v>
+        <v>1.9902</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4193</v>
+        <v>0.0449</v>
       </c>
       <c r="K16" t="n">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="L16" t="n">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3955</v>
+        <v>2.0351</v>
       </c>
       <c r="N16" t="n">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3503</v>
+        <v>2.6145</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4371</v>
+        <v>0.4863</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4924</v>
+        <v>0.5423</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3503</v>
+        <v>2.6145</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0621</v>
+        <v>1.9771</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2882</v>
+        <v>0.6374</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0621</v>
+        <v>1.9771</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6714</v>
+        <v>1.028</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2882</v>
+        <v>0.6374</v>
       </c>
       <c r="K17" t="n">
         <v>274</v>
@@ -1219,7 +1219,7 @@
         <v>130</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9596</v>
+        <v>1.6654</v>
       </c>
       <c r="N17" t="n">
         <v>404</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3843</v>
+        <v>2.3518</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2575</v>
+        <v>0.4374</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1076</v>
+        <v>0.4237</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3843</v>
+        <v>2.3518</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9401</v>
+        <v>0.442</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3244</v>
+        <v>1.9099</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9401</v>
+        <v>0.442</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.762</v>
+        <v>0.2298</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3244</v>
+        <v>1.9099</v>
       </c>
       <c r="K18" t="n">
         <v>196</v>
@@ -1265,7 +1265,7 @@
         <v>38</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5624</v>
+        <v>2.1397</v>
       </c>
       <c r="N18" t="n">
         <v>234</v>
@@ -1274,676 +1274,676 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>arch</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9983</v>
+        <v>1.9721</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1857</v>
+        <v>0.3668</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0462</v>
+        <v>0.2523</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9983</v>
+        <v>1.9721</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5965</v>
+        <v>2.2953</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4018</v>
+        <v>-0.3232</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5965</v>
+        <v>2.6008</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4835</v>
+        <v>1.3523</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4018</v>
+        <v>-0.3232</v>
       </c>
       <c r="K19" t="n">
-        <v>274</v>
+        <v>134</v>
       </c>
       <c r="L19" t="n">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8853</v>
+        <v>1.0291</v>
       </c>
       <c r="N19" t="n">
-        <v>404</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9932</v>
+        <v>1.8015</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1847</v>
+        <v>0.335</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0482</v>
+        <v>0.1753</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9932</v>
+        <v>1.8015</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9932</v>
+        <v>1.8731</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.0716</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9932</v>
+        <v>1.8731</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9932</v>
+        <v>0.9739</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.0716</v>
       </c>
       <c r="K20" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9932</v>
+        <v>0.9023</v>
       </c>
       <c r="N20" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9883</v>
+        <v>1.7871</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1838</v>
+        <v>0.3324</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0502</v>
+        <v>0.1688</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9883</v>
+        <v>1.7871</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1637</v>
+        <v>1.7263</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1754</v>
+        <v>0.0608</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1637</v>
+        <v>1.7263</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9432</v>
+        <v>0.8976</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1754</v>
+        <v>0.0608</v>
       </c>
       <c r="K21" t="n">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="L21" t="n">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7678</v>
+        <v>0.9583999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>145</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>arch</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7534</v>
+        <v>1.6412</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1401</v>
+        <v>0.3052</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1438</v>
+        <v>0.1029</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7534</v>
+        <v>1.6412</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3326</v>
+        <v>1.6412</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3326</v>
+        <v>1.6412</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0801</v>
+        <v>1.6412</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="L22" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5009</v>
+        <v>1.6412</v>
       </c>
       <c r="N22" t="n">
-        <v>213</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6337</v>
+        <v>1.3983</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1179</v>
+        <v>0.2601</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1914</v>
+        <v>-0.0068</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6337</v>
+        <v>1.3983</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6324</v>
+        <v>0.8718</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0013</v>
+        <v>0.5265</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6324</v>
+        <v>0.8718</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.4533</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0013</v>
+        <v>0.5265</v>
       </c>
       <c r="K23" t="n">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L23" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5138999999999999</v>
+        <v>0.9798</v>
       </c>
       <c r="N23" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4279</v>
+        <v>1.2766</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0796</v>
+        <v>0.2374</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2734</v>
+        <v>-0.0617</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4279</v>
+        <v>1.2766</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4279</v>
+        <v>-0.5243</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.8009</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4279</v>
+        <v>-0.5243</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4279</v>
+        <v>-0.2726</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.8009</v>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4279</v>
+        <v>1.5283</v>
       </c>
       <c r="N24" t="n">
-        <v>90</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3315</v>
+        <v>1.1995</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0617</v>
+        <v>0.2231</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3118</v>
+        <v>-0.0965</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3315</v>
+        <v>1.1995</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4141</v>
+        <v>2.1927</v>
       </c>
       <c r="G25" t="n">
-        <v>1.7456</v>
+        <v>-0.9932</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.4141</v>
+        <v>2.2392</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1462</v>
+        <v>1.1643</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7456</v>
+        <v>-0.9932</v>
       </c>
       <c r="K25" t="n">
-        <v>196</v>
+        <v>42</v>
       </c>
       <c r="L25" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5993999999999999</v>
+        <v>0.1710999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>234</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0959</v>
+        <v>0.5274</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0178</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4057</v>
+        <v>-0.3999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0959</v>
+        <v>0.5274</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3325</v>
+        <v>0.5274</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4284</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3325</v>
+        <v>0.5274</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2695</v>
+        <v>0.5274</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4284</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="L26" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1589</v>
+        <v>0.5274</v>
       </c>
       <c r="N26" t="n">
-        <v>234</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>AiyvaN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2601</v>
+        <v>0.4877</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0484</v>
+        <v>0.0907</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5475</v>
+        <v>-0.4178</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2601</v>
+        <v>0.4877</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2601</v>
+        <v>1.0526</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.5649</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2601</v>
+        <v>1.0526</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2601</v>
+        <v>0.5473</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.5649</v>
       </c>
       <c r="K27" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2601</v>
+        <v>-0.01759999999999995</v>
       </c>
       <c r="N27" t="n">
-        <v>123</v>
+        <v>213</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AiyvaN</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2737</v>
+        <v>0.4063</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0509</v>
+        <v>0.0756</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.553</v>
+        <v>-0.4546</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2737</v>
+        <v>0.4063</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6697</v>
+        <v>-1.012</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.9434</v>
+        <v>1.4183</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6697</v>
+        <v>-1.012</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5427999999999999</v>
+        <v>-0.5262</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9434</v>
+        <v>1.4183</v>
       </c>
       <c r="K28" t="n">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L28" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4006000000000001</v>
+        <v>0.8920999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2943</v>
+        <v>0.0751</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0547</v>
+        <v>0.014</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5612</v>
+        <v>-0.6041</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2943</v>
+        <v>0.0751</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1685</v>
+        <v>0.0751</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.4628</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1685</v>
+        <v>0.0751</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.0751</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.4628</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="L29" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5157</v>
+        <v>0.0751</v>
       </c>
       <c r="N29" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4327</v>
+        <v>0.0402</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0805</v>
+        <v>0.0075</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6163</v>
+        <v>-0.6199</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4327</v>
+        <v>0.0402</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4327</v>
+        <v>0.9051</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.8649</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4327</v>
+        <v>0.9051</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4327</v>
+        <v>0.4706</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.8649</v>
       </c>
       <c r="K30" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4327</v>
+        <v>-0.3943</v>
       </c>
       <c r="N30" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>pauf</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6798</v>
+        <v>-0.1158</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1264</v>
+        <v>-0.0215</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7147</v>
+        <v>-0.6903</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6798</v>
+        <v>-0.1158</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.2472</v>
+        <v>0.931</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5674</v>
+        <v>-1.0468</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.2472</v>
+        <v>0.931</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0109</v>
+        <v>0.4841</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5674</v>
+        <v>-1.0468</v>
       </c>
       <c r="K31" t="n">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="L31" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4434999999999999</v>
+        <v>-0.5627</v>
       </c>
       <c r="N31" t="n">
-        <v>268</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pauf</t>
+          <t>crush</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8135</v>
+        <v>-0.1253</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1513</v>
+        <v>-0.0233</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.768</v>
+        <v>-0.6946</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8135</v>
+        <v>-0.1253</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1314</v>
+        <v>0.3498</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.9449</v>
+        <v>-0.4751</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1314</v>
+        <v>0.3498</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1065</v>
+        <v>0.1819</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9449</v>
+        <v>-0.4751</v>
       </c>
       <c r="K32" t="n">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="L32" t="n">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8383999999999999</v>
+        <v>-0.2932</v>
       </c>
       <c r="N32" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.844</v>
+        <v>-0.2773</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.157</v>
+        <v>-0.0516</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7802</v>
+        <v>-0.7632</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.844</v>
+        <v>-0.2773</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.844</v>
+        <v>-0.2773</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.844</v>
+        <v>-0.2773</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.844</v>
+        <v>-0.2773</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.844</v>
+        <v>-0.2773</v>
       </c>
       <c r="N33" t="n">
         <v>123</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.978</v>
+        <v>-0.4917</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1819</v>
+        <v>-0.0914</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8335</v>
+        <v>-0.86</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.978</v>
+        <v>-0.4917</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.978</v>
+        <v>-0.4917</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.978</v>
+        <v>-0.4917</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.978</v>
+        <v>-0.4917</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.978</v>
+        <v>-0.4917</v>
       </c>
       <c r="N34" t="n">
         <v>123</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.041</v>
+        <v>-0.517</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1936</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8586</v>
+        <v>-0.8714</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.041</v>
+        <v>-0.517</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3474</v>
+        <v>-0.517</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.3884</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3474</v>
+        <v>-0.517</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2816</v>
+        <v>-0.517</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.3884</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="L35" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1068</v>
+        <v>-0.517</v>
       </c>
       <c r="N35" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>crush</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0681</v>
+        <v>-0.6748</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1986</v>
+        <v>-0.1255</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9427</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0681</v>
+        <v>-0.6748</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3721</v>
+        <v>-1.3143</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.696</v>
+        <v>0.6395</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3721</v>
+        <v>-1.3143</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3016</v>
+        <v>-0.6834</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.696</v>
+        <v>0.6395</v>
       </c>
       <c r="K36" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="L36" t="n">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9975999999999999</v>
+        <v>-0.04390000000000005</v>
       </c>
       <c r="N36" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.4149</v>
+        <v>-1.011</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2631</v>
+        <v>-0.188</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0076</v>
+        <v>-1.0944</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.4149</v>
+        <v>-1.011</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.4149</v>
+        <v>-1.011</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.4149</v>
+        <v>-1.011</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4149</v>
+        <v>-1.011</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4149</v>
+        <v>-1.011</v>
       </c>
       <c r="N37" t="n">
         <v>90</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7102</v>
+        <v>-1.2516</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3181</v>
+        <v>-0.2328</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1253</v>
+        <v>-1.203</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7102</v>
+        <v>-1.2516</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7102</v>
+        <v>-1.2516</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7102</v>
+        <v>-1.2516</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.7102</v>
+        <v>-1.2516</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7102</v>
+        <v>-1.2516</v>
       </c>
       <c r="N38" t="n">
         <v>90</v>
@@ -2194,32 +2194,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.796</v>
+        <v>-1.2717</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.334</v>
+        <v>-0.2365</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1594</v>
+        <v>-1.2121</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.796</v>
+        <v>-1.2717</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.796</v>
+        <v>-1.2717</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.796</v>
+        <v>-1.2717</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.796</v>
+        <v>-1.2717</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.796</v>
+        <v>-1.2717</v>
       </c>
       <c r="N39" t="n">
         <v>90</v>
@@ -2240,32 +2240,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8393</v>
+        <v>-1.3934</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3421</v>
+        <v>-0.2591</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1767</v>
+        <v>-1.2671</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8393</v>
+        <v>-1.3934</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8393</v>
+        <v>-1.3934</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8393</v>
+        <v>-1.3934</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8393</v>
+        <v>-1.3934</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8393</v>
+        <v>-1.3934</v>
       </c>
       <c r="N40" t="n">
         <v>90</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9772</v>
+        <v>-1.4268</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3677</v>
+        <v>-0.2654</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2316</v>
+        <v>-1.2821</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9772</v>
+        <v>-1.4268</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.2944</v>
+        <v>-0.0238</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.6828</v>
+        <v>-1.403</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2944</v>
+        <v>-0.0238</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2386</v>
+        <v>-0.0124</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.6828</v>
+        <v>-1.403</v>
       </c>
       <c r="K41" t="n">
         <v>106</v>
@@ -2323,7 +2323,7 @@
         <v>117</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.9214</v>
+        <v>-1.4154</v>
       </c>
       <c r="N41" t="n">
         <v>223</v>
@@ -2429,10 +2429,10 @@
         <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8666</v>
+        <v>0.8477</v>
       </c>
       <c r="J2" t="n">
-        <v>23.3982</v>
+        <v>22.8879</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4065</v>
+        <v>0.4014</v>
       </c>
       <c r="J3" t="n">
-        <v>10.9755</v>
+        <v>10.8378</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2982</v>
+        <v>0.3221</v>
       </c>
       <c r="J4" t="n">
-        <v>8.051399999999999</v>
+        <v>8.6967</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0583</v>
+        <v>0.1075</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5741</v>
+        <v>2.9025</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2246</v>
+        <v>-0.1581</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.0642</v>
+        <v>-4.2687</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4018</v>
+        <v>0.4657</v>
       </c>
       <c r="J7" t="n">
-        <v>10.8486</v>
+        <v>12.5739</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2981</v>
+        <v>0.3369</v>
       </c>
       <c r="J8" t="n">
-        <v>8.0487</v>
+        <v>9.096299999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2663</v>
+        <v>0.2986</v>
       </c>
       <c r="J9" t="n">
-        <v>7.1901</v>
+        <v>8.062200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0202</v>
+        <v>-0.0021</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5454</v>
+        <v>-0.0567</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5888</v>
+        <v>-0.3863</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.8976</v>
+        <v>-10.4301</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0508</v>
+        <v>-0.0725</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2192</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.71</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3374</v>
+        <v>-0.2738</v>
       </c>
       <c r="J13" t="n">
-        <v>-8.0976</v>
+        <v>-6.5712</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.54</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6292</v>
+        <v>-0.4313</v>
       </c>
       <c r="J14" t="n">
-        <v>-15.1008</v>
+        <v>-10.3512</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.49</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7004</v>
+        <v>-0.4782</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.8096</v>
+        <v>-11.4768</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.47</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7277</v>
+        <v>-0.4971</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.4648</v>
+        <v>-11.9304</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.63</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7262</v>
       </c>
       <c r="J17" t="n">
-        <v>19.1256</v>
+        <v>17.4288</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.46</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6002</v>
+        <v>0.5513</v>
       </c>
       <c r="J18" t="n">
-        <v>14.4048</v>
+        <v>13.2312</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.457</v>
+        <v>0.4473</v>
       </c>
       <c r="J19" t="n">
-        <v>10.968</v>
+        <v>10.7352</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3895</v>
+        <v>0.3924</v>
       </c>
       <c r="J20" t="n">
-        <v>9.348000000000001</v>
+        <v>9.4176</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2275</v>
+        <v>0.2501</v>
       </c>
       <c r="J21" t="n">
-        <v>5.46</v>
+        <v>6.0024</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.78</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7236</v>
+        <v>1.4745</v>
       </c>
       <c r="J22" t="n">
-        <v>44.8136</v>
+        <v>38.337</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7587</v>
       </c>
       <c r="J23" t="n">
-        <v>19.1464</v>
+        <v>19.7262</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3507</v>
+        <v>0.4262</v>
       </c>
       <c r="J24" t="n">
-        <v>9.1182</v>
+        <v>11.0812</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2695</v>
+        <v>0.3463</v>
       </c>
       <c r="J25" t="n">
-        <v>7.007</v>
+        <v>9.0038</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4626</v>
+        <v>-0.3864</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.0276</v>
+        <v>-10.0464</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1947</v>
+        <v>0.1886</v>
       </c>
       <c r="J27" t="n">
-        <v>5.0622</v>
+        <v>4.9036</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0534</v>
+        <v>-0.0543</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.3884</v>
+        <v>-1.4118</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.86</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2592</v>
+        <v>-0.1662</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.7392</v>
+        <v>-4.3212</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.293</v>
+        <v>-0.1868</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.618</v>
+        <v>-4.8568</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3716</v>
+        <v>-0.2371</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.6616</v>
+        <v>-6.1646</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.62</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4455</v>
+        <v>1.2876</v>
       </c>
       <c r="J32" t="n">
-        <v>36.1375</v>
+        <v>32.19</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5326</v>
+        <v>0.5812</v>
       </c>
       <c r="J33" t="n">
-        <v>13.315</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.19</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4756</v>
+        <v>0.5333</v>
       </c>
       <c r="J34" t="n">
-        <v>11.89</v>
+        <v>13.3325</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.08</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1683</v>
+        <v>0.24</v>
       </c>
       <c r="J35" t="n">
-        <v>4.2075</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1305</v>
+        <v>-0.0536</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.2625</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5028</v>
+        <v>0.5891</v>
       </c>
       <c r="J37" t="n">
-        <v>12.57</v>
+        <v>14.7275</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.87</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2111</v>
+        <v>-0.1528</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.2775</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.85</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2566</v>
+        <v>-0.1726</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.415</v>
+        <v>-4.315</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4333</v>
+        <v>-0.281</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.8325</v>
+        <v>-7.025</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6096</v>
+        <v>-0.4042</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.24</v>
+        <v>-10.105</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.631</v>
       </c>
       <c r="J42" t="n">
-        <v>18.3036</v>
+        <v>17.668</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3767</v>
+        <v>0.3754</v>
       </c>
       <c r="J43" t="n">
-        <v>10.5476</v>
+        <v>10.5112</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.12</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3767</v>
+        <v>0.3754</v>
       </c>
       <c r="J44" t="n">
-        <v>10.5476</v>
+        <v>10.5112</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2324</v>
+        <v>0.2663</v>
       </c>
       <c r="J45" t="n">
-        <v>6.5072</v>
+        <v>7.4564</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1424</v>
+        <v>-0.0793</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.9872</v>
+        <v>-2.2204</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.17</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3654</v>
+        <v>0.4076</v>
       </c>
       <c r="J47" t="n">
-        <v>10.2312</v>
+        <v>11.4128</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.98</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0203</v>
+        <v>-0.0298</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.5684</v>
+        <v>-0.8344</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.93</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1332</v>
+        <v>-0.0936</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.7296</v>
+        <v>-2.6208</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2359</v>
+        <v>-0.1481</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.6052</v>
+        <v>-4.1468</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5323</v>
+        <v>-0.3467</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.9044</v>
+        <v>-9.707599999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1828</v>
+        <v>1.1133</v>
       </c>
       <c r="J52" t="n">
-        <v>31.9356</v>
+        <v>30.0591</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6209</v>
+        <v>0.6161</v>
       </c>
       <c r="J53" t="n">
-        <v>16.7643</v>
+        <v>16.6347</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.11</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2892</v>
+        <v>0.3398</v>
       </c>
       <c r="J54" t="n">
-        <v>7.8084</v>
+        <v>9.1746</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.1297</v>
       </c>
       <c r="J55" t="n">
-        <v>1.8495</v>
+        <v>3.5019</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3139</v>
+        <v>-0.2397</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.475300000000001</v>
+        <v>-6.4719</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.48</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7667</v>
+        <v>0.9568</v>
       </c>
       <c r="J57" t="n">
-        <v>20.7009</v>
+        <v>25.8336</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0698</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.349</v>
+        <v>-1.8846</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2171</v>
+        <v>-0.1372</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.8617</v>
+        <v>-3.7044</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5581</v>
+        <v>-0.3653</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.0687</v>
+        <v>-9.863099999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.571</v>
+        <v>-0.3747</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.417</v>
+        <v>-10.1169</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7987</v>
+        <v>0.777</v>
       </c>
       <c r="J62" t="n">
-        <v>22.3636</v>
+        <v>21.756</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.24</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7032</v>
+        <v>0.6802</v>
       </c>
       <c r="J63" t="n">
-        <v>19.6896</v>
+        <v>19.0456</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4674</v>
+        <v>0.454</v>
       </c>
       <c r="J64" t="n">
-        <v>13.0872</v>
+        <v>12.712</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1424</v>
+        <v>-0.0793</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.9872</v>
+        <v>-2.2204</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.87</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5271</v>
+        <v>-0.464</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.7588</v>
+        <v>-12.992</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2879</v>
+        <v>0.3143</v>
       </c>
       <c r="J67" t="n">
-        <v>8.061199999999999</v>
+        <v>8.8004</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2718</v>
+        <v>0.2944</v>
       </c>
       <c r="J68" t="n">
-        <v>7.6104</v>
+        <v>8.2432</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1632</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.5696</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2526</v>
+        <v>-0.153</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.0728</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3768</v>
+        <v>-0.2357</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.5504</v>
+        <v>-6.5996</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3565</v>
+        <v>0.4035</v>
       </c>
       <c r="J72" t="n">
-        <v>9.981999999999999</v>
+        <v>11.298</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3112</v>
+        <v>0.3467</v>
       </c>
       <c r="J73" t="n">
-        <v>8.7136</v>
+        <v>9.707599999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1768</v>
+        <v>0.185</v>
       </c>
       <c r="J74" t="n">
-        <v>4.9504</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3074</v>
+        <v>-0.1873</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.607200000000001</v>
+        <v>-5.2444</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4928</v>
+        <v>-0.3165</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.7984</v>
+        <v>-8.862</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8012</v>
+        <v>0.7981</v>
       </c>
       <c r="J77" t="n">
-        <v>22.4336</v>
+        <v>22.3468</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7538</v>
+        <v>0.7516</v>
       </c>
       <c r="J78" t="n">
-        <v>21.1064</v>
+        <v>21.0448</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6803</v>
+        <v>0.6813</v>
       </c>
       <c r="J79" t="n">
-        <v>19.0484</v>
+        <v>19.0764</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.18</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4789</v>
+        <v>0.5148</v>
       </c>
       <c r="J80" t="n">
-        <v>13.4092</v>
+        <v>14.4144</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4433</v>
+        <v>-0.3702</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.4124</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4623</v>
+        <v>0.5359</v>
       </c>
       <c r="J82" t="n">
-        <v>13.869</v>
+        <v>16.077</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2523</v>
+        <v>0.2647</v>
       </c>
       <c r="J83" t="n">
-        <v>7.569</v>
+        <v>7.941</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.296</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.91</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1846</v>
+        <v>-0.1164</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.538</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.756</v>
+        <v>-0.5132</v>
       </c>
       <c r="J86" t="n">
-        <v>-22.68</v>
+        <v>-15.396</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.6</v>
       </c>
       <c r="I87" t="n">
-        <v>1.4441</v>
+        <v>1.2844</v>
       </c>
       <c r="J87" t="n">
-        <v>43.323</v>
+        <v>38.532</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9792</v>
+        <v>0.9669</v>
       </c>
       <c r="J88" t="n">
-        <v>29.376</v>
+        <v>29.007</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1737</v>
+        <v>0.2279</v>
       </c>
       <c r="J89" t="n">
-        <v>5.211</v>
+        <v>6.837</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2409</v>
+        <v>-0.1681</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.227</v>
+        <v>-5.043</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9</v>
+        <v>-0.8633</v>
       </c>
       <c r="J91" t="n">
-        <v>-27</v>
+        <v>-25.899</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.71</v>
       </c>
       <c r="I92" t="n">
-        <v>1.597</v>
+        <v>1.1156</v>
       </c>
       <c r="J92" t="n">
-        <v>38.328</v>
+        <v>26.7744</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5615</v>
+        <v>0.5043</v>
       </c>
       <c r="J93" t="n">
-        <v>13.476</v>
+        <v>12.1032</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.18</v>
       </c>
       <c r="I94" t="n">
-        <v>0.429</v>
+        <v>0.4332</v>
       </c>
       <c r="J94" t="n">
-        <v>10.296</v>
+        <v>10.3968</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.15</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3497</v>
+        <v>0.3881</v>
       </c>
       <c r="J95" t="n">
-        <v>8.392799999999999</v>
+        <v>9.314399999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1993</v>
+        <v>-0.1164</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.7832</v>
+        <v>-2.7936</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7163</v>
+        <v>0.6624</v>
       </c>
       <c r="J97" t="n">
-        <v>17.1912</v>
+        <v>15.8976</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0998</v>
+        <v>-0.0877</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.3952</v>
+        <v>-2.1048</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.7</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4921</v>
+        <v>-0.3205</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.8104</v>
+        <v>-7.692</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.66</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5462</v>
+        <v>-0.3584</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.1088</v>
+        <v>-8.601599999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5594</v>
+        <v>-0.3678</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.4256</v>
+        <v>-8.827199999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.524</v>
+        <v>0.4271</v>
       </c>
       <c r="J102" t="n">
-        <v>15.196</v>
+        <v>12.3859</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4112</v>
+        <v>0.3641</v>
       </c>
       <c r="J103" t="n">
-        <v>11.9248</v>
+        <v>10.5589</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1258</v>
+        <v>0.152</v>
       </c>
       <c r="J104" t="n">
-        <v>3.6482</v>
+        <v>4.408</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0016</v>
+        <v>0.0408</v>
       </c>
       <c r="J105" t="n">
-        <v>0.0464</v>
+        <v>1.1832</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1198</v>
+        <v>-0.0683</v>
       </c>
       <c r="J106" t="n">
-        <v>-3.4742</v>
+        <v>-1.9807</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3416</v>
+        <v>0.364</v>
       </c>
       <c r="J107" t="n">
-        <v>9.9064</v>
+        <v>10.556</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1578</v>
+        <v>0.1631</v>
       </c>
       <c r="J108" t="n">
-        <v>4.5762</v>
+        <v>4.7299</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.04</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1173</v>
+        <v>0.1172</v>
       </c>
       <c r="J109" t="n">
-        <v>3.4017</v>
+        <v>3.3988</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.96</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1118</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.2422</v>
+        <v>-1.8183</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.466</v>
+        <v>-0.2973</v>
       </c>
       <c r="J111" t="n">
-        <v>-13.514</v>
+        <v>-8.621700000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5326</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>15.978</v>
+        <v>15.318</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.03</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0912</v>
+        <v>0.0915</v>
       </c>
       <c r="J113" t="n">
-        <v>2.736</v>
+        <v>2.745</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.039</v>
+        <v>0.0375</v>
       </c>
       <c r="J114" t="n">
-        <v>1.17</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0029</v>
+        <v>-0.0001</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5719</v>
+        <v>-0.3741</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.157</v>
+        <v>-11.223</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>1.474</v>
+        <v>1.032</v>
       </c>
       <c r="J117" t="n">
-        <v>44.22</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I118" t="n">
-        <v>1.3014</v>
+        <v>0.9187</v>
       </c>
       <c r="J118" t="n">
-        <v>39.042</v>
+        <v>27.561</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5611</v>
+        <v>0.481</v>
       </c>
       <c r="J119" t="n">
-        <v>16.833</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1233</v>
+        <v>-0.0486</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.699</v>
+        <v>-1.458</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.1234</v>
+        <v>-1.1148</v>
       </c>
       <c r="J121" t="n">
-        <v>-33.702</v>
+        <v>-33.444</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.59</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8309</v>
+        <v>0.5768</v>
       </c>
       <c r="J122" t="n">
-        <v>22.4343</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3612</v>
+        <v>0.3047</v>
       </c>
       <c r="J123" t="n">
-        <v>9.7524</v>
+        <v>8.226900000000001</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2519</v>
+        <v>0.2152</v>
       </c>
       <c r="J124" t="n">
-        <v>6.8013</v>
+        <v>5.8104</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2391</v>
+        <v>-0.1345</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.4557</v>
+        <v>-3.6315</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.68</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5623</v>
+        <v>-0.366</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.1821</v>
+        <v>-9.882</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.28</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4893</v>
+        <v>0.3974</v>
       </c>
       <c r="J127" t="n">
-        <v>13.2111</v>
+        <v>10.7298</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.187</v>
+        <v>0.1544</v>
       </c>
       <c r="J128" t="n">
-        <v>5.049</v>
+        <v>4.1688</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.96</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1203</v>
+        <v>-0.0646</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.2481</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.249</v>
+        <v>-0.1468</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.723</v>
+        <v>-3.9636</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2972</v>
+        <v>-0.1791</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.0244</v>
+        <v>-4.8357</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5717</v>
+        <v>0.5409</v>
       </c>
       <c r="J132" t="n">
-        <v>12.5774</v>
+        <v>11.8998</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1308</v>
+        <v>-0.109</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.8776</v>
+        <v>-2.398</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2896</v>
+        <v>-0.1919</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.3712</v>
+        <v>-4.2218</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.74</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4313</v>
+        <v>-0.2802</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.4886</v>
+        <v>-6.1644</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.51</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7327</v>
+        <v>-0.4955</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.1194</v>
+        <v>-10.901</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4519</v>
+        <v>1.0241</v>
       </c>
       <c r="J137" t="n">
-        <v>31.9418</v>
+        <v>22.5302</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1395</v>
+        <v>0.8289</v>
       </c>
       <c r="J138" t="n">
-        <v>25.069</v>
+        <v>18.2358</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.42</v>
       </c>
       <c r="I139" t="n">
-        <v>0.9915</v>
+        <v>0.7417</v>
       </c>
       <c r="J139" t="n">
-        <v>21.813</v>
+        <v>16.3174</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.1</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1851</v>
+        <v>0.2726</v>
       </c>
       <c r="J140" t="n">
-        <v>4.0722</v>
+        <v>5.9972</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.98</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2623</v>
+        <v>-0.1753</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.7706</v>
+        <v>-3.8566</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.0222</v>
+        <v>-0.0418</v>
       </c>
       <c r="J142" t="n">
-        <v>-0.3774</v>
+        <v>-0.7106</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.57</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.4734</v>
+        <v>-0.3783</v>
       </c>
       <c r="J143" t="n">
-        <v>-8.047800000000001</v>
+        <v>-6.4311</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.45</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.697</v>
+        <v>-0.4895</v>
       </c>
       <c r="J144" t="n">
-        <v>-11.849</v>
+        <v>-8.3215</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.33</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.8746</v>
+        <v>-0.6065</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.8682</v>
+        <v>-10.3105</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.25</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.9812</v>
+        <v>-0.6874</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.6804</v>
+        <v>-11.6858</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.71</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4612</v>
+        <v>1.0536</v>
       </c>
       <c r="J147" t="n">
-        <v>24.8404</v>
+        <v>17.9112</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.64</v>
       </c>
       <c r="I148" t="n">
-        <v>1.3261</v>
+        <v>0.9745</v>
       </c>
       <c r="J148" t="n">
-        <v>22.5437</v>
+        <v>16.5665</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.64</v>
       </c>
       <c r="I149" t="n">
-        <v>1.3261</v>
+        <v>0.9745</v>
       </c>
       <c r="J149" t="n">
-        <v>22.5437</v>
+        <v>16.5665</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.58</v>
       </c>
       <c r="I150" t="n">
-        <v>1.1999</v>
+        <v>0.9067</v>
       </c>
       <c r="J150" t="n">
-        <v>20.3983</v>
+        <v>15.4139</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.25</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4832</v>
+        <v>0.4952</v>
       </c>
       <c r="J151" t="n">
-        <v>8.214399999999999</v>
+        <v>8.4184</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.03</v>
       </c>
       <c r="I152" t="n">
-        <v>0.21</v>
+        <v>0.1967</v>
       </c>
       <c r="J152" t="n">
-        <v>4.41</v>
+        <v>4.1307</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.97</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0467</v>
+        <v>-0.0025</v>
       </c>
       <c r="J153" t="n">
-        <v>0.9807</v>
+        <v>-0.0525</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1537</v>
+        <v>-0.1407</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.2277</v>
+        <v>-2.9547</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5851</v>
+        <v>-0.3931</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.2871</v>
+        <v>-8.255100000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.16</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.1161</v>
+        <v>-0.8005</v>
       </c>
       <c r="J156" t="n">
-        <v>-23.4381</v>
+        <v>-16.8105</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.83</v>
       </c>
       <c r="I157" t="n">
-        <v>1.7188</v>
+        <v>1.2128</v>
       </c>
       <c r="J157" t="n">
-        <v>36.0948</v>
+        <v>25.4688</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.65</v>
       </c>
       <c r="I158" t="n">
-        <v>1.4059</v>
+        <v>1.0041</v>
       </c>
       <c r="J158" t="n">
-        <v>29.5239</v>
+        <v>21.0861</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>1.1071</v>
+        <v>0.8264</v>
       </c>
       <c r="J159" t="n">
-        <v>23.2491</v>
+        <v>17.3544</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2844</v>
+        <v>0.3647</v>
       </c>
       <c r="J160" t="n">
-        <v>5.9724</v>
+        <v>7.6587</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0548</v>
+        <v>0.0313</v>
       </c>
       <c r="J161" t="n">
-        <v>-1.1508</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.91</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0956</v>
       </c>
       <c r="J162" t="n">
-        <v>-2.0724</v>
+        <v>-2.1032</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.9</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1119</v>
+        <v>-0.1074</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.4618</v>
+        <v>-2.3628</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.77</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3479</v>
+        <v>-0.2416</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.6538</v>
+        <v>-5.3152</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4769</v>
+        <v>-0.3171</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.4918</v>
+        <v>-6.9762</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.63</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5618</v>
+        <v>-0.3737</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.3596</v>
+        <v>-8.221399999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.99</v>
       </c>
       <c r="I167" t="n">
-        <v>1.8856</v>
+        <v>1.4044</v>
       </c>
       <c r="J167" t="n">
-        <v>41.4832</v>
+        <v>30.8968</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.46</v>
+        <v>1.0345</v>
       </c>
       <c r="J168" t="n">
-        <v>32.12</v>
+        <v>22.759</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.2</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4185</v>
+        <v>0.4444</v>
       </c>
       <c r="J169" t="n">
-        <v>9.207000000000001</v>
+        <v>9.7768</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.165</v>
+        <v>0.258</v>
       </c>
       <c r="J170" t="n">
-        <v>3.63</v>
+        <v>5.676</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.01</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1229</v>
+        <v>-0.0388</v>
       </c>
       <c r="J171" t="n">
-        <v>-2.7038</v>
+        <v>-0.8536</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.704</v>
+        <v>0.6506</v>
       </c>
       <c r="J172" t="n">
-        <v>19.712</v>
+        <v>18.2168</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.155</v>
+        <v>0.1405</v>
       </c>
       <c r="J173" t="n">
-        <v>4.34</v>
+        <v>3.934</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4019</v>
+        <v>-0.257</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.2532</v>
+        <v>-7.196</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.73</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.459</v>
+        <v>-0.2959</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.852</v>
+        <v>-8.2852</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6797</v>
+        <v>-0.4553</v>
       </c>
       <c r="J176" t="n">
-        <v>-19.0316</v>
+        <v>-12.7484</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2493</v>
+        <v>0.8869</v>
       </c>
       <c r="J177" t="n">
-        <v>34.9804</v>
+        <v>24.8332</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9805</v>
+        <v>0.7198</v>
       </c>
       <c r="J178" t="n">
-        <v>27.454</v>
+        <v>20.1544</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.25</v>
       </c>
       <c r="I179" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.5332</v>
       </c>
       <c r="J179" t="n">
-        <v>18.2196</v>
+        <v>14.9296</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3356</v>
+        <v>0.3761</v>
       </c>
       <c r="J180" t="n">
-        <v>9.396800000000001</v>
+        <v>10.5308</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.83</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6641</v>
+        <v>-0.6029</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.5948</v>
+        <v>-16.8812</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.96</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1329</v>
+        <v>1.0293</v>
       </c>
       <c r="J182" t="n">
-        <v>22.658</v>
+        <v>20.586</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.48</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6249</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>12.498</v>
+        <v>11.442</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.35</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4433</v>
+        <v>0.4366</v>
       </c>
       <c r="J184" t="n">
-        <v>8.866</v>
+        <v>8.731999999999999</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1157</v>
       </c>
       <c r="J185" t="n">
-        <v>1.594</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0469</v>
+        <v>0.0859</v>
       </c>
       <c r="J186" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.718</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.622</v>
+        <v>-1.836</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2629</v>
+        <v>-0.2134</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.258</v>
+        <v>-4.268</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.76</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.312</v>
+        <v>-0.2434</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.24</v>
+        <v>-4.868</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.6</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5815</v>
+        <v>-0.3915</v>
       </c>
       <c r="J190" t="n">
-        <v>-11.63</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6897</v>
+        <v>-0.4663</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.794</v>
+        <v>-9.326000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4779</v>
+        <v>0.5617</v>
       </c>
       <c r="J192" t="n">
-        <v>14.337</v>
+        <v>16.851</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3516</v>
+        <v>0.3992</v>
       </c>
       <c r="J193" t="n">
-        <v>10.548</v>
+        <v>11.976</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.96</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1179</v>
+        <v>-0.064</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.537</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.93</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1772</v>
+        <v>-0.1009</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.316</v>
+        <v>-3.027</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3371</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.651</v>
+        <v>-10.113</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.27</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7695</v>
+        <v>0.7494</v>
       </c>
       <c r="J197" t="n">
-        <v>23.085</v>
+        <v>22.482</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5965</v>
+        <v>0.5783</v>
       </c>
       <c r="J198" t="n">
-        <v>17.895</v>
+        <v>17.349</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.17</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5163</v>
+        <v>0.5028</v>
       </c>
       <c r="J199" t="n">
-        <v>15.489</v>
+        <v>15.084</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I200" t="n">
-        <v>0.159</v>
+        <v>0.2044</v>
       </c>
       <c r="J200" t="n">
-        <v>4.77</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5037</v>
+        <v>-0.4387</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.111</v>
+        <v>-13.161</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.11</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3091</v>
+        <v>0.3275</v>
       </c>
       <c r="J202" t="n">
-        <v>7.7275</v>
+        <v>8.1875</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.001</v>
+        <v>-0.0292</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.025</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2917</v>
+        <v>-0.1992</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.2925</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.77</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3765</v>
+        <v>-0.2478</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.4125</v>
+        <v>-6.195</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.49</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7524</v>
+        <v>-0.5107</v>
       </c>
       <c r="J206" t="n">
-        <v>-18.81</v>
+        <v>-12.7675</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.58</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3484</v>
+        <v>1.2269</v>
       </c>
       <c r="J207" t="n">
-        <v>33.71</v>
+        <v>30.6725</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0885</v>
+        <v>1.0637</v>
       </c>
       <c r="J208" t="n">
-        <v>27.2125</v>
+        <v>26.5925</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5733</v>
       </c>
       <c r="J209" t="n">
-        <v>12.5125</v>
+        <v>14.3325</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.04</v>
       </c>
       <c r="I210" t="n">
-        <v>0.0262</v>
+        <v>0.1036</v>
       </c>
       <c r="J210" t="n">
-        <v>0.655</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.0262</v>
+        <v>0.1036</v>
       </c>
       <c r="J211" t="n">
-        <v>0.655</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5567</v>
+        <v>0.4851</v>
       </c>
       <c r="J212" t="n">
-        <v>15.0309</v>
+        <v>13.0977</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3686</v>
+        <v>0.3209</v>
       </c>
       <c r="J213" t="n">
-        <v>9.952199999999999</v>
+        <v>8.664300000000001</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3686</v>
+        <v>0.3209</v>
       </c>
       <c r="J214" t="n">
-        <v>9.952199999999999</v>
+        <v>8.664300000000001</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3538</v>
+        <v>0.3089</v>
       </c>
       <c r="J215" t="n">
-        <v>9.5526</v>
+        <v>8.340299999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4417</v>
+        <v>-0.2764</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.9259</v>
+        <v>-7.4628</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.3</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5347</v>
+        <v>0.4854</v>
       </c>
       <c r="J217" t="n">
-        <v>14.4369</v>
+        <v>13.1058</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.08</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2093</v>
+        <v>0.1651</v>
       </c>
       <c r="J218" t="n">
-        <v>5.6511</v>
+        <v>4.4577</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.213</v>
+        <v>-0.1296</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.751</v>
+        <v>-3.4992</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3126</v>
+        <v>-0.1934</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.440200000000001</v>
+        <v>-5.2218</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.67</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5514</v>
+        <v>-0.3597</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.8878</v>
+        <v>-9.7119</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.22</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4375</v>
+        <v>0.5023</v>
       </c>
       <c r="J222" t="n">
-        <v>10.9375</v>
+        <v>12.5575</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.97</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.0975</v>
+        <v>-1.1025</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.0975</v>
+        <v>-1.1025</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4087</v>
+        <v>-0.2601</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.2175</v>
+        <v>-6.5025</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4923</v>
+        <v>-0.3182</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.3075</v>
+        <v>-7.955</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.32</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8452</v>
+        <v>0.843</v>
       </c>
       <c r="J227" t="n">
-        <v>21.13</v>
+        <v>21.075</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7514</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>18.785</v>
+        <v>18.7625</v>
       </c>
     </row>
     <row r="229">
@@ -11549,10 +11549,10 @@
         <v>1.15</v>
       </c>
       <c r="I230" t="n">
-        <v>0.3858</v>
+        <v>0.4395</v>
       </c>
       <c r="J230" t="n">
-        <v>9.645</v>
+        <v>10.9875</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.92</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4159</v>
+        <v>-0.3414</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.3975</v>
+        <v>-8.535</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4618</v>
+        <v>0.5413</v>
       </c>
       <c r="J232" t="n">
-        <v>16.6248</v>
+        <v>19.4868</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.09</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2041</v>
+        <v>0.2222</v>
       </c>
       <c r="J233" t="n">
-        <v>7.3476</v>
+        <v>7.9992</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1482</v>
+        <v>0.1585</v>
       </c>
       <c r="J234" t="n">
-        <v>5.3352</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2495</v>
+        <v>-0.1471</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.981999999999999</v>
+        <v>-5.2956</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4155</v>
+        <v>-0.2608</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.958</v>
+        <v>-9.3888</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.42</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1473</v>
+        <v>1.0844</v>
       </c>
       <c r="J237" t="n">
-        <v>41.3028</v>
+        <v>39.0384</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.27</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8176</v>
+        <v>0.7837</v>
       </c>
       <c r="J238" t="n">
-        <v>29.4336</v>
+        <v>28.2132</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.92</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3532</v>
+        <v>-0.2992</v>
       </c>
       <c r="J239" t="n">
-        <v>-12.7152</v>
+        <v>-10.7712</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6798</v>
+        <v>-0.6307</v>
       </c>
       <c r="J240" t="n">
-        <v>-24.4728</v>
+        <v>-22.7052</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8002</v>
+        <v>-0.7586000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-28.8072</v>
+        <v>-27.3096</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I242" t="n">
-        <v>0.03</v>
+        <v>-0.0137</v>
       </c>
       <c r="J242" t="n">
-        <v>0.57</v>
+        <v>-0.2603</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.19</v>
+        <v>-0.1724</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.61</v>
+        <v>-3.2756</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.59</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.5614</v>
+        <v>-0.3878</v>
       </c>
       <c r="J244" t="n">
-        <v>-10.6666</v>
+        <v>-7.3682</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.48</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.7195</v>
+        <v>-0.4906</v>
       </c>
       <c r="J245" t="n">
-        <v>-13.6705</v>
+        <v>-9.321400000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.36</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.874</v>
+        <v>-0.6042</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.606</v>
+        <v>-11.4798</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.93</v>
       </c>
       <c r="I247" t="n">
-        <v>1.8523</v>
+        <v>1.5738</v>
       </c>
       <c r="J247" t="n">
-        <v>35.1937</v>
+        <v>29.9022</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.75</v>
       </c>
       <c r="I248" t="n">
-        <v>1.5379</v>
+        <v>1.3732</v>
       </c>
       <c r="J248" t="n">
-        <v>29.2201</v>
+        <v>26.0908</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.57</v>
       </c>
       <c r="I249" t="n">
-        <v>1.1813</v>
+        <v>1.1696</v>
       </c>
       <c r="J249" t="n">
-        <v>22.4447</v>
+        <v>22.2224</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.34</v>
       </c>
       <c r="I250" t="n">
-        <v>0.6798</v>
+        <v>0.8146</v>
       </c>
       <c r="J250" t="n">
-        <v>12.9162</v>
+        <v>15.4774</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.2</v>
       </c>
       <c r="I251" t="n">
-        <v>0.3715</v>
+        <v>0.4878</v>
       </c>
       <c r="J251" t="n">
-        <v>7.0585</v>
+        <v>9.2682</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.56</v>
       </c>
       <c r="I252" t="n">
-        <v>0.8542999999999999</v>
+        <v>1.0515</v>
       </c>
       <c r="J252" t="n">
-        <v>24.7747</v>
+        <v>30.4935</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.9</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2035</v>
+        <v>-0.1274</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.9015</v>
+        <v>-3.6946</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.87</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2564</v>
+        <v>-0.1595</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.4356</v>
+        <v>-4.6255</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5208</v>
+        <v>-0.3382</v>
       </c>
       <c r="J255" t="n">
-        <v>-15.1032</v>
+        <v>-9.8078</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.66</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.3665</v>
       </c>
       <c r="J256" t="n">
-        <v>-16.24</v>
+        <v>-10.6285</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.4214</v>
+        <v>1.2686</v>
       </c>
       <c r="J257" t="n">
-        <v>41.2206</v>
+        <v>36.7894</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3241</v>
+        <v>0.3478</v>
       </c>
       <c r="J258" t="n">
-        <v>9.398899999999999</v>
+        <v>10.0862</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1921</v>
+        <v>0.2348</v>
       </c>
       <c r="J259" t="n">
-        <v>5.5709</v>
+        <v>6.8092</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.91</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4199</v>
+        <v>-0.3523</v>
       </c>
       <c r="J260" t="n">
-        <v>-12.1771</v>
+        <v>-10.2167</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4199</v>
+        <v>-0.3523</v>
       </c>
       <c r="J261" t="n">
-        <v>-12.1771</v>
+        <v>-10.2167</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4078</v>
+        <v>0.4592</v>
       </c>
       <c r="J262" t="n">
-        <v>9.7872</v>
+        <v>11.0208</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.87</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1828</v>
+        <v>-0.1475</v>
       </c>
       <c r="J263" t="n">
-        <v>-4.3872</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.79</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3369</v>
+        <v>-0.2267</v>
       </c>
       <c r="J264" t="n">
-        <v>-8.085599999999999</v>
+        <v>-5.4408</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.74</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.417</v>
+        <v>-0.2748</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.008</v>
+        <v>-6.5952</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.52</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7134</v>
+        <v>-0.4814</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.1216</v>
+        <v>-11.5536</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.99</v>
       </c>
       <c r="I267" t="n">
-        <v>2.0039</v>
+        <v>1.7106</v>
       </c>
       <c r="J267" t="n">
-        <v>48.0936</v>
+        <v>41.0544</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.13</v>
       </c>
       <c r="I268" t="n">
-        <v>0.2809</v>
+        <v>0.3647</v>
       </c>
       <c r="J268" t="n">
-        <v>6.7416</v>
+        <v>8.752800000000001</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2809</v>
+        <v>0.3647</v>
       </c>
       <c r="J269" t="n">
-        <v>6.7416</v>
+        <v>8.752800000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>0.199</v>
+        <v>0.2818</v>
       </c>
       <c r="J270" t="n">
-        <v>4.776</v>
+        <v>6.7632</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.09</v>
       </c>
       <c r="I271" t="n">
-        <v>0.1708</v>
+        <v>0.2532</v>
       </c>
       <c r="J271" t="n">
-        <v>4.0992</v>
+        <v>6.0768</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.08</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3128</v>
+        <v>0.3339</v>
       </c>
       <c r="J272" t="n">
-        <v>7.5072</v>
+        <v>8.0136</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.7</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.4223</v>
+        <v>-0.2981</v>
       </c>
       <c r="J273" t="n">
-        <v>-10.1352</v>
+        <v>-7.1544</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.65</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.5058</v>
+        <v>-0.3439</v>
       </c>
       <c r="J274" t="n">
-        <v>-12.1392</v>
+        <v>-8.2536</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.64</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.521</v>
+        <v>-0.3532</v>
       </c>
       <c r="J275" t="n">
-        <v>-12.504</v>
+        <v>-8.476800000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.5121</v>
       </c>
       <c r="J276" t="n">
-        <v>-18.06</v>
+        <v>-12.2904</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.76</v>
       </c>
       <c r="I277" t="n">
-        <v>1.6379</v>
+        <v>1.421</v>
       </c>
       <c r="J277" t="n">
-        <v>39.3096</v>
+        <v>34.104</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.56</v>
       </c>
       <c r="I278" t="n">
-        <v>1.264</v>
+        <v>1.1826</v>
       </c>
       <c r="J278" t="n">
-        <v>30.336</v>
+        <v>28.3824</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5263</v>
+        <v>0.625</v>
       </c>
       <c r="J279" t="n">
-        <v>12.6312</v>
+        <v>15</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.17</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3563</v>
+        <v>0.4529</v>
       </c>
       <c r="J280" t="n">
-        <v>8.5512</v>
+        <v>10.8696</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.08</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1184</v>
+        <v>0.207</v>
       </c>
       <c r="J281" t="n">
-        <v>2.8416</v>
+        <v>4.968</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.01</v>
       </c>
       <c r="I282" t="n">
-        <v>1.9719</v>
+        <v>1.6742</v>
       </c>
       <c r="J282" t="n">
-        <v>41.4099</v>
+        <v>35.1582</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.65</v>
       </c>
       <c r="I283" t="n">
-        <v>1.3758</v>
+        <v>1.2675</v>
       </c>
       <c r="J283" t="n">
-        <v>28.8918</v>
+        <v>26.6175</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.34</v>
       </c>
       <c r="I284" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.8258</v>
       </c>
       <c r="J284" t="n">
-        <v>14.6811</v>
+        <v>17.3418</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.3</v>
       </c>
       <c r="I285" t="n">
-        <v>0.612</v>
+        <v>0.7361</v>
       </c>
       <c r="J285" t="n">
-        <v>12.852</v>
+        <v>15.4581</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.2</v>
       </c>
       <c r="I286" t="n">
-        <v>0.3863</v>
+        <v>0.4992</v>
       </c>
       <c r="J286" t="n">
-        <v>8.112299999999999</v>
+        <v>10.4832</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.89</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.0625</v>
+        <v>-0.081</v>
       </c>
       <c r="J287" t="n">
-        <v>-1.3125</v>
+        <v>-1.701</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.71</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3505</v>
+        <v>-0.2789</v>
       </c>
       <c r="J288" t="n">
-        <v>-7.3605</v>
+        <v>-5.8569</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3827</v>
+        <v>-0.2984</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.0367</v>
+        <v>-6.2664</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.6</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.549</v>
+        <v>-0.3796</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.529</v>
+        <v>-7.9716</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.32</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.9241</v>
+        <v>-0.6431</v>
       </c>
       <c r="J291" t="n">
-        <v>-19.4061</v>
+        <v>-13.5051</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.26</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4458</v>
+        <v>0.4026</v>
       </c>
       <c r="J292" t="n">
-        <v>16.0488</v>
+        <v>14.4936</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.24</v>
       </c>
       <c r="I293" t="n">
-        <v>0.4183</v>
+        <v>0.3759</v>
       </c>
       <c r="J293" t="n">
-        <v>15.0588</v>
+        <v>13.5324</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1165</v>
+        <v>-0.0563</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.194</v>
+        <v>-2.0268</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1943</v>
+        <v>-0.1069</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.9948</v>
+        <v>-3.8484</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.92</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2119</v>
+        <v>-0.1186</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.6284</v>
+        <v>-4.2696</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8505</v>
+        <v>0.7659</v>
       </c>
       <c r="J297" t="n">
-        <v>30.618</v>
+        <v>27.5724</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.09</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1752</v>
+        <v>0.1503</v>
       </c>
       <c r="J298" t="n">
-        <v>6.3072</v>
+        <v>5.4108</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0442</v>
+        <v>0.0577</v>
       </c>
       <c r="J299" t="n">
-        <v>1.5912</v>
+        <v>2.0772</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1799</v>
+        <v>-0.0963</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.4764</v>
+        <v>-3.4668</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.73</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4944</v>
+        <v>-0.3161</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.7984</v>
+        <v>-11.3796</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.33</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8996</v>
+        <v>0.8861</v>
       </c>
       <c r="J302" t="n">
-        <v>26.0884</v>
+        <v>25.6969</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8545</v>
+        <v>0.8393</v>
       </c>
       <c r="J303" t="n">
-        <v>24.7805</v>
+        <v>24.3397</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8084</v>
+        <v>0.7921</v>
       </c>
       <c r="J304" t="n">
-        <v>23.4436</v>
+        <v>22.9709</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.07</v>
       </c>
       <c r="I305" t="n">
-        <v>0.1831</v>
+        <v>0.2316</v>
       </c>
       <c r="J305" t="n">
-        <v>5.3099</v>
+        <v>6.7164</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.0478</v>
+        <v>-1.0289</v>
       </c>
       <c r="J306" t="n">
-        <v>-30.3862</v>
+        <v>-29.8381</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.41</v>
       </c>
       <c r="I307" t="n">
-        <v>0.65</v>
+        <v>0.7942</v>
       </c>
       <c r="J307" t="n">
-        <v>18.85</v>
+        <v>23.0318</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3459</v>
+        <v>0.3946</v>
       </c>
       <c r="J308" t="n">
-        <v>10.0311</v>
+        <v>11.4434</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1026</v>
+        <v>-0.0523</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.9754</v>
+        <v>-1.5167</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2005</v>
+        <v>-0.1142</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.8145</v>
+        <v>-3.3118</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.64</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.395</v>
       </c>
       <c r="J311" t="n">
-        <v>-17.4087</v>
+        <v>-11.455</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.85</v>
       </c>
       <c r="I312" t="n">
-        <v>1.7659</v>
+        <v>1.509</v>
       </c>
       <c r="J312" t="n">
-        <v>37.0839</v>
+        <v>31.689</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.56</v>
       </c>
       <c r="I313" t="n">
-        <v>1.23</v>
+        <v>1.1713</v>
       </c>
       <c r="J313" t="n">
-        <v>25.83</v>
+        <v>24.5973</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.49</v>
       </c>
       <c r="I314" t="n">
-        <v>1.0844</v>
+        <v>1.088</v>
       </c>
       <c r="J314" t="n">
-        <v>22.7724</v>
+        <v>22.848</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.17</v>
       </c>
       <c r="I315" t="n">
-        <v>0.3332</v>
+        <v>0.4374</v>
       </c>
       <c r="J315" t="n">
-        <v>6.9972</v>
+        <v>9.1854</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.1</v>
       </c>
       <c r="I316" t="n">
-        <v>0.1542</v>
+        <v>0.2494</v>
       </c>
       <c r="J316" t="n">
-        <v>3.2382</v>
+        <v>5.2374</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>0.96</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0039</v>
+        <v>-0.0344</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.0819</v>
+        <v>-0.7224</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.89</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1341</v>
+        <v>-0.1208</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.8161</v>
+        <v>-2.5368</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.75</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3888</v>
+        <v>-0.2616</v>
       </c>
       <c r="J319" t="n">
-        <v>-8.1648</v>
+        <v>-5.4936</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4806</v>
+        <v>-0.3186</v>
       </c>
       <c r="J320" t="n">
-        <v>-10.0926</v>
+        <v>-6.6906</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.66</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5234</v>
+        <v>-0.3469</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.9914</v>
+        <v>-7.2849</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>2.11</v>
       </c>
       <c r="I322" t="n">
-        <v>2.0593</v>
+        <v>1.8023</v>
       </c>
       <c r="J322" t="n">
-        <v>43.2453</v>
+        <v>37.8483</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>1.4807</v>
+        <v>1.3247</v>
       </c>
       <c r="J323" t="n">
-        <v>31.0947</v>
+        <v>27.8187</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.29</v>
       </c>
       <c r="I324" t="n">
-        <v>0.6139</v>
+        <v>0.7269</v>
       </c>
       <c r="J324" t="n">
-        <v>12.8919</v>
+        <v>15.2649</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.1274</v>
+        <v>0.2212</v>
       </c>
       <c r="J325" t="n">
-        <v>2.6754</v>
+        <v>4.6452</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.98</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2868</v>
+        <v>-0.1974</v>
       </c>
       <c r="J326" t="n">
-        <v>-6.0228</v>
+        <v>-4.1454</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.78</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.2726</v>
+        <v>-0.2212</v>
       </c>
       <c r="J327" t="n">
-        <v>-5.7246</v>
+        <v>-4.6452</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.77</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2888</v>
+        <v>-0.2313</v>
       </c>
       <c r="J328" t="n">
-        <v>-6.0648</v>
+        <v>-4.8573</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.75</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.3214</v>
+        <v>-0.2512</v>
       </c>
       <c r="J329" t="n">
-        <v>-6.7494</v>
+        <v>-5.2752</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.61</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.5626</v>
+        <v>-0.3802</v>
       </c>
       <c r="J330" t="n">
-        <v>-11.8146</v>
+        <v>-7.9842</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.6</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.577</v>
+        <v>-0.3895</v>
       </c>
       <c r="J331" t="n">
-        <v>-12.117</v>
+        <v>-8.179500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2187/event_2187_evp_summary.xlsx
+++ b/database/event/2187/event_2187_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.012</v>
+        <v>7.1978</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3041</v>
+        <v>1.3387</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5276</v>
+        <v>2.6524</v>
       </c>
       <c r="E2" t="n">
-        <v>7.012</v>
+        <v>7.1978</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4058</v>
+        <v>3.2865</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6062</v>
+        <v>3.9112</v>
       </c>
       <c r="H2" t="n">
-        <v>6.5137</v>
+        <v>5.9494</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3868</v>
+        <v>3.2126</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6062</v>
+        <v>3.9112</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>127</v>
       </c>
       <c r="M2" t="n">
-        <v>6.993</v>
+        <v>7.1238</v>
       </c>
       <c r="N2" t="n">
         <v>268</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1951</v>
+        <v>5.27</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9801</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7073</v>
+        <v>1.7748</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1951</v>
+        <v>5.27</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3329</v>
+        <v>3.287</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8622</v>
+        <v>1.983</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2567</v>
+        <v>5.9508</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2532</v>
+        <v>3.2134</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8622</v>
+        <v>1.983</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1154</v>
+        <v>5.196400000000001</v>
       </c>
       <c r="N3" t="n">
         <v>223</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.077</v>
+        <v>5.216</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9442</v>
+        <v>0.9701</v>
       </c>
       <c r="D4" t="n">
-        <v>1.654</v>
+        <v>1.7502</v>
       </c>
       <c r="E4" t="n">
-        <v>5.077</v>
+        <v>5.216</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4487</v>
+        <v>3.3979</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6283</v>
+        <v>1.8181</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6648</v>
+        <v>6.3168</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4654</v>
+        <v>3.411</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6283</v>
+        <v>1.8181</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0937</v>
+        <v>5.2291</v>
       </c>
       <c r="N4" t="n">
         <v>213</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0399</v>
+        <v>5.031</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9373</v>
+        <v>0.9357</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6372</v>
+        <v>1.666</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0399</v>
+        <v>5.031</v>
       </c>
       <c r="F5" t="n">
-        <v>3.042</v>
+        <v>2.9631</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9979</v>
+        <v>2.0679</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2318</v>
+        <v>4.8821</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7203</v>
+        <v>2.6363</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9979</v>
+        <v>2.0679</v>
       </c>
       <c r="K5" t="n">
         <v>274</v>
@@ -667,7 +667,7 @@
         <v>130</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7182</v>
+        <v>4.7042</v>
       </c>
       <c r="N5" t="n">
         <v>404</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8915</v>
+        <v>4.9669</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9097</v>
+        <v>0.9238</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5703</v>
+        <v>1.6368</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8915</v>
+        <v>4.9669</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1377</v>
+        <v>2.6059</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7538</v>
+        <v>2.361</v>
       </c>
       <c r="H6" t="n">
-        <v>5.569</v>
+        <v>3.7036</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8956</v>
+        <v>1.9999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7538</v>
+        <v>2.361</v>
       </c>
       <c r="K6" t="n">
-        <v>274</v>
+        <v>196</v>
       </c>
       <c r="L6" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6494</v>
+        <v>4.3609</v>
       </c>
       <c r="N6" t="n">
-        <v>404</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8912</v>
+        <v>4.9469</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9097</v>
+        <v>0.92</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5701</v>
+        <v>1.6277</v>
       </c>
       <c r="E7" t="n">
-        <v>4.8912</v>
+        <v>4.9469</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7484</v>
+        <v>3.0728</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1428</v>
+        <v>1.8741</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1973</v>
+        <v>5.244</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1824</v>
+        <v>2.8317</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1428</v>
+        <v>1.8741</v>
       </c>
       <c r="K7" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="L7" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3252</v>
+        <v>4.7058</v>
       </c>
       <c r="N7" t="n">
-        <v>234</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.651</v>
+        <v>4.6574</v>
       </c>
       <c r="C8" t="n">
-        <v>0.865</v>
+        <v>0.8662</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4617</v>
+        <v>1.4959</v>
       </c>
       <c r="E8" t="n">
-        <v>4.651</v>
+        <v>4.6574</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6743</v>
+        <v>3.6121</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9767</v>
+        <v>1.0453</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4595</v>
+        <v>7.0234</v>
       </c>
       <c r="I8" t="n">
-        <v>3.8786</v>
+        <v>3.7926</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9767</v>
+        <v>1.0453</v>
       </c>
       <c r="K8" t="n">
         <v>274</v>
@@ -805,7 +805,7 @@
         <v>130</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8553</v>
+        <v>4.8379</v>
       </c>
       <c r="N8" t="n">
         <v>404</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5532</v>
+        <v>4.5673</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8468</v>
+        <v>0.8494</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4175</v>
+        <v>1.4549</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5532</v>
+        <v>4.5673</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7453</v>
+        <v>2.6972</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8079</v>
+        <v>1.8701</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1865</v>
+        <v>4.0049</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1768</v>
+        <v>2.1626</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8079</v>
+        <v>1.8701</v>
       </c>
       <c r="K9" t="n">
         <v>141</v>
@@ -851,7 +851,7 @@
         <v>127</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9847</v>
+        <v>4.0327</v>
       </c>
       <c r="N9" t="n">
         <v>268</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.2713</v>
+        <v>4.1923</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7944</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2903</v>
+        <v>1.2842</v>
       </c>
       <c r="E10" t="n">
-        <v>4.2713</v>
+        <v>4.1923</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1383</v>
+        <v>3.0628</v>
       </c>
       <c r="G10" t="n">
-        <v>1.133</v>
+        <v>1.1295</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5711</v>
+        <v>5.2112</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8967</v>
+        <v>2.814</v>
       </c>
       <c r="J10" t="n">
-        <v>1.133</v>
+        <v>1.1295</v>
       </c>
       <c r="K10" t="n">
         <v>141</v>
@@ -897,7 +897,7 @@
         <v>127</v>
       </c>
       <c r="M10" t="n">
-        <v>4.0297</v>
+        <v>3.9435</v>
       </c>
       <c r="N10" t="n">
         <v>268</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7926</v>
+        <v>3.8732</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7054</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0742</v>
+        <v>1.139</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7926</v>
+        <v>3.8732</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2989</v>
+        <v>2.2247</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4937</v>
+        <v>1.6484</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6135</v>
+        <v>2.446</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3589</v>
+        <v>1.3208</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4937</v>
+        <v>1.6484</v>
       </c>
       <c r="K11" t="n">
         <v>106</v>
@@ -943,7 +943,7 @@
         <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8526</v>
+        <v>2.9692</v>
       </c>
       <c r="N11" t="n">
         <v>223</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5871</v>
+        <v>3.5977</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6671</v>
+        <v>0.6691</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9814000000000001</v>
+        <v>1.0135</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5871</v>
+        <v>3.5977</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1348</v>
+        <v>3.0913</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4523</v>
+        <v>0.5064</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5588</v>
+        <v>5.3053</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8903</v>
+        <v>2.8648</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4523</v>
+        <v>0.5064</v>
       </c>
       <c r="K12" t="n">
         <v>42</v>
@@ -989,7 +989,7 @@
         <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3426</v>
+        <v>3.3712</v>
       </c>
       <c r="N12" t="n">
         <v>145</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2725</v>
+        <v>3.339</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6086</v>
+        <v>0.621</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8394</v>
+        <v>0.8958</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2725</v>
+        <v>3.339</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7735</v>
+        <v>3.0051</v>
       </c>
       <c r="G13" t="n">
-        <v>0.499</v>
+        <v>0.3339</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2858</v>
+        <v>5.0206</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2284</v>
+        <v>2.7111</v>
       </c>
       <c r="J13" t="n">
-        <v>0.499</v>
+        <v>0.3339</v>
       </c>
       <c r="K13" t="n">
-        <v>274</v>
+        <v>141</v>
       </c>
       <c r="L13" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7274</v>
+        <v>3.045</v>
       </c>
       <c r="N13" t="n">
-        <v>404</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2576</v>
+        <v>3.2141</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6059</v>
+        <v>0.5978</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8326</v>
+        <v>0.8389</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2576</v>
+        <v>3.2141</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0691</v>
+        <v>2.701</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1885</v>
+        <v>0.5131</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3272</v>
+        <v>4.0173</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7699</v>
+        <v>2.1693</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1885</v>
+        <v>0.5131</v>
       </c>
       <c r="K14" t="n">
-        <v>141</v>
+        <v>274</v>
       </c>
       <c r="L14" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9584</v>
+        <v>2.6824</v>
       </c>
       <c r="N14" t="n">
-        <v>268</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0411</v>
+        <v>3.0224</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5656</v>
+        <v>0.5621</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7349</v>
+        <v>0.7517</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0411</v>
+        <v>3.0224</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1039</v>
+        <v>3.0625</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0401</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4499</v>
+        <v>5.2101</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8337</v>
+        <v>2.8134</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0401</v>
       </c>
       <c r="K15" t="n">
         <v>42</v>
@@ -1127,7 +1127,7 @@
         <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7709</v>
+        <v>2.7733</v>
       </c>
       <c r="N15" t="n">
         <v>145</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.6884</v>
+        <v>2.7402</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5757</v>
+        <v>0.6232</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6884</v>
+        <v>2.7402</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6435</v>
+        <v>2.5985</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0449</v>
+        <v>0.1417</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8276</v>
+        <v>3.6793</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9902</v>
+        <v>1.9868</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0449</v>
+        <v>0.1417</v>
       </c>
       <c r="K16" t="n">
         <v>106</v>
@@ -1173,7 +1173,7 @@
         <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0351</v>
+        <v>2.1285</v>
       </c>
       <c r="N16" t="n">
         <v>223</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6145</v>
+        <v>2.5397</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4863</v>
+        <v>0.4723</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5423</v>
+        <v>0.5319</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6145</v>
+        <v>2.5397</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9771</v>
+        <v>0.4226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6374</v>
+        <v>2.1171</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9771</v>
+        <v>0.4226</v>
       </c>
       <c r="I17" t="n">
-        <v>1.028</v>
+        <v>0.2282</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6374</v>
+        <v>2.1171</v>
       </c>
       <c r="K17" t="n">
-        <v>274</v>
+        <v>196</v>
       </c>
       <c r="L17" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6654</v>
+        <v>2.3453</v>
       </c>
       <c r="N17" t="n">
-        <v>404</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.3518</v>
+        <v>2.4775</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4374</v>
+        <v>0.4608</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4237</v>
+        <v>0.5036</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3518</v>
+        <v>2.4775</v>
       </c>
       <c r="F18" t="n">
-        <v>0.442</v>
+        <v>1.7752</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9099</v>
+        <v>0.7023</v>
       </c>
       <c r="H18" t="n">
-        <v>0.442</v>
+        <v>1.7752</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2298</v>
+        <v>0.9586</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9099</v>
+        <v>0.7023</v>
       </c>
       <c r="K18" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="L18" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1397</v>
+        <v>1.6609</v>
       </c>
       <c r="N18" t="n">
-        <v>234</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.9721</v>
+        <v>1.8952</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3668</v>
+        <v>0.3525</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2523</v>
+        <v>0.2385</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9721</v>
+        <v>1.8952</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2953</v>
+        <v>2.2363</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3232</v>
+        <v>-0.3411</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6008</v>
+        <v>2.4843</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3523</v>
+        <v>1.3415</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3232</v>
+        <v>-0.3411</v>
       </c>
       <c r="K19" t="n">
         <v>134</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0291</v>
+        <v>1.0004</v>
       </c>
       <c r="N19" t="n">
         <v>213</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8015</v>
+        <v>1.7071</v>
       </c>
       <c r="C20" t="n">
-        <v>0.335</v>
+        <v>0.3175</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1753</v>
+        <v>0.1529</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8015</v>
+        <v>1.7071</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8731</v>
+        <v>1.8022</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0716</v>
+        <v>-0.0951</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8731</v>
+        <v>1.8022</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9739</v>
+        <v>0.9732</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0716</v>
+        <v>-0.0951</v>
       </c>
       <c r="K20" t="n">
         <v>42</v>
@@ -1357,7 +1357,7 @@
         <v>103</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9023</v>
+        <v>0.8781</v>
       </c>
       <c r="N20" t="n">
         <v>145</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.7871</v>
+        <v>1.6694</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3324</v>
+        <v>0.3105</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1688</v>
+        <v>0.1357</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7871</v>
+        <v>1.6694</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7263</v>
+        <v>1.6043</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0608</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7263</v>
+        <v>1.6043</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8976</v>
+        <v>0.8663</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0608</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>134</v>
@@ -1403,7 +1403,7 @@
         <v>79</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9583999999999999</v>
+        <v>0.9314</v>
       </c>
       <c r="N21" t="n">
         <v>213</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.6412</v>
+        <v>1.5486</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3052</v>
+        <v>0.288</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1029</v>
+        <v>0.0808</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6412</v>
+        <v>1.5486</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6412</v>
+        <v>1.5486</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6412</v>
+        <v>1.5486</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6412</v>
+        <v>1.5486</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6412</v>
+        <v>1.5486</v>
       </c>
       <c r="N22" t="n">
         <v>123</v>
@@ -1458,35 +1458,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>innocent</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3983</v>
+        <v>1.4002</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2601</v>
+        <v>0.2604</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0068</v>
+        <v>0.0132</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3983</v>
+        <v>1.4002</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8718</v>
+        <v>-0.6039</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5265</v>
+        <v>2.0041</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8718</v>
+        <v>-0.6039</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4533</v>
+        <v>-0.3261</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5265</v>
+        <v>2.0041</v>
       </c>
       <c r="K23" t="n">
         <v>196</v>
@@ -1495,7 +1495,7 @@
         <v>38</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9798</v>
+        <v>1.678</v>
       </c>
       <c r="N23" t="n">
         <v>234</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>innocent</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2766</v>
+        <v>1.1786</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2374</v>
+        <v>0.2192</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0617</v>
+        <v>-0.0877</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2766</v>
+        <v>1.1786</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5243</v>
+        <v>0.5522</v>
       </c>
       <c r="G24" t="n">
-        <v>1.8009</v>
+        <v>0.6264</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5243</v>
+        <v>0.5522</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2726</v>
+        <v>0.2982</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8009</v>
+        <v>0.6264</v>
       </c>
       <c r="K24" t="n">
         <v>196</v>
@@ -1541,7 +1541,7 @@
         <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.5283</v>
+        <v>0.9246</v>
       </c>
       <c r="N24" t="n">
         <v>234</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.1995</v>
+        <v>1.082</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2231</v>
+        <v>0.2012</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0965</v>
+        <v>-0.1317</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1995</v>
+        <v>1.082</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1927</v>
+        <v>2.1252</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9932</v>
+        <v>-1.0432</v>
       </c>
       <c r="H25" t="n">
-        <v>2.2392</v>
+        <v>2.1252</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1643</v>
+        <v>1.1476</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9932</v>
+        <v>-1.0432</v>
       </c>
       <c r="K25" t="n">
         <v>42</v>
@@ -1587,7 +1587,7 @@
         <v>103</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1710999999999999</v>
+        <v>0.1044</v>
       </c>
       <c r="N25" t="n">
         <v>145</v>
@@ -1596,231 +1596,231 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5274</v>
+        <v>0.4984</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0927</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3999</v>
+        <v>-0.3973</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5274</v>
+        <v>0.4984</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5274</v>
+        <v>-1.0682</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.5666</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5274</v>
+        <v>-1.0682</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5274</v>
+        <v>-0.5768</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.5666</v>
       </c>
       <c r="K26" t="n">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5274</v>
+        <v>0.9898</v>
       </c>
       <c r="N26" t="n">
-        <v>90</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AiyvaN</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4877</v>
+        <v>0.4421</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0907</v>
+        <v>0.0822</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4178</v>
+        <v>-0.423</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4877</v>
+        <v>0.4421</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0526</v>
+        <v>0.4421</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5649</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0526</v>
+        <v>0.4421</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5473</v>
+        <v>0.4421</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5649</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="L27" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.01759999999999995</v>
+        <v>0.4421</v>
       </c>
       <c r="N27" t="n">
-        <v>213</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>AiyvaN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4063</v>
+        <v>0.4079</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0756</v>
+        <v>0.0759</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4546</v>
+        <v>-0.4385</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4063</v>
+        <v>0.4079</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.012</v>
+        <v>0.9756</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4183</v>
+        <v>-0.5677</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.012</v>
+        <v>0.9756</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5262</v>
+        <v>0.5268</v>
       </c>
       <c r="J28" t="n">
-        <v>1.4183</v>
+        <v>-0.5677</v>
       </c>
       <c r="K28" t="n">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="L28" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8920999999999999</v>
+        <v>-0.04089999999999994</v>
       </c>
       <c r="N28" t="n">
-        <v>234</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0751</v>
+        <v>0.0629</v>
       </c>
       <c r="C29" t="n">
-        <v>0.014</v>
+        <v>0.0117</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6041</v>
+        <v>-0.5956</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0751</v>
+        <v>0.0629</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0751</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.9003</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0751</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0751</v>
+        <v>0.5201</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.9003</v>
       </c>
       <c r="K29" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0751</v>
+        <v>-0.3802</v>
       </c>
       <c r="N29" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0402</v>
+        <v>0.0292</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0075</v>
+        <v>0.0054</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6199</v>
+        <v>-0.6109</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0402</v>
+        <v>0.0292</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9051</v>
+        <v>0.0292</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8649</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9051</v>
+        <v>0.0292</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4706</v>
+        <v>0.0292</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8649</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="L30" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3943</v>
+        <v>0.0292</v>
       </c>
       <c r="N30" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1158</v>
+        <v>0.0104</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0215</v>
+        <v>0.0019</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6903</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1158</v>
+        <v>0.0104</v>
       </c>
       <c r="F31" t="n">
-        <v>0.931</v>
+        <v>0.8798</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.0468</v>
+        <v>-0.8694</v>
       </c>
       <c r="H31" t="n">
-        <v>0.931</v>
+        <v>0.8798</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4841</v>
+        <v>0.4751</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.0468</v>
+        <v>-0.8694</v>
       </c>
       <c r="K31" t="n">
         <v>106</v>
@@ -1863,7 +1863,7 @@
         <v>117</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5627</v>
+        <v>-0.3942999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>223</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1253</v>
+        <v>-0.1808</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0233</v>
+        <v>-0.0336</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6946</v>
+        <v>-0.7065</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1253</v>
+        <v>-0.1808</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3498</v>
+        <v>0.3185</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4751</v>
+        <v>-0.4993</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3498</v>
+        <v>0.3185</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1819</v>
+        <v>0.172</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4751</v>
+        <v>-0.4993</v>
       </c>
       <c r="K32" t="n">
         <v>134</v>
@@ -1909,7 +1909,7 @@
         <v>79</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2932</v>
+        <v>-0.3273</v>
       </c>
       <c r="N32" t="n">
         <v>213</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.2773</v>
+        <v>-0.3166</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0516</v>
+        <v>-0.0589</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7632</v>
+        <v>-0.7683</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.2773</v>
+        <v>-0.3166</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2773</v>
+        <v>-0.3166</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2773</v>
+        <v>-0.3166</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2773</v>
+        <v>-0.3166</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2773</v>
+        <v>-0.3166</v>
       </c>
       <c r="N33" t="n">
         <v>123</v>
@@ -1964,78 +1964,78 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>wayLander</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4917</v>
+        <v>-0.3249</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0914</v>
+        <v>-0.0604</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.86</v>
+        <v>-0.7721</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4917</v>
+        <v>-0.3249</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4917</v>
+        <v>-1.0795</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.7546</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4917</v>
+        <v>-1.0795</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4917</v>
+        <v>-0.5829</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.7546</v>
       </c>
       <c r="K34" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4917</v>
+        <v>0.1717000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>123</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>wayLander</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.517</v>
+        <v>-0.53</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8714</v>
+        <v>-0.8655</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.517</v>
+        <v>-0.53</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.517</v>
+        <v>-0.53</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.517</v>
+        <v>-0.53</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.517</v>
+        <v>-0.53</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.517</v>
+        <v>-0.53</v>
       </c>
       <c r="N35" t="n">
         <v>123</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6748</v>
+        <v>-0.544</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1255</v>
+        <v>-0.1012</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9427</v>
+        <v>-0.8718</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6748</v>
+        <v>-0.544</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3143</v>
+        <v>-0.544</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6395</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3143</v>
+        <v>-0.544</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6834</v>
+        <v>-0.544</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6395</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="L36" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.04390000000000005</v>
+        <v>-0.544</v>
       </c>
       <c r="N36" t="n">
-        <v>268</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.011</v>
+        <v>-1.0821</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.188</v>
+        <v>-0.2013</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0944</v>
+        <v>-1.1168</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.011</v>
+        <v>-1.0821</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.011</v>
+        <v>-1.0821</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.011</v>
+        <v>-1.0821</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.011</v>
+        <v>-1.0821</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.011</v>
+        <v>-1.0821</v>
       </c>
       <c r="N37" t="n">
         <v>90</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2516</v>
+        <v>-1.3186</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2328</v>
+        <v>-0.2452</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.203</v>
+        <v>-1.2245</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2516</v>
+        <v>-1.3186</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2516</v>
+        <v>-1.3186</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2516</v>
+        <v>-1.3186</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2516</v>
+        <v>-1.3186</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2516</v>
+        <v>-1.3186</v>
       </c>
       <c r="N38" t="n">
         <v>90</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2717</v>
+        <v>-1.3432</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2365</v>
+        <v>-0.2498</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2121</v>
+        <v>-1.2357</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2717</v>
+        <v>-1.3432</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2717</v>
+        <v>-1.3432</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2717</v>
+        <v>-1.3432</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2717</v>
+        <v>-1.3432</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2717</v>
+        <v>-1.3432</v>
       </c>
       <c r="N39" t="n">
         <v>90</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3934</v>
+        <v>-1.453</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2591</v>
+        <v>-0.2702</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2671</v>
+        <v>-1.2856</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3934</v>
+        <v>-1.453</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3934</v>
+        <v>-0.0709</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-1.3821</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3934</v>
+        <v>-0.0709</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3934</v>
+        <v>-0.0383</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-1.3821</v>
       </c>
       <c r="K40" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3934</v>
+        <v>-1.4204</v>
       </c>
       <c r="N40" t="n">
-        <v>90</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4268</v>
+        <v>-1.4583</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2654</v>
+        <v>-0.2712</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2821</v>
+        <v>-1.2881</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4268</v>
+        <v>-1.4583</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0238</v>
+        <v>-1.4583</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.403</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0238</v>
+        <v>-1.4583</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0124</v>
+        <v>-1.4583</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.403</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="L41" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4154</v>
+        <v>-1.4583</v>
       </c>
       <c r="N41" t="n">
-        <v>223</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8477</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>22.8879</v>
+        <v>21.4623</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4014</v>
+        <v>0.3971</v>
       </c>
       <c r="J3" t="n">
-        <v>10.8378</v>
+        <v>10.7217</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3221</v>
+        <v>0.3236</v>
       </c>
       <c r="J4" t="n">
-        <v>8.6967</v>
+        <v>8.7372</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1075</v>
+        <v>0.1201</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9025</v>
+        <v>3.2427</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1581</v>
+        <v>-0.1548</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.2687</v>
+        <v>-4.1796</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4657</v>
+        <v>0.4605</v>
       </c>
       <c r="J7" t="n">
-        <v>12.5739</v>
+        <v>12.4335</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3369</v>
+        <v>0.3403</v>
       </c>
       <c r="J8" t="n">
-        <v>9.096299999999999</v>
+        <v>9.1881</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2986</v>
+        <v>0.304</v>
       </c>
       <c r="J9" t="n">
-        <v>8.062200000000001</v>
+        <v>8.208</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0021</v>
+        <v>-0.0016</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0567</v>
+        <v>-0.0432</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3863</v>
+        <v>-0.3955</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.4301</v>
+        <v>-10.6785</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0725</v>
+        <v>-0.1015</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.74</v>
+        <v>-2.436</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.71</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2738</v>
+        <v>-0.2974</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.5712</v>
+        <v>-7.1376</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.54</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4313</v>
+        <v>-0.4479</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.3512</v>
+        <v>-10.7496</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.49</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4782</v>
+        <v>-0.4919</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.4768</v>
+        <v>-11.8056</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.47</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4971</v>
+        <v>-0.5095</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.9304</v>
+        <v>-12.228</v>
       </c>
     </row>
     <row r="17">
@@ -3069,10 +3069,10 @@
         <v>1.46</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5513</v>
+        <v>0.5626</v>
       </c>
       <c r="J18" t="n">
-        <v>13.2312</v>
+        <v>13.5024</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4473</v>
+        <v>0.4633</v>
       </c>
       <c r="J19" t="n">
-        <v>10.7352</v>
+        <v>11.1192</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3924</v>
+        <v>0.4106</v>
       </c>
       <c r="J20" t="n">
-        <v>9.4176</v>
+        <v>9.8544</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2501</v>
+        <v>0.2725</v>
       </c>
       <c r="J21" t="n">
-        <v>6.0024</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.78</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4745</v>
+        <v>1.5977</v>
       </c>
       <c r="J22" t="n">
-        <v>38.337</v>
+        <v>41.5402</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7587</v>
+        <v>0.7246</v>
       </c>
       <c r="J23" t="n">
-        <v>19.7262</v>
+        <v>18.8396</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4262</v>
+        <v>0.4261</v>
       </c>
       <c r="J24" t="n">
-        <v>11.0812</v>
+        <v>11.0786</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3463</v>
+        <v>0.3532</v>
       </c>
       <c r="J25" t="n">
-        <v>9.0038</v>
+        <v>9.183199999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3864</v>
+        <v>-0.3617</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.0464</v>
+        <v>-9.404199999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1886</v>
+        <v>0.1896</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9036</v>
+        <v>4.9296</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0543</v>
+        <v>-0.0658</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.4118</v>
+        <v>-1.7108</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.86</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1662</v>
+        <v>-0.1822</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.3212</v>
+        <v>-4.7372</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1868</v>
+        <v>-0.2029</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.8568</v>
+        <v>-5.2754</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2371</v>
+        <v>-0.253</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.1646</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.62</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2876</v>
+        <v>1.2612</v>
       </c>
       <c r="J32" t="n">
-        <v>32.19</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5812</v>
+        <v>0.5648</v>
       </c>
       <c r="J33" t="n">
-        <v>14.53</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.19</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5333</v>
+        <v>0.5216</v>
       </c>
       <c r="J34" t="n">
-        <v>13.3325</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.08</v>
       </c>
       <c r="I35" t="n">
-        <v>0.24</v>
+        <v>0.2533</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>6.3325</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0536</v>
+        <v>-0.0371</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.34</v>
+        <v>-0.9275</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5891</v>
+        <v>0.5613</v>
       </c>
       <c r="J37" t="n">
-        <v>14.7275</v>
+        <v>14.0325</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.87</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1528</v>
+        <v>-0.1694</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.82</v>
+        <v>-4.235</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.85</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1726</v>
+        <v>-0.1896</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.315</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.281</v>
+        <v>-0.2972</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.025</v>
+        <v>-7.43</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4042</v>
+        <v>-0.4159</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.105</v>
+        <v>-10.3975</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.631</v>
+        <v>0.604</v>
       </c>
       <c r="J42" t="n">
-        <v>17.668</v>
+        <v>16.912</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3754</v>
+        <v>0.3731</v>
       </c>
       <c r="J43" t="n">
-        <v>10.5112</v>
+        <v>10.4468</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.12</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3754</v>
+        <v>0.3731</v>
       </c>
       <c r="J44" t="n">
-        <v>10.5112</v>
+        <v>10.4468</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2663</v>
+        <v>0.2715</v>
       </c>
       <c r="J45" t="n">
-        <v>7.4564</v>
+        <v>7.602</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0793</v>
+        <v>-0.0765</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.2204</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.17</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4076</v>
+        <v>0.3999</v>
       </c>
       <c r="J47" t="n">
-        <v>11.4128</v>
+        <v>11.1972</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.98</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0298</v>
+        <v>-0.038</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.8344</v>
+        <v>-1.064</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.93</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0936</v>
+        <v>-0.1066</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.6208</v>
+        <v>-2.9848</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1481</v>
+        <v>-0.1631</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.1468</v>
+        <v>-4.5668</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3467</v>
+        <v>-0.3593</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.707599999999999</v>
+        <v>-10.0604</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1133</v>
+        <v>1.0718</v>
       </c>
       <c r="J52" t="n">
-        <v>30.0591</v>
+        <v>28.9386</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6161</v>
+        <v>0.5937</v>
       </c>
       <c r="J53" t="n">
-        <v>16.6347</v>
+        <v>16.0299</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.11</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3398</v>
+        <v>0.3425</v>
       </c>
       <c r="J54" t="n">
-        <v>9.1746</v>
+        <v>9.2475</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1297</v>
+        <v>0.1451</v>
       </c>
       <c r="J55" t="n">
-        <v>3.5019</v>
+        <v>3.9177</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2397</v>
+        <v>-0.2297</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.4719</v>
+        <v>-6.2019</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.48</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9568</v>
+        <v>0.8992</v>
       </c>
       <c r="J57" t="n">
-        <v>25.8336</v>
+        <v>24.2784</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0698</v>
+        <v>-0.0815</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.8846</v>
+        <v>-2.2005</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1372</v>
+        <v>-0.152</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.7044</v>
+        <v>-4.104</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3653</v>
+        <v>-0.3773</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.863099999999999</v>
+        <v>-10.1871</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3747</v>
+        <v>-0.3863</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.1169</v>
+        <v>-10.4301</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.777</v>
+        <v>0.7329</v>
       </c>
       <c r="J62" t="n">
-        <v>21.756</v>
+        <v>20.5212</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.24</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6802</v>
+        <v>0.6476</v>
       </c>
       <c r="J63" t="n">
-        <v>19.0456</v>
+        <v>18.1328</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.454</v>
+        <v>0.445</v>
       </c>
       <c r="J64" t="n">
-        <v>12.712</v>
+        <v>12.46</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0793</v>
+        <v>-0.0765</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.2204</v>
+        <v>-2.142</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.87</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.464</v>
+        <v>-0.4405</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.992</v>
+        <v>-12.334</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3143</v>
+        <v>0.3155</v>
       </c>
       <c r="J67" t="n">
-        <v>8.8004</v>
+        <v>8.834</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2944</v>
+        <v>0.2966</v>
       </c>
       <c r="J68" t="n">
-        <v>8.2432</v>
+        <v>8.3048</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1093</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.7216</v>
+        <v>-3.0604</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.153</v>
+        <v>-0.1668</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.284</v>
+        <v>-4.6704</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2357</v>
+        <v>-0.2498</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.5996</v>
+        <v>-6.9944</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4035</v>
+        <v>0.4007</v>
       </c>
       <c r="J72" t="n">
-        <v>11.298</v>
+        <v>11.2196</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3467</v>
+        <v>0.3475</v>
       </c>
       <c r="J73" t="n">
-        <v>9.707599999999999</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.185</v>
+        <v>0.1926</v>
       </c>
       <c r="J74" t="n">
-        <v>5.18</v>
+        <v>5.3928</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1873</v>
+        <v>-0.2009</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.2444</v>
+        <v>-5.6252</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3165</v>
+        <v>-0.3286</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.862</v>
+        <v>-9.200799999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7981</v>
+        <v>0.7561</v>
       </c>
       <c r="J77" t="n">
-        <v>22.3468</v>
+        <v>21.1708</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7516</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>21.0448</v>
+        <v>20.0256</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6813</v>
+        <v>0.653</v>
       </c>
       <c r="J79" t="n">
-        <v>19.0764</v>
+        <v>18.284</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.18</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5148</v>
+        <v>0.5036</v>
       </c>
       <c r="J80" t="n">
-        <v>14.4144</v>
+        <v>14.1008</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3702</v>
+        <v>-0.3503</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.3656</v>
+        <v>-9.808400000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5359</v>
+        <v>0.5188</v>
       </c>
       <c r="J82" t="n">
-        <v>16.077</v>
+        <v>15.564</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2647</v>
+        <v>0.2658</v>
       </c>
       <c r="J83" t="n">
-        <v>7.941</v>
+        <v>7.974</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.82</v>
+        <v>-3.207</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.91</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1164</v>
+        <v>-0.1303</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.492</v>
+        <v>-3.909</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5132</v>
+        <v>-0.5181</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.396</v>
+        <v>-15.543</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.6</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2844</v>
+        <v>1.2539</v>
       </c>
       <c r="J87" t="n">
-        <v>38.532</v>
+        <v>37.617</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9669</v>
+        <v>0.9056</v>
       </c>
       <c r="J88" t="n">
-        <v>29.007</v>
+        <v>27.168</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2279</v>
+        <v>0.2377</v>
       </c>
       <c r="J89" t="n">
-        <v>6.837</v>
+        <v>7.131</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1681</v>
+        <v>-0.1618</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.043</v>
+        <v>-4.854</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8633</v>
+        <v>-0.7935</v>
       </c>
       <c r="J91" t="n">
-        <v>-25.899</v>
+        <v>-23.805</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.71</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1156</v>
+        <v>1.2232</v>
       </c>
       <c r="J92" t="n">
-        <v>26.7744</v>
+        <v>29.3568</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5043</v>
+        <v>0.5605</v>
       </c>
       <c r="J93" t="n">
-        <v>12.1032</v>
+        <v>13.452</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.18</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4332</v>
+        <v>0.4803</v>
       </c>
       <c r="J94" t="n">
-        <v>10.3968</v>
+        <v>11.5272</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.15</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3881</v>
+        <v>0.4244</v>
       </c>
       <c r="J95" t="n">
-        <v>9.314399999999999</v>
+        <v>10.1856</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1164</v>
+        <v>-0.1024</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.7936</v>
+        <v>-2.4576</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6624</v>
+        <v>0.7304</v>
       </c>
       <c r="J97" t="n">
-        <v>15.8976</v>
+        <v>17.5296</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0877</v>
+        <v>-0.1021</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.1048</v>
+        <v>-2.4504</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.7</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3205</v>
+        <v>-0.3353</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.692</v>
+        <v>-8.0472</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.66</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3584</v>
+        <v>-0.3719</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.601599999999999</v>
+        <v>-8.925599999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3678</v>
+        <v>-0.381</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.827199999999999</v>
+        <v>-9.144</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4271</v>
+        <v>0.4667</v>
       </c>
       <c r="J102" t="n">
-        <v>12.3859</v>
+        <v>13.5343</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3641</v>
+        <v>0.3797</v>
       </c>
       <c r="J103" t="n">
-        <v>10.5589</v>
+        <v>11.0113</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.152</v>
+        <v>0.1604</v>
       </c>
       <c r="J104" t="n">
-        <v>4.408</v>
+        <v>4.6516</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0408</v>
+        <v>0.0502</v>
       </c>
       <c r="J105" t="n">
-        <v>1.1832</v>
+        <v>1.4558</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0683</v>
+        <v>-0.0689</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.9807</v>
+        <v>-1.9981</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.364</v>
+        <v>0.3831</v>
       </c>
       <c r="J107" t="n">
-        <v>10.556</v>
+        <v>11.1099</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1631</v>
+        <v>0.1711</v>
       </c>
       <c r="J108" t="n">
-        <v>4.7299</v>
+        <v>4.9619</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.04</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1172</v>
+        <v>0.1254</v>
       </c>
       <c r="J109" t="n">
-        <v>3.3988</v>
+        <v>3.6366</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.96</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.8183</v>
+        <v>-2.0909</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2973</v>
+        <v>-0.3099</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.621700000000001</v>
+        <v>-8.9871</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.5672</v>
       </c>
       <c r="J112" t="n">
-        <v>15.318</v>
+        <v>17.016</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.03</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0915</v>
+        <v>0.0997</v>
       </c>
       <c r="J113" t="n">
-        <v>2.745</v>
+        <v>2.991</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0375</v>
+        <v>0.0432</v>
       </c>
       <c r="J114" t="n">
-        <v>1.125</v>
+        <v>1.296</v>
       </c>
     </row>
     <row r="115">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3741</v>
+        <v>-0.3842</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.223</v>
+        <v>-11.526</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>1.032</v>
+        <v>1.1321</v>
       </c>
       <c r="J117" t="n">
-        <v>30.96</v>
+        <v>33.963</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9187</v>
+        <v>1.0116</v>
       </c>
       <c r="J118" t="n">
-        <v>27.561</v>
+        <v>30.348</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.481</v>
+        <v>0.533</v>
       </c>
       <c r="J119" t="n">
-        <v>14.43</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0486</v>
+        <v>-0.0336</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.458</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.1148</v>
+        <v>-1.0099</v>
       </c>
       <c r="J121" t="n">
-        <v>-33.444</v>
+        <v>-30.297</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.59</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5768</v>
+        <v>0.6577</v>
       </c>
       <c r="J122" t="n">
-        <v>15.5736</v>
+        <v>17.7579</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3047</v>
+        <v>0.3192</v>
       </c>
       <c r="J123" t="n">
-        <v>8.226900000000001</v>
+        <v>8.618399999999999</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2152</v>
+        <v>0.2312</v>
       </c>
       <c r="J124" t="n">
-        <v>5.8104</v>
+        <v>6.2424</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1345</v>
+        <v>-0.1443</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.6315</v>
+        <v>-3.8961</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.68</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.366</v>
+        <v>-0.3745</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.882</v>
+        <v>-10.1115</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.28</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3974</v>
+        <v>0.4371</v>
       </c>
       <c r="J127" t="n">
-        <v>10.7298</v>
+        <v>11.8017</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1544</v>
+        <v>0.1646</v>
       </c>
       <c r="J128" t="n">
-        <v>4.1688</v>
+        <v>4.4442</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.96</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0646</v>
+        <v>-0.0736</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.7442</v>
+        <v>-1.9872</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1468</v>
+        <v>-0.1594</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.9636</v>
+        <v>-4.3038</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1791</v>
+        <v>-0.1922</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.8357</v>
+        <v>-5.1894</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5409</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>11.8998</v>
+        <v>13.0504</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.109</v>
+        <v>-0.1247</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.398</v>
+        <v>-2.7434</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1919</v>
+        <v>-0.2093</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.2218</v>
+        <v>-4.6046</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.74</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2802</v>
+        <v>-0.2965</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.1644</v>
+        <v>-6.523</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.51</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4955</v>
+        <v>-0.5027</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.901</v>
+        <v>-11.0594</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0241</v>
+        <v>1.1296</v>
       </c>
       <c r="J137" t="n">
-        <v>22.5302</v>
+        <v>24.8512</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8289</v>
+        <v>0.9204</v>
       </c>
       <c r="J138" t="n">
-        <v>18.2358</v>
+        <v>20.2488</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.42</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7417</v>
+        <v>0.8257</v>
       </c>
       <c r="J139" t="n">
-        <v>16.3174</v>
+        <v>18.1654</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.1</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2726</v>
+        <v>0.2895</v>
       </c>
       <c r="J140" t="n">
-        <v>5.9972</v>
+        <v>6.369</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.98</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1753</v>
+        <v>-0.1563</v>
       </c>
       <c r="J141" t="n">
-        <v>-3.8566</v>
+        <v>-3.4386</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.0418</v>
+        <v>-0.0843</v>
       </c>
       <c r="J142" t="n">
-        <v>-0.7106</v>
+        <v>-1.4331</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.57</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.3783</v>
+        <v>-0.4023</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.4311</v>
+        <v>-6.8391</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.45</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4895</v>
+        <v>-0.5064</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.3215</v>
+        <v>-8.6088</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.33</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6065</v>
+        <v>-0.6138</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.3105</v>
+        <v>-10.4346</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.25</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6874</v>
+        <v>-0.6872</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6858</v>
+        <v>-11.6824</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.71</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0536</v>
+        <v>1.1686</v>
       </c>
       <c r="J147" t="n">
-        <v>17.9112</v>
+        <v>19.8662</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.64</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9745</v>
+        <v>1.0838</v>
       </c>
       <c r="J148" t="n">
-        <v>16.5665</v>
+        <v>18.4246</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.64</v>
       </c>
       <c r="I149" t="n">
-        <v>0.9745</v>
+        <v>1.0838</v>
       </c>
       <c r="J149" t="n">
-        <v>16.5665</v>
+        <v>18.4246</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.58</v>
       </c>
       <c r="I150" t="n">
-        <v>0.9067</v>
+        <v>1.0107</v>
       </c>
       <c r="J150" t="n">
-        <v>15.4139</v>
+        <v>17.1819</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.25</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4952</v>
+        <v>0.5595</v>
       </c>
       <c r="J151" t="n">
-        <v>8.4184</v>
+        <v>9.5115</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.03</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1967</v>
+        <v>0.1768</v>
       </c>
       <c r="J152" t="n">
-        <v>4.1307</v>
+        <v>3.7128</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.97</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0025</v>
+        <v>-0.0212</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.0525</v>
+        <v>-0.4452</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1407</v>
+        <v>-0.1626</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.9547</v>
+        <v>-3.4146</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3931</v>
+        <v>-0.4088</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.255100000000001</v>
+        <v>-8.5848</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.16</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8005</v>
+        <v>-0.7869</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.8105</v>
+        <v>-16.5249</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.83</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2128</v>
+        <v>1.3332</v>
       </c>
       <c r="J157" t="n">
-        <v>25.4688</v>
+        <v>27.9972</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.65</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0041</v>
+        <v>1.112</v>
       </c>
       <c r="J158" t="n">
-        <v>21.0861</v>
+        <v>23.352</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8264</v>
+        <v>0.9208</v>
       </c>
       <c r="J159" t="n">
-        <v>17.3544</v>
+        <v>19.3368</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3647</v>
+        <v>0.398</v>
       </c>
       <c r="J160" t="n">
-        <v>7.6587</v>
+        <v>8.358000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0313</v>
+        <v>0.0669</v>
       </c>
       <c r="J161" t="n">
-        <v>0.6573</v>
+        <v>1.4049</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.91</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.0956</v>
+        <v>-0.1143</v>
       </c>
       <c r="J162" t="n">
-        <v>-2.1032</v>
+        <v>-2.5146</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.9</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1074</v>
+        <v>-0.1263</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.3628</v>
+        <v>-2.7786</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.77</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2416</v>
+        <v>-0.2607</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.3152</v>
+        <v>-5.7354</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3171</v>
+        <v>-0.3345</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.9762</v>
+        <v>-7.359</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.63</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3737</v>
+        <v>-0.3888</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.221399999999999</v>
+        <v>-8.553599999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.99</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4044</v>
+        <v>1.5326</v>
       </c>
       <c r="J167" t="n">
-        <v>30.8968</v>
+        <v>33.7172</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0345</v>
+        <v>1.1431</v>
       </c>
       <c r="J168" t="n">
-        <v>22.759</v>
+        <v>25.1482</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.2</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4444</v>
+        <v>0.4976</v>
       </c>
       <c r="J169" t="n">
-        <v>9.7768</v>
+        <v>10.9472</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.258</v>
+        <v>0.2792</v>
       </c>
       <c r="J170" t="n">
-        <v>5.676</v>
+        <v>6.1424</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.01</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0388</v>
+        <v>-0.0053</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.8536</v>
+        <v>-0.1166</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6506</v>
+        <v>0.7194</v>
       </c>
       <c r="J172" t="n">
-        <v>18.2168</v>
+        <v>20.1432</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1405</v>
+        <v>0.1423</v>
       </c>
       <c r="J173" t="n">
-        <v>3.934</v>
+        <v>3.9844</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.257</v>
+        <v>-0.2726</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.196</v>
+        <v>-7.6328</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.73</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2959</v>
+        <v>-0.3107</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.2852</v>
+        <v>-8.6996</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4553</v>
+        <v>-0.4638</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.7484</v>
+        <v>-12.9864</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8869</v>
+        <v>0.9787</v>
       </c>
       <c r="J177" t="n">
-        <v>24.8332</v>
+        <v>27.4036</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7198</v>
+        <v>0.7983</v>
       </c>
       <c r="J178" t="n">
-        <v>20.1544</v>
+        <v>22.3524</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.25</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5332</v>
+        <v>0.5925</v>
       </c>
       <c r="J179" t="n">
-        <v>14.9296</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3761</v>
+        <v>0.4057</v>
       </c>
       <c r="J180" t="n">
-        <v>10.5308</v>
+        <v>11.3596</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.83</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6029</v>
+        <v>-0.5597</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.8812</v>
+        <v>-15.6716</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.96</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0293</v>
+        <v>1.0168</v>
       </c>
       <c r="J182" t="n">
-        <v>20.586</v>
+        <v>20.336</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.48</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>11.442</v>
+        <v>11.644</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.35</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4366</v>
+        <v>0.453</v>
       </c>
       <c r="J184" t="n">
-        <v>8.731999999999999</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1157</v>
+        <v>0.1389</v>
       </c>
       <c r="J185" t="n">
-        <v>2.314</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0859</v>
+        <v>0.1085</v>
       </c>
       <c r="J186" t="n">
-        <v>1.718</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.1141</v>
       </c>
       <c r="J187" t="n">
-        <v>-1.836</v>
+        <v>-2.282</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2134</v>
+        <v>-0.2348</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.268</v>
+        <v>-4.696</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.76</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2434</v>
+        <v>-0.2642</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.868</v>
+        <v>-5.284</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.6</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3915</v>
+        <v>-0.4076</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.83</v>
+        <v>-8.151999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4663</v>
+        <v>-0.4783</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.326000000000001</v>
+        <v>-9.566000000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5617</v>
+        <v>0.5474</v>
       </c>
       <c r="J192" t="n">
-        <v>16.851</v>
+        <v>16.422</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3992</v>
+        <v>0.3975</v>
       </c>
       <c r="J193" t="n">
-        <v>11.976</v>
+        <v>11.925</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.96</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.064</v>
+        <v>-0.0731</v>
       </c>
       <c r="J194" t="n">
-        <v>-1.92</v>
+        <v>-2.193</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.93</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1009</v>
+        <v>-0.1122</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.027</v>
+        <v>-3.366</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3371</v>
+        <v>-0.3484</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.113</v>
+        <v>-10.452</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.27</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7494</v>
+        <v>0.7093</v>
       </c>
       <c r="J197" t="n">
-        <v>22.482</v>
+        <v>21.279</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5783</v>
+        <v>0.5576</v>
       </c>
       <c r="J198" t="n">
-        <v>17.349</v>
+        <v>16.728</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.17</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5028</v>
+        <v>0.4898</v>
       </c>
       <c r="J199" t="n">
-        <v>15.084</v>
+        <v>14.694</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2044</v>
+        <v>0.2137</v>
       </c>
       <c r="J200" t="n">
-        <v>6.132</v>
+        <v>6.411</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4387</v>
+        <v>-0.417</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.161</v>
+        <v>-12.51</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.11</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3275</v>
+        <v>0.3165</v>
       </c>
       <c r="J202" t="n">
-        <v>8.1875</v>
+        <v>7.9125</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0292</v>
+        <v>-0.0422</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.73</v>
+        <v>-1.055</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1992</v>
+        <v>-0.2172</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.98</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.77</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2478</v>
+        <v>-0.2654</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.195</v>
+        <v>-6.635</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.49</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5107</v>
+        <v>-0.5174</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.7675</v>
+        <v>-12.935</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.58</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2269</v>
+        <v>1.1986</v>
       </c>
       <c r="J207" t="n">
-        <v>30.6725</v>
+        <v>29.965</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0637</v>
+        <v>1.0198</v>
       </c>
       <c r="J208" t="n">
-        <v>26.5925</v>
+        <v>25.495</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5733</v>
+        <v>0.5595</v>
       </c>
       <c r="J209" t="n">
-        <v>14.3325</v>
+        <v>13.9875</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.04</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1036</v>
+        <v>0.1269</v>
       </c>
       <c r="J210" t="n">
-        <v>2.59</v>
+        <v>3.1725</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1036</v>
+        <v>0.1269</v>
       </c>
       <c r="J211" t="n">
-        <v>2.59</v>
+        <v>3.1725</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4851</v>
+        <v>0.494</v>
       </c>
       <c r="J212" t="n">
-        <v>13.0977</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3209</v>
+        <v>0.3367</v>
       </c>
       <c r="J213" t="n">
-        <v>8.664300000000001</v>
+        <v>9.0909</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3209</v>
+        <v>0.3367</v>
       </c>
       <c r="J214" t="n">
-        <v>8.664300000000001</v>
+        <v>9.0909</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.3089</v>
+        <v>0.325</v>
       </c>
       <c r="J215" t="n">
-        <v>8.340299999999999</v>
+        <v>8.775</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2764</v>
+        <v>-0.2858</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.4628</v>
+        <v>-7.7166</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.3</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4854</v>
+        <v>0.4778</v>
       </c>
       <c r="J217" t="n">
-        <v>13.1058</v>
+        <v>12.9006</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.08</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1651</v>
+        <v>0.1725</v>
       </c>
       <c r="J218" t="n">
-        <v>4.4577</v>
+        <v>4.6575</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1296</v>
+        <v>-0.1434</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.4992</v>
+        <v>-3.8718</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1934</v>
+        <v>-0.2081</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.2218</v>
+        <v>-5.6187</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.67</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3597</v>
+        <v>-0.3713</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.7119</v>
+        <v>-10.0251</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.22</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5023</v>
+        <v>0.4874</v>
       </c>
       <c r="J222" t="n">
-        <v>12.5575</v>
+        <v>12.185</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.97</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.1025</v>
+        <v>-1.3425</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.1025</v>
+        <v>-1.3425</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2601</v>
+        <v>-0.275</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.5025</v>
+        <v>-6.875</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3182</v>
+        <v>-0.3317</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.955</v>
+        <v>-8.2925</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.32</v>
       </c>
       <c r="I227" t="n">
-        <v>0.843</v>
+        <v>0.7957</v>
       </c>
       <c r="J227" t="n">
-        <v>21.075</v>
+        <v>19.8925</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7145</v>
       </c>
       <c r="J228" t="n">
-        <v>18.7625</v>
+        <v>17.8625</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.27</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7272</v>
+        <v>0.6939</v>
       </c>
       <c r="J229" t="n">
-        <v>18.18</v>
+        <v>17.3475</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.15</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4395</v>
+        <v>0.4352</v>
       </c>
       <c r="J230" t="n">
-        <v>10.9875</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.92</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3414</v>
+        <v>-0.3234</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.535</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5413</v>
+        <v>0.5293</v>
       </c>
       <c r="J232" t="n">
-        <v>19.4868</v>
+        <v>19.0548</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.09</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2222</v>
+        <v>0.23</v>
       </c>
       <c r="J233" t="n">
-        <v>7.9992</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1585</v>
+        <v>0.1678</v>
       </c>
       <c r="J234" t="n">
-        <v>5.706</v>
+        <v>6.0408</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1471</v>
+        <v>-0.1596</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.2956</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2608</v>
+        <v>-0.2735</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.3888</v>
+        <v>-9.846</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.42</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0844</v>
+        <v>1.0313</v>
       </c>
       <c r="J237" t="n">
-        <v>39.0384</v>
+        <v>37.1268</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.27</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7837</v>
+        <v>0.7332</v>
       </c>
       <c r="J238" t="n">
-        <v>28.2132</v>
+        <v>26.3952</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.92</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2992</v>
+        <v>-0.2939</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.7712</v>
+        <v>-10.5804</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6307</v>
+        <v>-0.5941</v>
       </c>
       <c r="J240" t="n">
-        <v>-22.7052</v>
+        <v>-21.3876</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.7069</v>
       </c>
       <c r="J241" t="n">
-        <v>-27.3096</v>
+        <v>-25.4484</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0137</v>
+        <v>-0.0409</v>
       </c>
       <c r="J242" t="n">
-        <v>-0.2603</v>
+        <v>-0.7771</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1724</v>
+        <v>-0.1986</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.2756</v>
+        <v>-3.7734</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.59</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3878</v>
+        <v>-0.4063</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.3682</v>
+        <v>-7.7197</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.48</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.4906</v>
+        <v>-0.503</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.321400000000001</v>
+        <v>-9.557</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.36</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6042</v>
+        <v>-0.6083</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.4798</v>
+        <v>-11.5577</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.93</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5738</v>
+        <v>1.5766</v>
       </c>
       <c r="J247" t="n">
-        <v>29.9022</v>
+        <v>29.9554</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.75</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3732</v>
+        <v>1.3646</v>
       </c>
       <c r="J248" t="n">
-        <v>26.0908</v>
+        <v>25.9274</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.57</v>
       </c>
       <c r="I249" t="n">
-        <v>1.1696</v>
+        <v>1.1462</v>
       </c>
       <c r="J249" t="n">
-        <v>22.2224</v>
+        <v>21.7778</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.34</v>
       </c>
       <c r="I250" t="n">
-        <v>0.8146</v>
+        <v>0.7846</v>
       </c>
       <c r="J250" t="n">
-        <v>15.4774</v>
+        <v>14.9074</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.2</v>
       </c>
       <c r="I251" t="n">
-        <v>0.4878</v>
+        <v>0.495</v>
       </c>
       <c r="J251" t="n">
-        <v>9.2682</v>
+        <v>9.404999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.56</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0515</v>
+        <v>1.0048</v>
       </c>
       <c r="J252" t="n">
-        <v>30.4935</v>
+        <v>29.1392</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.9</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1274</v>
+        <v>-0.1416</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.6946</v>
+        <v>-4.1064</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.87</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1595</v>
+        <v>-0.1745</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.6255</v>
+        <v>-5.0605</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3382</v>
+        <v>-0.351</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.8078</v>
+        <v>-10.179</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.66</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3665</v>
+        <v>-0.3783</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.6285</v>
+        <v>-10.9707</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2686</v>
+        <v>1.2355</v>
       </c>
       <c r="J257" t="n">
-        <v>36.7894</v>
+        <v>35.8295</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3478</v>
+        <v>0.3479</v>
       </c>
       <c r="J258" t="n">
-        <v>10.0862</v>
+        <v>10.0891</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2348</v>
+        <v>0.2424</v>
       </c>
       <c r="J259" t="n">
-        <v>6.8092</v>
+        <v>7.0296</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.91</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3523</v>
+        <v>-0.3378</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.2167</v>
+        <v>-9.796200000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3523</v>
+        <v>-0.3378</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.2167</v>
+        <v>-9.796200000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4592</v>
+        <v>0.4379</v>
       </c>
       <c r="J262" t="n">
-        <v>11.0208</v>
+        <v>10.5096</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.87</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1475</v>
+        <v>-0.1653</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.54</v>
+        <v>-3.9672</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.79</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2267</v>
+        <v>-0.245</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.4408</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.74</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2748</v>
+        <v>-0.2924</v>
       </c>
       <c r="J265" t="n">
-        <v>-6.5952</v>
+        <v>-7.0176</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.52</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4814</v>
+        <v>-0.4901</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.5536</v>
+        <v>-11.7624</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.99</v>
       </c>
       <c r="I267" t="n">
-        <v>1.7106</v>
+        <v>1.7088</v>
       </c>
       <c r="J267" t="n">
-        <v>41.0544</v>
+        <v>41.0112</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.13</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3647</v>
+        <v>0.3719</v>
       </c>
       <c r="J268" t="n">
-        <v>8.752800000000001</v>
+        <v>8.925599999999999</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3647</v>
+        <v>0.3719</v>
       </c>
       <c r="J269" t="n">
-        <v>8.752800000000001</v>
+        <v>8.925599999999999</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2818</v>
+        <v>0.2959</v>
       </c>
       <c r="J270" t="n">
-        <v>6.7632</v>
+        <v>7.1016</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.09</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2532</v>
+        <v>0.2693</v>
       </c>
       <c r="J271" t="n">
-        <v>6.0768</v>
+        <v>6.4632</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.08</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3339</v>
+        <v>0.3073</v>
       </c>
       <c r="J272" t="n">
-        <v>8.0136</v>
+        <v>7.3752</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.7</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.2981</v>
+        <v>-0.318</v>
       </c>
       <c r="J273" t="n">
-        <v>-7.1544</v>
+        <v>-7.632</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.65</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3439</v>
+        <v>-0.3623</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.2536</v>
+        <v>-8.6952</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.64</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3532</v>
+        <v>-0.3712</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.476800000000001</v>
+        <v>-8.908799999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5121</v>
+        <v>-0.5212</v>
       </c>
       <c r="J276" t="n">
-        <v>-12.2904</v>
+        <v>-12.5088</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.76</v>
       </c>
       <c r="I277" t="n">
-        <v>1.421</v>
+        <v>1.4087</v>
       </c>
       <c r="J277" t="n">
-        <v>34.104</v>
+        <v>33.8088</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.56</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1826</v>
+        <v>1.1549</v>
       </c>
       <c r="J278" t="n">
-        <v>28.3824</v>
+        <v>27.7176</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.625</v>
+        <v>0.6097</v>
       </c>
       <c r="J279" t="n">
-        <v>15</v>
+        <v>14.6328</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.17</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4529</v>
+        <v>0.4555</v>
       </c>
       <c r="J280" t="n">
-        <v>10.8696</v>
+        <v>10.932</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.08</v>
       </c>
       <c r="I281" t="n">
-        <v>0.207</v>
+        <v>0.2303</v>
       </c>
       <c r="J281" t="n">
-        <v>4.968</v>
+        <v>5.5272</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.01</v>
       </c>
       <c r="I282" t="n">
-        <v>1.6742</v>
+        <v>1.6799</v>
       </c>
       <c r="J282" t="n">
-        <v>35.1582</v>
+        <v>35.2779</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.65</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2675</v>
+        <v>1.2502</v>
       </c>
       <c r="J283" t="n">
-        <v>26.6175</v>
+        <v>26.2542</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.34</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8258</v>
+        <v>0.7924</v>
       </c>
       <c r="J284" t="n">
-        <v>17.3418</v>
+        <v>16.6404</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.3</v>
       </c>
       <c r="I285" t="n">
-        <v>0.7361</v>
+        <v>0.7135</v>
       </c>
       <c r="J285" t="n">
-        <v>15.4581</v>
+        <v>14.9835</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.2</v>
       </c>
       <c r="I286" t="n">
-        <v>0.4992</v>
+        <v>0.503</v>
       </c>
       <c r="J286" t="n">
-        <v>10.4832</v>
+        <v>10.563</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.89</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.081</v>
+        <v>-0.1082</v>
       </c>
       <c r="J287" t="n">
-        <v>-1.701</v>
+        <v>-2.2722</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.71</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2789</v>
+        <v>-0.3014</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.8569</v>
+        <v>-6.3294</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2984</v>
+        <v>-0.3201</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.2664</v>
+        <v>-6.7221</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.6</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3796</v>
+        <v>-0.3984</v>
       </c>
       <c r="J290" t="n">
-        <v>-7.9716</v>
+        <v>-8.366400000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.32</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6431</v>
+        <v>-0.6439</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.5051</v>
+        <v>-13.5219</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.26</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4026</v>
+        <v>0.4059</v>
       </c>
       <c r="J292" t="n">
-        <v>14.4936</v>
+        <v>14.6124</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.24</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3759</v>
+        <v>0.3807</v>
       </c>
       <c r="J293" t="n">
-        <v>13.5324</v>
+        <v>13.7052</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.0563</v>
+        <v>-0.063</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.0268</v>
+        <v>-2.268</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1069</v>
+        <v>-0.1168</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.8484</v>
+        <v>-4.2048</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.92</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1186</v>
+        <v>-0.129</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.2696</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7659</v>
+        <v>0.7518</v>
       </c>
       <c r="J297" t="n">
-        <v>27.5724</v>
+        <v>27.0648</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.09</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1503</v>
+        <v>0.165</v>
       </c>
       <c r="J298" t="n">
-        <v>5.4108</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0577</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="J299" t="n">
-        <v>2.0772</v>
+        <v>2.4696</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0963</v>
+        <v>-0.1054</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.4668</v>
+        <v>-3.7944</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.73</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3161</v>
+        <v>-0.3265</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.3796</v>
+        <v>-11.754</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.33</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8861</v>
+        <v>0.8298</v>
       </c>
       <c r="J302" t="n">
-        <v>25.6969</v>
+        <v>24.0642</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.8393</v>
+        <v>0.789</v>
       </c>
       <c r="J303" t="n">
-        <v>24.3397</v>
+        <v>22.881</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7921</v>
+        <v>0.7477</v>
       </c>
       <c r="J304" t="n">
-        <v>22.9709</v>
+        <v>21.6833</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.07</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2316</v>
+        <v>0.2402</v>
       </c>
       <c r="J305" t="n">
-        <v>6.7164</v>
+        <v>6.9658</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-1.0289</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="J306" t="n">
-        <v>-29.8381</v>
+        <v>-27.202</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.41</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7942</v>
+        <v>0.7585</v>
       </c>
       <c r="J307" t="n">
-        <v>23.0318</v>
+        <v>21.9965</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3946</v>
+        <v>0.3941</v>
       </c>
       <c r="J308" t="n">
-        <v>11.4434</v>
+        <v>11.4289</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0523</v>
+        <v>-0.0599</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.5167</v>
+        <v>-1.7371</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1142</v>
+        <v>-0.1256</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.3118</v>
+        <v>-3.6424</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.64</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.395</v>
+        <v>-0.4039</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.455</v>
+        <v>-11.7131</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.85</v>
       </c>
       <c r="I312" t="n">
-        <v>1.509</v>
+        <v>1.5042</v>
       </c>
       <c r="J312" t="n">
-        <v>31.689</v>
+        <v>31.5882</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.56</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1713</v>
+        <v>1.1451</v>
       </c>
       <c r="J313" t="n">
-        <v>24.5973</v>
+        <v>24.0471</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.49</v>
       </c>
       <c r="I314" t="n">
-        <v>1.088</v>
+        <v>1.0541</v>
       </c>
       <c r="J314" t="n">
-        <v>22.848</v>
+        <v>22.1361</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.17</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4374</v>
+        <v>0.4447</v>
       </c>
       <c r="J315" t="n">
-        <v>9.1854</v>
+        <v>9.338699999999999</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.1</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2494</v>
+        <v>0.2732</v>
       </c>
       <c r="J316" t="n">
-        <v>5.2374</v>
+        <v>5.7372</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>0.96</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0344</v>
+        <v>-0.0502</v>
       </c>
       <c r="J317" t="n">
-        <v>-0.7224</v>
+        <v>-1.0542</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.89</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1208</v>
+        <v>-0.1395</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.5368</v>
+        <v>-2.9295</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.75</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2616</v>
+        <v>-0.2802</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.4936</v>
+        <v>-5.8842</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3186</v>
+        <v>-0.3356</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.6906</v>
+        <v>-7.0476</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.66</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3469</v>
+        <v>-0.3629</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.2849</v>
+        <v>-7.6209</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>2.11</v>
       </c>
       <c r="I322" t="n">
-        <v>1.8023</v>
+        <v>1.8107</v>
       </c>
       <c r="J322" t="n">
-        <v>37.8483</v>
+        <v>38.0247</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3247</v>
+        <v>1.3092</v>
       </c>
       <c r="J323" t="n">
-        <v>27.8187</v>
+        <v>27.4932</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.29</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7269</v>
+        <v>0.7029</v>
       </c>
       <c r="J324" t="n">
-        <v>15.2649</v>
+        <v>14.7609</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2212</v>
+        <v>0.2469</v>
       </c>
       <c r="J325" t="n">
-        <v>4.6452</v>
+        <v>5.1849</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.98</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1974</v>
+        <v>-0.1719</v>
       </c>
       <c r="J326" t="n">
-        <v>-4.1454</v>
+        <v>-3.6099</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.78</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.2212</v>
+        <v>-0.243</v>
       </c>
       <c r="J327" t="n">
-        <v>-4.6452</v>
+        <v>-5.103</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.77</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2313</v>
+        <v>-0.2529</v>
       </c>
       <c r="J328" t="n">
-        <v>-4.8573</v>
+        <v>-5.3109</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.75</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2512</v>
+        <v>-0.2722</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.2752</v>
+        <v>-5.7162</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.61</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3802</v>
+        <v>-0.3972</v>
       </c>
       <c r="J330" t="n">
-        <v>-7.9842</v>
+        <v>-8.341200000000001</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.6</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3895</v>
+        <v>-0.4061</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.179500000000001</v>
+        <v>-8.5281</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2187/event_2187_evp_summary.xlsx
+++ b/database/event/2187/event_2187_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1978</v>
+        <v>7.1766</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3387</v>
+        <v>1.3347</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6524</v>
+        <v>2.6635</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1978</v>
+        <v>7.1766</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2865</v>
+        <v>3.2191</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9112</v>
+        <v>3.9575</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9494</v>
+        <v>5.6434</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2126</v>
+        <v>3.1686</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9112</v>
+        <v>3.9575</v>
       </c>
       <c r="K2" t="n">
         <v>141</v>
@@ -529,7 +529,7 @@
         <v>127</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1238</v>
+        <v>7.1261</v>
       </c>
       <c r="N2" t="n">
         <v>268</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.27</v>
+        <v>5.1949</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9801</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7748</v>
+        <v>1.7607</v>
       </c>
       <c r="E3" t="n">
-        <v>5.27</v>
+        <v>5.1949</v>
       </c>
       <c r="F3" t="n">
-        <v>3.287</v>
+        <v>3.2132</v>
       </c>
       <c r="G3" t="n">
-        <v>1.983</v>
+        <v>1.9817</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9508</v>
+        <v>5.621</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2134</v>
+        <v>3.156</v>
       </c>
       <c r="J3" t="n">
-        <v>1.983</v>
+        <v>1.9817</v>
       </c>
       <c r="K3" t="n">
         <v>106</v>
@@ -575,7 +575,7 @@
         <v>117</v>
       </c>
       <c r="M3" t="n">
-        <v>5.196400000000001</v>
+        <v>5.137700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>223</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.216</v>
+        <v>5.0803</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9701</v>
+        <v>0.9449</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7502</v>
+        <v>1.7085</v>
       </c>
       <c r="E4" t="n">
-        <v>5.216</v>
+        <v>5.0803</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3979</v>
+        <v>3.3501</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8181</v>
+        <v>1.7302</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3168</v>
+        <v>6.135</v>
       </c>
       <c r="I4" t="n">
-        <v>3.411</v>
+        <v>3.4446</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8181</v>
+        <v>1.7302</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2291</v>
+        <v>5.174799999999999</v>
       </c>
       <c r="N4" t="n">
         <v>213</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.031</v>
+        <v>5.0122</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9357</v>
+        <v>0.9322</v>
       </c>
       <c r="D5" t="n">
-        <v>1.666</v>
+        <v>1.6775</v>
       </c>
       <c r="E5" t="n">
-        <v>5.031</v>
+        <v>5.0122</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9631</v>
+        <v>2.6369</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0679</v>
+        <v>2.3753</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8821</v>
+        <v>3.4574</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6363</v>
+        <v>1.9412</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0679</v>
+        <v>2.3753</v>
       </c>
       <c r="K5" t="n">
-        <v>274</v>
+        <v>196</v>
       </c>
       <c r="L5" t="n">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>4.7042</v>
+        <v>4.3165</v>
       </c>
       <c r="N5" t="n">
-        <v>404</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9669</v>
+        <v>4.7812</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9238</v>
+        <v>0.8892</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6368</v>
+        <v>1.5723</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9669</v>
+        <v>4.7812</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6059</v>
+        <v>2.8803</v>
       </c>
       <c r="G6" t="n">
-        <v>2.361</v>
+        <v>1.9009</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7036</v>
+        <v>4.3714</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9999</v>
+        <v>2.4544</v>
       </c>
       <c r="J6" t="n">
-        <v>2.361</v>
+        <v>1.9009</v>
       </c>
       <c r="K6" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3609</v>
+        <v>4.3553</v>
       </c>
       <c r="N6" t="n">
-        <v>234</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.9469</v>
+        <v>4.7003</v>
       </c>
       <c r="C7" t="n">
-        <v>0.92</v>
+        <v>0.8742</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6277</v>
+        <v>1.5354</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9469</v>
+        <v>4.7003</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0728</v>
+        <v>2.9353</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8741</v>
+        <v>1.765</v>
       </c>
       <c r="H7" t="n">
-        <v>5.244</v>
+        <v>4.5778</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8317</v>
+        <v>2.5703</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8741</v>
+        <v>1.765</v>
       </c>
       <c r="K7" t="n">
         <v>274</v>
@@ -759,7 +759,7 @@
         <v>130</v>
       </c>
       <c r="M7" t="n">
-        <v>4.7058</v>
+        <v>4.3353</v>
       </c>
       <c r="N7" t="n">
         <v>404</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6574</v>
+        <v>4.436</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8662</v>
+        <v>0.825</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4959</v>
+        <v>1.415</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6574</v>
+        <v>4.436</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6121</v>
+        <v>2.6753</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0453</v>
+        <v>1.7607</v>
       </c>
       <c r="H8" t="n">
-        <v>7.0234</v>
+        <v>3.6014</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7926</v>
+        <v>2.0221</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0453</v>
+        <v>1.7607</v>
       </c>
       <c r="K8" t="n">
-        <v>274</v>
+        <v>141</v>
       </c>
       <c r="L8" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8379</v>
+        <v>3.7828</v>
       </c>
       <c r="N8" t="n">
-        <v>404</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5673</v>
+        <v>4.4181</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8494</v>
+        <v>0.8217</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4549</v>
+        <v>1.4069</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5673</v>
+        <v>4.4181</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6972</v>
+        <v>3.518</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8701</v>
+        <v>0.9001</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0049</v>
+        <v>6.7655</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1626</v>
+        <v>3.7986</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8701</v>
+        <v>0.9001</v>
       </c>
       <c r="K9" t="n">
-        <v>141</v>
+        <v>274</v>
       </c>
       <c r="L9" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M9" t="n">
-        <v>4.0327</v>
+        <v>4.6987</v>
       </c>
       <c r="N9" t="n">
-        <v>268</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.1923</v>
+        <v>4.0966</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7619</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2842</v>
+        <v>1.2604</v>
       </c>
       <c r="E10" t="n">
-        <v>4.1923</v>
+        <v>4.0966</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0628</v>
+        <v>3.0701</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1295</v>
+        <v>1.0265</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2112</v>
+        <v>5.0838</v>
       </c>
       <c r="I10" t="n">
-        <v>2.814</v>
+        <v>2.8544</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1295</v>
+        <v>1.0265</v>
       </c>
       <c r="K10" t="n">
         <v>141</v>
@@ -897,7 +897,7 @@
         <v>127</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9435</v>
+        <v>3.8809</v>
       </c>
       <c r="N10" t="n">
         <v>268</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8732</v>
+        <v>3.8701</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7198</v>
       </c>
       <c r="D11" t="n">
-        <v>1.139</v>
+        <v>1.1572</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8732</v>
+        <v>3.8701</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2247</v>
+        <v>2.203</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6484</v>
+        <v>1.6671</v>
       </c>
       <c r="H11" t="n">
-        <v>2.446</v>
+        <v>2.203</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3208</v>
+        <v>1.2369</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6484</v>
+        <v>1.6671</v>
       </c>
       <c r="K11" t="n">
         <v>106</v>
@@ -943,7 +943,7 @@
         <v>117</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9692</v>
+        <v>2.904</v>
       </c>
       <c r="N11" t="n">
         <v>223</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5977</v>
+        <v>3.5694</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6691</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0135</v>
+        <v>1.0202</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5977</v>
+        <v>3.5694</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0913</v>
+        <v>3.1094</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5064</v>
+        <v>0.46</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3053</v>
+        <v>5.2313</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8648</v>
+        <v>2.9372</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5064</v>
+        <v>0.46</v>
       </c>
       <c r="K12" t="n">
         <v>42</v>
@@ -989,7 +989,7 @@
         <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3712</v>
+        <v>3.3972</v>
       </c>
       <c r="N12" t="n">
         <v>145</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.339</v>
+        <v>3.3598</v>
       </c>
       <c r="C13" t="n">
-        <v>0.621</v>
+        <v>0.6249</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8958</v>
+        <v>0.9248</v>
       </c>
       <c r="E13" t="n">
-        <v>3.339</v>
+        <v>3.3598</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0051</v>
+        <v>2.9906</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3339</v>
+        <v>0.3692</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0206</v>
+        <v>4.7853</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7111</v>
+        <v>2.6868</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3339</v>
+        <v>0.3692</v>
       </c>
       <c r="K13" t="n">
         <v>141</v>
@@ -1035,7 +1035,7 @@
         <v>127</v>
       </c>
       <c r="M13" t="n">
-        <v>3.045</v>
+        <v>3.056</v>
       </c>
       <c r="N13" t="n">
         <v>268</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2141</v>
+        <v>3.0963</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5978</v>
+        <v>0.5759</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8389</v>
+        <v>0.8047</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2141</v>
+        <v>3.0963</v>
       </c>
       <c r="F14" t="n">
-        <v>2.701</v>
+        <v>2.642</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5131</v>
+        <v>0.4543</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0173</v>
+        <v>3.4764</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1693</v>
+        <v>1.9519</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5131</v>
+        <v>0.4543</v>
       </c>
       <c r="K14" t="n">
         <v>274</v>
@@ -1081,7 +1081,7 @@
         <v>130</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6824</v>
+        <v>2.4062</v>
       </c>
       <c r="N14" t="n">
         <v>404</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0224</v>
+        <v>3.0556</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5621</v>
+        <v>0.5683</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7517</v>
+        <v>0.7862</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0224</v>
+        <v>3.0556</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0625</v>
+        <v>3.0755</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0401</v>
+        <v>-0.0199</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2101</v>
+        <v>5.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8134</v>
+        <v>2.8658</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0401</v>
+        <v>-0.0199</v>
       </c>
       <c r="K15" t="n">
         <v>42</v>
@@ -1127,7 +1127,7 @@
         <v>103</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7733</v>
+        <v>2.8459</v>
       </c>
       <c r="N15" t="n">
         <v>145</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7402</v>
+        <v>2.7661</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.5144</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6232</v>
+        <v>0.6543</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7402</v>
+        <v>2.7661</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5985</v>
+        <v>2.6481</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1417</v>
+        <v>0.118</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6793</v>
+        <v>3.4994</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9868</v>
+        <v>1.9648</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1417</v>
+        <v>0.118</v>
       </c>
       <c r="K16" t="n">
         <v>106</v>
@@ -1173,7 +1173,7 @@
         <v>117</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1285</v>
+        <v>2.0828</v>
       </c>
       <c r="N16" t="n">
         <v>223</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.5397</v>
+        <v>2.5364</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4723</v>
+        <v>0.4717</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5319</v>
+        <v>0.5497</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5397</v>
+        <v>2.5364</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4226</v>
+        <v>0.4267</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1171</v>
+        <v>2.1097</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4226</v>
+        <v>0.4267</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2282</v>
+        <v>0.2396</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1171</v>
+        <v>2.1097</v>
       </c>
       <c r="K17" t="n">
         <v>196</v>
@@ -1219,7 +1219,7 @@
         <v>38</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3453</v>
+        <v>2.3493</v>
       </c>
       <c r="N17" t="n">
         <v>234</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4775</v>
+        <v>2.2869</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4608</v>
+        <v>0.4253</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5036</v>
+        <v>0.436</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4775</v>
+        <v>2.2869</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7752</v>
+        <v>1.6592</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7023</v>
+        <v>0.6277</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7752</v>
+        <v>1.6592</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9586</v>
+        <v>0.9316</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7023</v>
+        <v>0.6277</v>
       </c>
       <c r="K18" t="n">
         <v>274</v>
@@ -1265,7 +1265,7 @@
         <v>130</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6609</v>
+        <v>1.5593</v>
       </c>
       <c r="N18" t="n">
         <v>404</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8952</v>
+        <v>1.8178</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3525</v>
+        <v>0.3381</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2385</v>
+        <v>0.2223</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8952</v>
+        <v>1.8178</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2363</v>
+        <v>2.1474</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3411</v>
+        <v>-0.3296</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4843</v>
+        <v>2.1474</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3415</v>
+        <v>1.2057</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3411</v>
+        <v>-0.3296</v>
       </c>
       <c r="K19" t="n">
         <v>134</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0004</v>
+        <v>0.8761</v>
       </c>
       <c r="N19" t="n">
         <v>213</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7071</v>
+        <v>1.6739</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3175</v>
+        <v>0.3113</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1529</v>
+        <v>0.1568</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7071</v>
+        <v>1.6739</v>
       </c>
       <c r="F20" t="n">
         <v>1.8022</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0951</v>
+        <v>-0.1283</v>
       </c>
       <c r="H20" t="n">
         <v>1.8022</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9732</v>
+        <v>1.0119</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0951</v>
+        <v>-0.1283</v>
       </c>
       <c r="K20" t="n">
         <v>42</v>
@@ -1357,7 +1357,7 @@
         <v>103</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8781</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>145</v>
@@ -1366,139 +1366,139 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fix</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.6694</v>
+        <v>1.4325</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3105</v>
+        <v>0.2664</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1357</v>
+        <v>0.0468</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6694</v>
+        <v>1.4325</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6043</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06510000000000001</v>
+        <v>1.9905</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6043</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8663</v>
+        <v>-0.3133</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06510000000000001</v>
+        <v>1.9905</v>
       </c>
       <c r="K21" t="n">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="L21" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9314</v>
+        <v>1.6772</v>
       </c>
       <c r="N21" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>fix</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.5486</v>
+        <v>1.4185</v>
       </c>
       <c r="C22" t="n">
-        <v>0.288</v>
+        <v>0.2638</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0808</v>
+        <v>0.0404</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5486</v>
+        <v>1.4185</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5486</v>
+        <v>1.3953</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5486</v>
+        <v>1.3953</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5486</v>
+        <v>0.7834</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="K22" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5486</v>
+        <v>0.8066</v>
       </c>
       <c r="N22" t="n">
-        <v>123</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.4002</v>
+        <v>1.4024</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2604</v>
+        <v>0.2608</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0132</v>
+        <v>0.0331</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4002</v>
+        <v>1.4024</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6039</v>
+        <v>1.4024</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0041</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6039</v>
+        <v>1.4024</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3261</v>
+        <v>1.4024</v>
       </c>
       <c r="J23" t="n">
-        <v>2.0041</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.678</v>
+        <v>1.4024</v>
       </c>
       <c r="N23" t="n">
-        <v>234</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1786</v>
+        <v>1.2377</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2192</v>
+        <v>0.2302</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0877</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1786</v>
+        <v>1.2377</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5522</v>
+        <v>0.636</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6264</v>
+        <v>0.6017</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5522</v>
+        <v>0.636</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2982</v>
+        <v>0.3571</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6264</v>
+        <v>0.6017</v>
       </c>
       <c r="K24" t="n">
         <v>196</v>
@@ -1541,7 +1541,7 @@
         <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9246</v>
+        <v>0.9588</v>
       </c>
       <c r="N24" t="n">
         <v>234</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.082</v>
+        <v>0.9578</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2012</v>
+        <v>0.1781</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1317</v>
+        <v>-0.1695</v>
       </c>
       <c r="E25" t="n">
-        <v>1.082</v>
+        <v>0.9578</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1252</v>
+        <v>1.9545</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0432</v>
+        <v>-0.9967</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1252</v>
+        <v>1.9545</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1476</v>
+        <v>1.0974</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0432</v>
+        <v>-0.9967</v>
       </c>
       <c r="K25" t="n">
         <v>42</v>
@@ -1587,7 +1587,7 @@
         <v>103</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1044</v>
+        <v>0.1006999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>145</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4984</v>
+        <v>0.5294</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0927</v>
+        <v>0.0985</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3973</v>
+        <v>-0.3646</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4984</v>
+        <v>0.5294</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0682</v>
+        <v>-1.0036</v>
       </c>
       <c r="G26" t="n">
-        <v>1.5666</v>
+        <v>1.533</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0682</v>
+        <v>-1.0036</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5768</v>
+        <v>-0.5635</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5666</v>
+        <v>1.533</v>
       </c>
       <c r="K26" t="n">
         <v>196</v>
@@ -1633,7 +1633,7 @@
         <v>38</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9898</v>
+        <v>0.9694999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>234</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4421</v>
+        <v>0.3796</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0822</v>
+        <v>0.0706</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.423</v>
+        <v>-0.4329</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4421</v>
+        <v>0.3796</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4421</v>
+        <v>0.3796</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4421</v>
+        <v>0.3796</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4421</v>
+        <v>0.3796</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4421</v>
+        <v>0.3796</v>
       </c>
       <c r="N27" t="n">
         <v>90</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4079</v>
+        <v>0.294</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0759</v>
+        <v>0.0547</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4385</v>
+        <v>-0.4719</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4079</v>
+        <v>0.294</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9756</v>
+        <v>0.9069</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5677</v>
+        <v>-0.6129</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9756</v>
+        <v>0.9069</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5268</v>
+        <v>0.5092</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.5677</v>
+        <v>-0.6129</v>
       </c>
       <c r="K28" t="n">
         <v>134</v>
@@ -1725,7 +1725,7 @@
         <v>79</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.04089999999999994</v>
+        <v>-0.1037</v>
       </c>
       <c r="N28" t="n">
         <v>213</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0629</v>
+        <v>-0.0319</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0117</v>
+        <v>-0.0059</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5956</v>
+        <v>-0.6203</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0629</v>
+        <v>-0.0319</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9631999999999999</v>
+        <v>-0.0319</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9003</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9631999999999999</v>
+        <v>-0.0319</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5201</v>
+        <v>-0.0319</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9003</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="L29" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3802</v>
+        <v>-0.0319</v>
       </c>
       <c r="N29" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0292</v>
+        <v>-0.0833</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0054</v>
+        <v>-0.0155</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6109</v>
+        <v>-0.6437</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0292</v>
+        <v>-0.0833</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0292</v>
+        <v>0.8109</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.8942</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0292</v>
+        <v>0.8109</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0292</v>
+        <v>0.4553</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.8942</v>
       </c>
       <c r="K30" t="n">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0292</v>
+        <v>-0.4389</v>
       </c>
       <c r="N30" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0104</v>
+        <v>-0.1092</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0019</v>
+        <v>-0.0203</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.6555</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0104</v>
+        <v>-0.1092</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8798</v>
+        <v>0.8027</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.8694</v>
+        <v>-0.9119</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8798</v>
+        <v>0.8027</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4751</v>
+        <v>0.4507</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8694</v>
+        <v>-0.9119</v>
       </c>
       <c r="K31" t="n">
         <v>106</v>
@@ -1863,7 +1863,7 @@
         <v>117</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3942999999999999</v>
+        <v>-0.4612000000000001</v>
       </c>
       <c r="N31" t="n">
         <v>223</v>
@@ -1872,139 +1872,139 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>crush</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1808</v>
+        <v>-0.2466</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0336</v>
+        <v>-0.0459</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7065</v>
+        <v>-0.7181</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1808</v>
+        <v>-0.2466</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3185</v>
+        <v>-0.9986</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4993</v>
+        <v>0.752</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3185</v>
+        <v>-0.9986</v>
       </c>
       <c r="I32" t="n">
-        <v>0.172</v>
+        <v>-0.5607</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.4993</v>
+        <v>0.752</v>
       </c>
       <c r="K32" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="L32" t="n">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3273</v>
+        <v>0.1913</v>
       </c>
       <c r="N32" t="n">
-        <v>213</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Shara</t>
+          <t>crush</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3166</v>
+        <v>-0.2754</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0589</v>
+        <v>-0.0512</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7683</v>
+        <v>-0.7312</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3166</v>
+        <v>-0.2754</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3166</v>
+        <v>0.1968</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4722</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3166</v>
+        <v>0.1968</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3166</v>
+        <v>0.1105</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4722</v>
       </c>
       <c r="K33" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3166</v>
+        <v>-0.3617</v>
       </c>
       <c r="N33" t="n">
-        <v>123</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Shara</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3249</v>
+        <v>-0.2903</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0604</v>
+        <v>-0.054</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7721</v>
+        <v>-0.738</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3249</v>
+        <v>-0.2903</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0795</v>
+        <v>-0.2903</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7546</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0795</v>
+        <v>-0.2903</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5829</v>
+        <v>-0.2903</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7546</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="L34" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1717000000000001</v>
+        <v>-0.2903</v>
       </c>
       <c r="N34" t="n">
-        <v>268</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.53</v>
+        <v>-0.5571</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1036</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8655</v>
+        <v>-0.8596</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.53</v>
+        <v>-0.5571</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.53</v>
+        <v>-0.5571</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.53</v>
+        <v>-0.5571</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.53</v>
+        <v>-0.5571</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.53</v>
+        <v>-0.5571</v>
       </c>
       <c r="N35" t="n">
         <v>123</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.544</v>
+        <v>-0.5888</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1012</v>
+        <v>-0.1095</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8718</v>
+        <v>-0.874</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.544</v>
+        <v>-0.5888</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.544</v>
+        <v>-0.5888</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.544</v>
+        <v>-0.5888</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.544</v>
+        <v>-0.5888</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.544</v>
+        <v>-0.5888</v>
       </c>
       <c r="N36" t="n">
         <v>123</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0821</v>
+        <v>-1.0272</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2013</v>
+        <v>-0.191</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1168</v>
+        <v>-1.0737</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0821</v>
+        <v>-1.0272</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0821</v>
+        <v>-1.0272</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0821</v>
+        <v>-1.0272</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0821</v>
+        <v>-1.0272</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0821</v>
+        <v>-1.0272</v>
       </c>
       <c r="N37" t="n">
         <v>90</v>
@@ -2148,78 +2148,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Friis</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3186</v>
+        <v>-1.2652</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2452</v>
+        <v>-0.2353</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2245</v>
+        <v>-1.1821</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3186</v>
+        <v>-1.2652</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3186</v>
+        <v>0.0654</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-1.3306</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3186</v>
+        <v>0.0654</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3186</v>
+        <v>0.0367</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-1.3306</v>
       </c>
       <c r="K38" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3186</v>
+        <v>-1.2939</v>
       </c>
       <c r="N38" t="n">
-        <v>90</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>Friis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3432</v>
+        <v>-1.2701</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2498</v>
+        <v>-0.2362</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2357</v>
+        <v>-1.1844</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3432</v>
+        <v>-1.2701</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3432</v>
+        <v>-1.2701</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3432</v>
+        <v>-1.2701</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3432</v>
+        <v>-1.2701</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3432</v>
+        <v>-1.2701</v>
       </c>
       <c r="N39" t="n">
         <v>90</v>
@@ -2240,47 +2240,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.453</v>
+        <v>-1.2849</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2702</v>
+        <v>-0.239</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2856</v>
+        <v>-1.1911</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.453</v>
+        <v>-1.2849</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.0709</v>
+        <v>-1.2849</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3821</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.0709</v>
+        <v>-1.2849</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.0383</v>
+        <v>-1.2849</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.3821</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="L40" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4204</v>
+        <v>-1.2849</v>
       </c>
       <c r="N40" t="n">
-        <v>223</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4147</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2712</v>
+        <v>-0.2631</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2881</v>
+        <v>-1.2503</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4147</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4147</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4147</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4147</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4583</v>
+        <v>-1.4147</v>
       </c>
       <c r="N41" t="n">
         <v>90</v>
@@ -2429,10 +2429,10 @@
         <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7679</v>
       </c>
       <c r="J2" t="n">
-        <v>21.4623</v>
+        <v>20.7333</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.13</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3971</v>
+        <v>0.3583</v>
       </c>
       <c r="J3" t="n">
-        <v>10.7217</v>
+        <v>9.674099999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3236</v>
+        <v>0.287</v>
       </c>
       <c r="J4" t="n">
-        <v>8.7372</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1201</v>
+        <v>0.098</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2427</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1548</v>
+        <v>-0.1235</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.1796</v>
+        <v>-3.3345</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4605</v>
+        <v>0.4022</v>
       </c>
       <c r="J7" t="n">
-        <v>12.4335</v>
+        <v>10.8594</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3403</v>
+        <v>0.2873</v>
       </c>
       <c r="J8" t="n">
-        <v>9.1881</v>
+        <v>7.7571</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.304</v>
+        <v>0.2536</v>
       </c>
       <c r="J9" t="n">
-        <v>8.208</v>
+        <v>6.8472</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0016</v>
+        <v>-0.0008</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0432</v>
+        <v>-0.0216</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3955</v>
+        <v>-0.3852</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.6785</v>
+        <v>-10.4004</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.89</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1015</v>
+        <v>-0.0806</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.436</v>
+        <v>-1.9344</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.71</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2974</v>
+        <v>-0.2857</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.1376</v>
+        <v>-6.8568</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.54</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4479</v>
+        <v>-0.4415</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.7496</v>
+        <v>-10.596</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.49</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4919</v>
+        <v>-0.4892</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.8056</v>
+        <v>-11.7408</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.47</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5095</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.228</v>
+        <v>-12.2064</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.63</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7262</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>17.4288</v>
+        <v>15.7128</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.46</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5626</v>
+        <v>0.4952</v>
       </c>
       <c r="J18" t="n">
-        <v>13.5024</v>
+        <v>11.8848</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4633</v>
+        <v>0.4015</v>
       </c>
       <c r="J19" t="n">
-        <v>11.1192</v>
+        <v>9.635999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4106</v>
+        <v>0.3524</v>
       </c>
       <c r="J20" t="n">
-        <v>9.8544</v>
+        <v>8.457599999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2725</v>
+        <v>0.2256</v>
       </c>
       <c r="J21" t="n">
-        <v>6.54</v>
+        <v>5.4144</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.78</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5977</v>
+        <v>1.6271</v>
       </c>
       <c r="J22" t="n">
-        <v>41.5402</v>
+        <v>42.3046</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7246</v>
+        <v>0.6984</v>
       </c>
       <c r="J23" t="n">
-        <v>18.8396</v>
+        <v>18.1584</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.15</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4261</v>
+        <v>0.3932</v>
       </c>
       <c r="J24" t="n">
-        <v>11.0786</v>
+        <v>10.2232</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.12</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3532</v>
+        <v>0.3206</v>
       </c>
       <c r="J25" t="n">
-        <v>9.183199999999999</v>
+        <v>8.335599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3617</v>
+        <v>-0.3221</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.404199999999999</v>
+        <v>-8.374599999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1896</v>
+        <v>0.1496</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9296</v>
+        <v>3.8896</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.96</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0658</v>
+        <v>-0.0541</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.7108</v>
+        <v>-1.4066</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.86</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1822</v>
+        <v>-0.1629</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.7372</v>
+        <v>-4.2354</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.84</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2029</v>
+        <v>-0.1832</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.2754</v>
+        <v>-4.7632</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.253</v>
+        <v>-0.2334</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.578</v>
+        <v>-6.0684</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.62</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2612</v>
+        <v>1.2791</v>
       </c>
       <c r="J32" t="n">
-        <v>31.53</v>
+        <v>31.9775</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.21</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5648</v>
+        <v>0.532</v>
       </c>
       <c r="J33" t="n">
-        <v>14.12</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.19</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5216</v>
+        <v>0.4883</v>
       </c>
       <c r="J34" t="n">
-        <v>13.04</v>
+        <v>12.2075</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.08</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2533</v>
+        <v>0.2227</v>
       </c>
       <c r="J35" t="n">
-        <v>6.3325</v>
+        <v>5.5675</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0371</v>
+        <v>-0.0316</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9275</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.25</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5613</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>14.0325</v>
+        <v>12.715</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.87</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1694</v>
+        <v>-0.1515</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.235</v>
+        <v>-3.7875</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.85</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1896</v>
+        <v>-0.1711</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.74</v>
+        <v>-4.2775</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.74</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2972</v>
+        <v>-0.2792</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.43</v>
+        <v>-6.98</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4159</v>
+        <v>-0.4061</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.3975</v>
+        <v>-10.1525</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.22</v>
       </c>
       <c r="I42" t="n">
-        <v>0.604</v>
+        <v>0.5667</v>
       </c>
       <c r="J42" t="n">
-        <v>16.912</v>
+        <v>15.8676</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.12</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3731</v>
+        <v>0.3348</v>
       </c>
       <c r="J43" t="n">
-        <v>10.4468</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.12</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3731</v>
+        <v>0.3348</v>
       </c>
       <c r="J44" t="n">
-        <v>10.4468</v>
+        <v>9.3744</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.08</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2715</v>
+        <v>0.2371</v>
       </c>
       <c r="J45" t="n">
-        <v>7.602</v>
+        <v>6.6388</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.99</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0765</v>
+        <v>-0.0562</v>
       </c>
       <c r="J46" t="n">
-        <v>-2.142</v>
+        <v>-1.5736</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.17</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3999</v>
+        <v>0.3444</v>
       </c>
       <c r="J47" t="n">
-        <v>11.1972</v>
+        <v>9.6432</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.98</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.038</v>
+        <v>-0.0297</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.064</v>
+        <v>-0.8316</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.93</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1066</v>
+        <v>-0.0906</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.9848</v>
+        <v>-2.5368</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.88</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1631</v>
+        <v>-0.1438</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.5668</v>
+        <v>-4.0264</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3593</v>
+        <v>-0.3449</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.0604</v>
+        <v>-9.6572</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.47</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0718</v>
+        <v>1.0803</v>
       </c>
       <c r="J52" t="n">
-        <v>28.9386</v>
+        <v>29.1681</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.22</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5937</v>
+        <v>0.5582</v>
       </c>
       <c r="J53" t="n">
-        <v>16.0299</v>
+        <v>15.0714</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.11</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3425</v>
+        <v>0.3075</v>
       </c>
       <c r="J54" t="n">
-        <v>9.2475</v>
+        <v>8.3025</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.04</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1451</v>
+        <v>0.1208</v>
       </c>
       <c r="J55" t="n">
-        <v>3.9177</v>
+        <v>3.2616</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.95</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2297</v>
+        <v>-0.1928</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.2019</v>
+        <v>-5.2056</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.48</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8992</v>
+        <v>0.861</v>
       </c>
       <c r="J57" t="n">
-        <v>24.2784</v>
+        <v>23.247</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0815</v>
+        <v>-0.0678</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2005</v>
+        <v>-1.8306</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.89</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.152</v>
+        <v>-0.1332</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.104</v>
+        <v>-3.5964</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3773</v>
+        <v>-0.3643</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.1871</v>
+        <v>-9.8361</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.65</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3863</v>
+        <v>-0.3741</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.4301</v>
+        <v>-10.1007</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.28</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7329</v>
+        <v>0.7018</v>
       </c>
       <c r="J62" t="n">
-        <v>20.5212</v>
+        <v>19.6504</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.24</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6476</v>
+        <v>0.612</v>
       </c>
       <c r="J63" t="n">
-        <v>18.1328</v>
+        <v>17.136</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I64" t="n">
-        <v>0.445</v>
+        <v>0.4055</v>
       </c>
       <c r="J64" t="n">
-        <v>12.46</v>
+        <v>11.354</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0765</v>
+        <v>-0.0562</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.142</v>
+        <v>-1.5736</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.87</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4405</v>
+        <v>-0.398</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.334</v>
+        <v>-11.144</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3155</v>
+        <v>0.2637</v>
       </c>
       <c r="J67" t="n">
-        <v>8.834</v>
+        <v>7.3836</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.12</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2966</v>
+        <v>0.2461</v>
       </c>
       <c r="J68" t="n">
-        <v>8.3048</v>
+        <v>6.8908</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.93</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1093</v>
+        <v>-0.0921</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.0604</v>
+        <v>-2.5788</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1668</v>
+        <v>-0.1468</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.6704</v>
+        <v>-4.1104</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.8</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2498</v>
+        <v>-0.2299</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.9944</v>
+        <v>-6.4372</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.18</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4007</v>
+        <v>0.3443</v>
       </c>
       <c r="J72" t="n">
-        <v>11.2196</v>
+        <v>9.6404</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3475</v>
+        <v>0.2937</v>
       </c>
       <c r="J73" t="n">
-        <v>9.73</v>
+        <v>8.223599999999999</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1926</v>
+        <v>0.1524</v>
       </c>
       <c r="J74" t="n">
-        <v>5.3928</v>
+        <v>4.2672</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.85</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2009</v>
+        <v>-0.1803</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.6252</v>
+        <v>-5.0484</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3286</v>
+        <v>-0.3124</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.200799999999999</v>
+        <v>-8.747199999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.3</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7561</v>
+        <v>0.7285</v>
       </c>
       <c r="J77" t="n">
-        <v>21.1708</v>
+        <v>20.398</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.28</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.6855</v>
       </c>
       <c r="J78" t="n">
-        <v>20.0256</v>
+        <v>19.194</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.25</v>
       </c>
       <c r="I79" t="n">
-        <v>0.653</v>
+        <v>0.6206</v>
       </c>
       <c r="J79" t="n">
-        <v>18.284</v>
+        <v>17.3768</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.18</v>
       </c>
       <c r="I80" t="n">
-        <v>0.5036</v>
+        <v>0.4682</v>
       </c>
       <c r="J80" t="n">
-        <v>14.1008</v>
+        <v>13.1096</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3503</v>
+        <v>-0.3093</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.808400000000001</v>
+        <v>-8.660399999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.24</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5188</v>
+        <v>0.4613</v>
       </c>
       <c r="J82" t="n">
-        <v>15.564</v>
+        <v>13.839</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.1</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2658</v>
+        <v>0.2179</v>
       </c>
       <c r="J83" t="n">
-        <v>7.974</v>
+        <v>6.537</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.207</v>
+        <v>-2.721</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.91</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1303</v>
+        <v>-0.1124</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.909</v>
+        <v>-3.372</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.5</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5181</v>
+        <v>-0.5214</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.543</v>
+        <v>-15.642</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.6</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2539</v>
+        <v>1.273</v>
       </c>
       <c r="J87" t="n">
-        <v>37.617</v>
+        <v>38.19</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9056</v>
+        <v>0.8882</v>
       </c>
       <c r="J88" t="n">
-        <v>27.168</v>
+        <v>26.646</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2377</v>
+        <v>0.2066</v>
       </c>
       <c r="J89" t="n">
-        <v>7.131</v>
+        <v>6.198</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.97</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1618</v>
+        <v>-0.1302</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.854</v>
+        <v>-3.906</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7935</v>
+        <v>-0.7711</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.805</v>
+        <v>-23.133</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.71</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2232</v>
+        <v>1.2216</v>
       </c>
       <c r="J92" t="n">
-        <v>29.3568</v>
+        <v>29.3184</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5605</v>
+        <v>0.5548</v>
       </c>
       <c r="J93" t="n">
-        <v>13.452</v>
+        <v>13.3152</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.18</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4803</v>
+        <v>0.4626</v>
       </c>
       <c r="J94" t="n">
-        <v>11.5272</v>
+        <v>11.1024</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.15</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4244</v>
+        <v>0.393</v>
       </c>
       <c r="J95" t="n">
-        <v>10.1856</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.99</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1024</v>
+        <v>-0.0819</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.4576</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7304</v>
+        <v>0.705</v>
       </c>
       <c r="J97" t="n">
-        <v>17.5296</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.93</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1021</v>
+        <v>-0.0877</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.4504</v>
+        <v>-2.1048</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.7</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3353</v>
+        <v>-0.3192</v>
       </c>
       <c r="J99" t="n">
-        <v>-8.0472</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.66</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3719</v>
+        <v>-0.3582</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.925599999999999</v>
+        <v>-8.5968</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.65</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.381</v>
+        <v>-0.368</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.144</v>
+        <v>-8.832000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4667</v>
+        <v>0.4355</v>
       </c>
       <c r="J102" t="n">
-        <v>13.5343</v>
+        <v>12.6295</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.12</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3797</v>
+        <v>0.3391</v>
       </c>
       <c r="J103" t="n">
-        <v>11.0113</v>
+        <v>9.8339</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1604</v>
+        <v>0.1327</v>
       </c>
       <c r="J104" t="n">
-        <v>4.6516</v>
+        <v>3.8483</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.01</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0502</v>
+        <v>0.0378</v>
       </c>
       <c r="J105" t="n">
-        <v>1.4558</v>
+        <v>1.0962</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.99</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0689</v>
+        <v>-0.0497</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.9981</v>
+        <v>-1.4413</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3831</v>
+        <v>0.3275</v>
       </c>
       <c r="J107" t="n">
-        <v>11.1099</v>
+        <v>9.4975</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1711</v>
+        <v>0.1336</v>
       </c>
       <c r="J108" t="n">
-        <v>4.9619</v>
+        <v>3.8744</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.04</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1254</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J109" t="n">
-        <v>3.6366</v>
+        <v>2.7463</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.96</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0721</v>
+        <v>-0.0579</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.0909</v>
+        <v>-1.6791</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.74</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3099</v>
+        <v>-0.2925</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.9871</v>
+        <v>-8.4825</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5672</v>
+        <v>0.5412</v>
       </c>
       <c r="J112" t="n">
-        <v>17.016</v>
+        <v>16.236</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.03</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0997</v>
+        <v>0.0737</v>
       </c>
       <c r="J113" t="n">
-        <v>2.991</v>
+        <v>2.211</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0432</v>
+        <v>0.0292</v>
       </c>
       <c r="J114" t="n">
-        <v>1.296</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.66</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3842</v>
+        <v>-0.3725</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.526</v>
+        <v>-11.175</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.63</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1321</v>
+        <v>1.1258</v>
       </c>
       <c r="J117" t="n">
-        <v>33.963</v>
+        <v>33.774</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.54</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0116</v>
+        <v>0.9994</v>
       </c>
       <c r="J118" t="n">
-        <v>30.348</v>
+        <v>29.982</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.21</v>
       </c>
       <c r="I119" t="n">
-        <v>0.533</v>
+        <v>0.5253</v>
       </c>
       <c r="J119" t="n">
-        <v>15.99</v>
+        <v>15.759</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0336</v>
+        <v>-0.028</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.008</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.62</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.0099</v>
+        <v>-1.0132</v>
       </c>
       <c r="J121" t="n">
-        <v>-30.297</v>
+        <v>-30.396</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.59</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6577</v>
+        <v>0.617</v>
       </c>
       <c r="J122" t="n">
-        <v>17.7579</v>
+        <v>16.659</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.21</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3192</v>
+        <v>0.2625</v>
       </c>
       <c r="J123" t="n">
-        <v>8.618399999999999</v>
+        <v>7.0875</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.14</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2312</v>
+        <v>0.1844</v>
       </c>
       <c r="J124" t="n">
-        <v>6.2424</v>
+        <v>4.9788</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.91</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1443</v>
+        <v>-0.1247</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.8961</v>
+        <v>-3.3669</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.68</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3745</v>
+        <v>-0.3631</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.1115</v>
+        <v>-9.803699999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.28</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4371</v>
+        <v>0.4417</v>
       </c>
       <c r="J127" t="n">
-        <v>11.8017</v>
+        <v>11.9259</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1646</v>
+        <v>0.148</v>
       </c>
       <c r="J128" t="n">
-        <v>4.4442</v>
+        <v>3.996</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.96</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0736</v>
+        <v>-0.059</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.9872</v>
+        <v>-1.593</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1594</v>
+        <v>-0.1393</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.3038</v>
+        <v>-3.7611</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1922</v>
+        <v>-0.1715</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.1894</v>
+        <v>-4.6305</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.3</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.572</v>
       </c>
       <c r="J132" t="n">
-        <v>13.0504</v>
+        <v>12.584</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.91</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1247</v>
+        <v>-0.1091</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.7434</v>
+        <v>-2.4002</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2093</v>
+        <v>-0.1904</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.6046</v>
+        <v>-4.1888</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.74</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2965</v>
+        <v>-0.2786</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.523</v>
+        <v>-6.1292</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.51</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5027</v>
+        <v>-0.5029</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.0594</v>
+        <v>-11.0638</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1296</v>
+        <v>1.1222</v>
       </c>
       <c r="J137" t="n">
-        <v>24.8512</v>
+        <v>24.6884</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.49</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9204</v>
+        <v>0.9074</v>
       </c>
       <c r="J138" t="n">
-        <v>20.2488</v>
+        <v>19.9628</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.42</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8257</v>
+        <v>0.8129</v>
       </c>
       <c r="J139" t="n">
-        <v>18.1654</v>
+        <v>17.8838</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.1</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2895</v>
+        <v>0.2579</v>
       </c>
       <c r="J140" t="n">
-        <v>6.369</v>
+        <v>5.6738</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.98</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1563</v>
+        <v>-0.1311</v>
       </c>
       <c r="J141" t="n">
-        <v>-3.4386</v>
+        <v>-2.8842</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>0.86</v>
       </c>
       <c r="I142" t="n">
-        <v>-0.0843</v>
+        <v>-0.0444</v>
       </c>
       <c r="J142" t="n">
-        <v>-1.4331</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.57</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.4023</v>
+        <v>-0.3988</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.8391</v>
+        <v>-6.7796</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.45</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.5064</v>
+        <v>-0.5072</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.6088</v>
+        <v>-8.622400000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.33</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.6138</v>
+        <v>-0.6261</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.4346</v>
+        <v>-10.6437</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.25</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6872</v>
+        <v>-0.7126</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.6824</v>
+        <v>-12.1142</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.71</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1686</v>
+        <v>1.1667</v>
       </c>
       <c r="J147" t="n">
-        <v>19.8662</v>
+        <v>19.8339</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.64</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0838</v>
+        <v>1.0797</v>
       </c>
       <c r="J148" t="n">
-        <v>18.4246</v>
+        <v>18.3549</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.64</v>
       </c>
       <c r="I149" t="n">
-        <v>1.0838</v>
+        <v>1.0797</v>
       </c>
       <c r="J149" t="n">
-        <v>18.4246</v>
+        <v>18.3549</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.58</v>
       </c>
       <c r="I150" t="n">
-        <v>1.0107</v>
+        <v>1.0056</v>
       </c>
       <c r="J150" t="n">
-        <v>17.1819</v>
+        <v>17.0952</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.25</v>
       </c>
       <c r="I151" t="n">
-        <v>0.5595</v>
+        <v>0.5581</v>
       </c>
       <c r="J151" t="n">
-        <v>9.5115</v>
+        <v>9.4877</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.03</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1768</v>
+        <v>0.1517</v>
       </c>
       <c r="J152" t="n">
-        <v>3.7128</v>
+        <v>3.1857</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.97</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0212</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.4452</v>
+        <v>-0.2016</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.86</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1626</v>
+        <v>-0.147</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.4146</v>
+        <v>-3.087</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4088</v>
+        <v>-0.3983</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.5848</v>
+        <v>-8.3643</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.16</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7869</v>
+        <v>-0.8395</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.5249</v>
+        <v>-17.6295</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.83</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3332</v>
+        <v>1.3377</v>
       </c>
       <c r="J157" t="n">
-        <v>27.9972</v>
+        <v>28.0917</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.65</v>
       </c>
       <c r="I158" t="n">
-        <v>1.112</v>
+        <v>1.1052</v>
       </c>
       <c r="J158" t="n">
-        <v>23.352</v>
+        <v>23.2092</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.5</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9208</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="J159" t="n">
-        <v>19.3368</v>
+        <v>19.1268</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.15</v>
       </c>
       <c r="I160" t="n">
-        <v>0.398</v>
+        <v>0.3663</v>
       </c>
       <c r="J160" t="n">
-        <v>8.358000000000001</v>
+        <v>7.6923</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0669</v>
+        <v>0.0436</v>
       </c>
       <c r="J161" t="n">
-        <v>1.4049</v>
+        <v>0.9156</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.91</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1143</v>
+        <v>-0.0998</v>
       </c>
       <c r="J162" t="n">
-        <v>-2.5146</v>
+        <v>-2.1956</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.9</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1263</v>
+        <v>-0.1113</v>
       </c>
       <c r="J163" t="n">
-        <v>-2.7786</v>
+        <v>-2.4486</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.77</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2607</v>
+        <v>-0.2438</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.7354</v>
+        <v>-5.3636</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3345</v>
+        <v>-0.319</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.359</v>
+        <v>-7.018</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.63</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3888</v>
+        <v>-0.3765</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.553599999999999</v>
+        <v>-8.282999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.99</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5326</v>
+        <v>1.5543</v>
       </c>
       <c r="J167" t="n">
-        <v>33.7172</v>
+        <v>34.1946</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1431</v>
+        <v>1.1368</v>
       </c>
       <c r="J168" t="n">
-        <v>25.1482</v>
+        <v>25.0096</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.2</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4976</v>
+        <v>0.4888</v>
       </c>
       <c r="J169" t="n">
-        <v>10.9472</v>
+        <v>10.7536</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.1</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2792</v>
+        <v>0.2471</v>
       </c>
       <c r="J170" t="n">
-        <v>6.1424</v>
+        <v>5.4362</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.01</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0053</v>
+        <v>-0.0178</v>
       </c>
       <c r="J171" t="n">
-        <v>-0.1166</v>
+        <v>-0.3916</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.42</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7194</v>
+        <v>0.6916</v>
       </c>
       <c r="J172" t="n">
-        <v>20.1432</v>
+        <v>19.3648</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1423</v>
+        <v>0.1085</v>
       </c>
       <c r="J173" t="n">
-        <v>3.9844</v>
+        <v>3.038</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.77</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2726</v>
+        <v>-0.2535</v>
       </c>
       <c r="J174" t="n">
-        <v>-7.6328</v>
+        <v>-7.098</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.73</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3107</v>
+        <v>-0.2931</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.6996</v>
+        <v>-8.206799999999999</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4638</v>
+        <v>-0.4595</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.9864</v>
+        <v>-12.866</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.52</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9787</v>
+        <v>0.9655</v>
       </c>
       <c r="J177" t="n">
-        <v>27.4036</v>
+        <v>27.034</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.39</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7983</v>
+        <v>0.7832</v>
       </c>
       <c r="J178" t="n">
-        <v>22.3524</v>
+        <v>21.9296</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.25</v>
       </c>
       <c r="I179" t="n">
-        <v>0.5925</v>
+        <v>0.584</v>
       </c>
       <c r="J179" t="n">
-        <v>16.59</v>
+        <v>16.352</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.14</v>
       </c>
       <c r="I180" t="n">
-        <v>0.4057</v>
+        <v>0.3724</v>
       </c>
       <c r="J180" t="n">
-        <v>11.3596</v>
+        <v>10.4272</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.83</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5597</v>
+        <v>-0.5232</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.6716</v>
+        <v>-14.6496</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.96</v>
       </c>
       <c r="I182" t="n">
-        <v>1.0168</v>
+        <v>0.9618</v>
       </c>
       <c r="J182" t="n">
-        <v>20.336</v>
+        <v>19.236</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.48</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="J183" t="n">
-        <v>11.644</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.35</v>
       </c>
       <c r="I184" t="n">
-        <v>0.453</v>
+        <v>0.3919</v>
       </c>
       <c r="J184" t="n">
-        <v>9.06</v>
+        <v>7.838</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1389</v>
+        <v>0.107</v>
       </c>
       <c r="J185" t="n">
-        <v>2.778</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.07</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1085</v>
+        <v>0.0809</v>
       </c>
       <c r="J186" t="n">
-        <v>2.17</v>
+        <v>1.618</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.9</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1141</v>
+        <v>-0.0984</v>
       </c>
       <c r="J187" t="n">
-        <v>-2.282</v>
+        <v>-1.968</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.79</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2348</v>
+        <v>-0.2198</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.696</v>
+        <v>-4.396</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.76</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2642</v>
+        <v>-0.2496</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.284</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.6</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4076</v>
+        <v>-0.397</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.151999999999999</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.52</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4783</v>
+        <v>-0.4741</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.566000000000001</v>
+        <v>-9.481999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5474</v>
+        <v>0.488</v>
       </c>
       <c r="J192" t="n">
-        <v>16.422</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3975</v>
+        <v>0.3413</v>
       </c>
       <c r="J193" t="n">
-        <v>11.925</v>
+        <v>10.239</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.96</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0731</v>
+        <v>-0.0586</v>
       </c>
       <c r="J194" t="n">
-        <v>-2.193</v>
+        <v>-1.758</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.93</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1122</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.366</v>
+        <v>-2.829</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.7</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3484</v>
+        <v>-0.3337</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.452</v>
+        <v>-10.011</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.27</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7093</v>
+        <v>0.677</v>
       </c>
       <c r="J197" t="n">
-        <v>21.279</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.2</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5576</v>
+        <v>0.5195</v>
       </c>
       <c r="J198" t="n">
-        <v>16.728</v>
+        <v>15.585</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.17</v>
       </c>
       <c r="I199" t="n">
-        <v>0.4898</v>
+        <v>0.4508</v>
       </c>
       <c r="J199" t="n">
-        <v>14.694</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.06</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2137</v>
+        <v>0.1833</v>
       </c>
       <c r="J200" t="n">
-        <v>6.411</v>
+        <v>5.499</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.88</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.417</v>
+        <v>-0.3744</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.51</v>
+        <v>-11.232</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.11</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3165</v>
+        <v>0.2688</v>
       </c>
       <c r="J202" t="n">
-        <v>7.9125</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.97</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0422</v>
+        <v>-0.033</v>
       </c>
       <c r="J203" t="n">
-        <v>-1.055</v>
+        <v>-0.825</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2172</v>
+        <v>-0.199</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.43</v>
+        <v>-4.975</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.77</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2654</v>
+        <v>-0.2471</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.635</v>
+        <v>-6.1775</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.49</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5174</v>
+        <v>-0.5193</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.935</v>
+        <v>-12.9825</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.58</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1986</v>
+        <v>1.2133</v>
       </c>
       <c r="J207" t="n">
-        <v>29.965</v>
+        <v>30.3325</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0198</v>
+        <v>1.0214</v>
       </c>
       <c r="J208" t="n">
-        <v>25.495</v>
+        <v>25.535</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5595</v>
+        <v>0.5288</v>
       </c>
       <c r="J209" t="n">
-        <v>13.9875</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.04</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1269</v>
+        <v>0.1033</v>
       </c>
       <c r="J210" t="n">
-        <v>3.1725</v>
+        <v>2.5825</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.04</v>
       </c>
       <c r="I211" t="n">
-        <v>0.1269</v>
+        <v>0.1033</v>
       </c>
       <c r="J211" t="n">
-        <v>3.1725</v>
+        <v>2.5825</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.37</v>
       </c>
       <c r="I212" t="n">
-        <v>0.494</v>
+        <v>0.426</v>
       </c>
       <c r="J212" t="n">
-        <v>13.338</v>
+        <v>11.502</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3367</v>
+        <v>0.2796</v>
       </c>
       <c r="J213" t="n">
-        <v>9.0909</v>
+        <v>7.5492</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.23</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3367</v>
+        <v>0.2796</v>
       </c>
       <c r="J214" t="n">
-        <v>9.0909</v>
+        <v>7.5492</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.325</v>
+        <v>0.2689</v>
       </c>
       <c r="J215" t="n">
-        <v>8.775</v>
+        <v>7.2603</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2858</v>
+        <v>-0.2685</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.7166</v>
+        <v>-7.2495</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.3</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4778</v>
+        <v>0.486</v>
       </c>
       <c r="J217" t="n">
-        <v>12.9006</v>
+        <v>13.122</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.08</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1725</v>
+        <v>0.1552</v>
       </c>
       <c r="J218" t="n">
-        <v>4.6575</v>
+        <v>4.1904</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.9</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1434</v>
+        <v>-0.1244</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.8718</v>
+        <v>-3.3588</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.84</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2081</v>
+        <v>-0.1876</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.6187</v>
+        <v>-5.0652</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.67</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3713</v>
+        <v>-0.358</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.0251</v>
+        <v>-9.666</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.22</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4874</v>
+        <v>0.4303</v>
       </c>
       <c r="J222" t="n">
-        <v>12.185</v>
+        <v>10.7575</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.97</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J223" t="n">
-        <v>-1.3425</v>
+        <v>-1.0775</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.97</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.3425</v>
+        <v>-1.0775</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.77</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.275</v>
+        <v>-0.2559</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.875</v>
+        <v>-6.3975</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.71</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3317</v>
+        <v>-0.3154</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.2925</v>
+        <v>-7.885</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.32</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7957</v>
+        <v>0.7706</v>
       </c>
       <c r="J227" t="n">
-        <v>19.8925</v>
+        <v>19.265</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.28</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7145</v>
+        <v>0.6848</v>
       </c>
       <c r="J228" t="n">
-        <v>17.8625</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.27</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6939</v>
+        <v>0.6633</v>
       </c>
       <c r="J229" t="n">
-        <v>17.3475</v>
+        <v>16.5825</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.15</v>
       </c>
       <c r="I230" t="n">
-        <v>0.4352</v>
+        <v>0.4001</v>
       </c>
       <c r="J230" t="n">
-        <v>10.88</v>
+        <v>10.0025</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.92</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3234</v>
+        <v>-0.2829</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.085000000000001</v>
+        <v>-7.0725</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5293</v>
+        <v>0.4698</v>
       </c>
       <c r="J232" t="n">
-        <v>19.0548</v>
+        <v>16.9128</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.09</v>
       </c>
       <c r="I233" t="n">
-        <v>0.23</v>
+        <v>0.186</v>
       </c>
       <c r="J233" t="n">
-        <v>8.279999999999999</v>
+        <v>6.696</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.06</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1678</v>
+        <v>0.1314</v>
       </c>
       <c r="J234" t="n">
-        <v>6.0408</v>
+        <v>4.7304</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1596</v>
+        <v>-0.1395</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.7456</v>
+        <v>-5.022</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.78</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2735</v>
+        <v>-0.2544</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.846</v>
+        <v>-9.1584</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.42</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0313</v>
+        <v>1.0365</v>
       </c>
       <c r="J237" t="n">
-        <v>37.1268</v>
+        <v>37.314</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.27</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7332</v>
+        <v>0.7019</v>
       </c>
       <c r="J238" t="n">
-        <v>26.3952</v>
+        <v>25.2684</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.92</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2939</v>
+        <v>-0.2531</v>
       </c>
       <c r="J239" t="n">
-        <v>-10.5804</v>
+        <v>-9.111599999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.8</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5941</v>
+        <v>-0.5553</v>
       </c>
       <c r="J240" t="n">
-        <v>-21.3876</v>
+        <v>-19.9908</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.75</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7069</v>
+        <v>-0.6747</v>
       </c>
       <c r="J241" t="n">
-        <v>-25.4484</v>
+        <v>-24.2892</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.0409</v>
+        <v>-0.0206</v>
       </c>
       <c r="J242" t="n">
-        <v>-0.7771</v>
+        <v>-0.3914</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1986</v>
+        <v>-0.1825</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.7734</v>
+        <v>-3.4675</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.59</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.4063</v>
+        <v>-0.3973</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.7197</v>
+        <v>-7.5487</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.48</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.503</v>
+        <v>-0.5014</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.557</v>
+        <v>-9.5266</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.36</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6083</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.5577</v>
+        <v>-11.8085</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.93</v>
       </c>
       <c r="I247" t="n">
-        <v>1.5766</v>
+        <v>1.6141</v>
       </c>
       <c r="J247" t="n">
-        <v>29.9554</v>
+        <v>30.6679</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.75</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3646</v>
+        <v>1.39</v>
       </c>
       <c r="J248" t="n">
-        <v>25.9274</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.57</v>
       </c>
       <c r="I249" t="n">
-        <v>1.1462</v>
+        <v>1.1663</v>
       </c>
       <c r="J249" t="n">
-        <v>21.7778</v>
+        <v>22.1597</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.34</v>
       </c>
       <c r="I250" t="n">
-        <v>0.7846</v>
+        <v>0.7731</v>
       </c>
       <c r="J250" t="n">
-        <v>14.9074</v>
+        <v>14.6889</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1.2</v>
       </c>
       <c r="I251" t="n">
-        <v>0.495</v>
+        <v>0.4655</v>
       </c>
       <c r="J251" t="n">
-        <v>9.404999999999999</v>
+        <v>8.8445</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.56</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0048</v>
+        <v>0.9831</v>
       </c>
       <c r="J252" t="n">
-        <v>29.1392</v>
+        <v>28.5099</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.9</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1416</v>
+        <v>-0.1231</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.1064</v>
+        <v>-3.5699</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.87</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1745</v>
+        <v>-0.1548</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.0605</v>
+        <v>-4.4892</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.351</v>
+        <v>-0.336</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.179</v>
+        <v>-9.744</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.66</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3783</v>
+        <v>-0.3654</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.9707</v>
+        <v>-10.5966</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.58</v>
       </c>
       <c r="I257" t="n">
-        <v>1.2355</v>
+        <v>1.2544</v>
       </c>
       <c r="J257" t="n">
-        <v>35.8295</v>
+        <v>36.3776</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.11</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3479</v>
+        <v>0.3107</v>
       </c>
       <c r="J258" t="n">
-        <v>10.0891</v>
+        <v>9.010300000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2424</v>
+        <v>0.2102</v>
       </c>
       <c r="J259" t="n">
-        <v>7.0296</v>
+        <v>6.0958</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.91</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3378</v>
+        <v>-0.2958</v>
       </c>
       <c r="J260" t="n">
-        <v>-9.796200000000001</v>
+        <v>-8.578200000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3378</v>
+        <v>-0.2958</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.796200000000001</v>
+        <v>-8.578200000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.17</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4379</v>
+        <v>0.3879</v>
       </c>
       <c r="J262" t="n">
-        <v>10.5096</v>
+        <v>9.3096</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>0.87</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1653</v>
+        <v>-0.1488</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.9672</v>
+        <v>-3.5712</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.79</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.245</v>
+        <v>-0.2269</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.88</v>
+        <v>-5.4456</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.74</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2924</v>
+        <v>-0.2748</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.0176</v>
+        <v>-6.5952</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.52</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4901</v>
+        <v>-0.4882</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.7624</v>
+        <v>-11.7168</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.99</v>
       </c>
       <c r="I267" t="n">
-        <v>1.7088</v>
+        <v>1.7627</v>
       </c>
       <c r="J267" t="n">
-        <v>41.0112</v>
+        <v>42.3048</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.13</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3719</v>
+        <v>0.3397</v>
       </c>
       <c r="J268" t="n">
-        <v>8.925599999999999</v>
+        <v>8.152799999999999</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.3719</v>
+        <v>0.3397</v>
       </c>
       <c r="J269" t="n">
-        <v>8.925599999999999</v>
+        <v>8.152799999999999</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.1</v>
       </c>
       <c r="I270" t="n">
-        <v>0.2959</v>
+        <v>0.2643</v>
       </c>
       <c r="J270" t="n">
-        <v>7.1016</v>
+        <v>6.3432</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1.09</v>
       </c>
       <c r="I271" t="n">
-        <v>0.2693</v>
+        <v>0.2384</v>
       </c>
       <c r="J271" t="n">
-        <v>6.4632</v>
+        <v>5.7216</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.08</v>
       </c>
       <c r="I272" t="n">
-        <v>0.3073</v>
+        <v>0.2741</v>
       </c>
       <c r="J272" t="n">
-        <v>7.3752</v>
+        <v>6.5784</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.7</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.318</v>
+        <v>-0.304</v>
       </c>
       <c r="J273" t="n">
-        <v>-7.632</v>
+        <v>-7.296</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.65</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3623</v>
+        <v>-0.3494</v>
       </c>
       <c r="J274" t="n">
-        <v>-8.6952</v>
+        <v>-8.3856</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.64</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3712</v>
+        <v>-0.3587</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.908799999999999</v>
+        <v>-8.6088</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.47</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5212</v>
+        <v>-0.5222</v>
       </c>
       <c r="J276" t="n">
-        <v>-12.5088</v>
+        <v>-12.5328</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.76</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4087</v>
+        <v>1.434</v>
       </c>
       <c r="J277" t="n">
-        <v>33.8088</v>
+        <v>34.416</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.56</v>
       </c>
       <c r="I278" t="n">
-        <v>1.1549</v>
+        <v>1.1695</v>
       </c>
       <c r="J278" t="n">
-        <v>27.7176</v>
+        <v>28.068</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.6097</v>
+        <v>0.5839</v>
       </c>
       <c r="J279" t="n">
-        <v>14.6328</v>
+        <v>14.0136</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.17</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4555</v>
+        <v>0.4248</v>
       </c>
       <c r="J280" t="n">
-        <v>10.932</v>
+        <v>10.1952</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.08</v>
       </c>
       <c r="I281" t="n">
-        <v>0.2303</v>
+        <v>0.1996</v>
       </c>
       <c r="J281" t="n">
-        <v>5.5272</v>
+        <v>4.7904</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>2.01</v>
       </c>
       <c r="I282" t="n">
-        <v>1.6799</v>
+        <v>1.7257</v>
       </c>
       <c r="J282" t="n">
-        <v>35.2779</v>
+        <v>36.2397</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.65</v>
       </c>
       <c r="I283" t="n">
-        <v>1.2502</v>
+        <v>1.2702</v>
       </c>
       <c r="J283" t="n">
-        <v>26.2542</v>
+        <v>26.6742</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>1.34</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7924</v>
+        <v>0.7804</v>
       </c>
       <c r="J284" t="n">
-        <v>16.6404</v>
+        <v>16.3884</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>1.3</v>
       </c>
       <c r="I285" t="n">
-        <v>0.7135</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="J285" t="n">
-        <v>14.9835</v>
+        <v>14.6181</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>1.2</v>
       </c>
       <c r="I286" t="n">
-        <v>0.503</v>
+        <v>0.4742</v>
       </c>
       <c r="J286" t="n">
-        <v>10.563</v>
+        <v>9.9582</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>0.89</v>
       </c>
       <c r="I287" t="n">
-        <v>-0.1082</v>
+        <v>-0.0892</v>
       </c>
       <c r="J287" t="n">
-        <v>-2.2722</v>
+        <v>-1.8732</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>0.71</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3014</v>
+        <v>-0.2894</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.3294</v>
+        <v>-6.0774</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3201</v>
+        <v>-0.3087</v>
       </c>
       <c r="J289" t="n">
-        <v>-6.7221</v>
+        <v>-6.4827</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.6</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3984</v>
+        <v>-0.3888</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.366400000000001</v>
+        <v>-8.1648</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.32</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6439</v>
+        <v>-0.6635</v>
       </c>
       <c r="J291" t="n">
-        <v>-13.5219</v>
+        <v>-13.9335</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.26</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4059</v>
+        <v>0.4033</v>
       </c>
       <c r="J292" t="n">
-        <v>14.6124</v>
+        <v>14.5188</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.24</v>
       </c>
       <c r="I293" t="n">
-        <v>0.3807</v>
+        <v>0.3756</v>
       </c>
       <c r="J293" t="n">
-        <v>13.7052</v>
+        <v>13.5216</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.97</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.063</v>
+        <v>-0.0493</v>
       </c>
       <c r="J294" t="n">
-        <v>-2.268</v>
+        <v>-1.7748</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1168</v>
+        <v>-0.0983</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.2048</v>
+        <v>-3.5388</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.92</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.129</v>
+        <v>-0.1099</v>
       </c>
       <c r="J296" t="n">
-        <v>-4.644</v>
+        <v>-3.9564</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7518</v>
+        <v>0.6835</v>
       </c>
       <c r="J297" t="n">
-        <v>27.0648</v>
+        <v>24.606</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.09</v>
       </c>
       <c r="I298" t="n">
-        <v>0.165</v>
+        <v>0.1272</v>
       </c>
       <c r="J298" t="n">
-        <v>5.94</v>
+        <v>4.5792</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.03</v>
       </c>
       <c r="I299" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0491</v>
       </c>
       <c r="J299" t="n">
-        <v>2.4696</v>
+        <v>1.7676</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1054</v>
+        <v>-0.0876</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.7944</v>
+        <v>-3.1536</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.73</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3265</v>
+        <v>-0.3108</v>
       </c>
       <c r="J301" t="n">
-        <v>-11.754</v>
+        <v>-11.1888</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.33</v>
       </c>
       <c r="I302" t="n">
-        <v>0.8298</v>
+        <v>0.8058</v>
       </c>
       <c r="J302" t="n">
-        <v>24.0642</v>
+        <v>23.3682</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.31</v>
       </c>
       <c r="I303" t="n">
-        <v>0.789</v>
+        <v>0.762</v>
       </c>
       <c r="J303" t="n">
-        <v>22.881</v>
+        <v>22.098</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7477</v>
+        <v>0.718</v>
       </c>
       <c r="J304" t="n">
-        <v>21.6833</v>
+        <v>20.822</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.07</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2402</v>
+        <v>0.2086</v>
       </c>
       <c r="J305" t="n">
-        <v>6.9658</v>
+        <v>6.0494</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.9303</v>
       </c>
       <c r="J306" t="n">
-        <v>-27.202</v>
+        <v>-26.9787</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.41</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7585</v>
+        <v>0.7038</v>
       </c>
       <c r="J307" t="n">
-        <v>21.9965</v>
+        <v>20.4102</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.18</v>
       </c>
       <c r="I308" t="n">
-        <v>0.3941</v>
+        <v>0.3381</v>
       </c>
       <c r="J308" t="n">
-        <v>11.4289</v>
+        <v>9.8049</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0599</v>
+        <v>-0.0468</v>
       </c>
       <c r="J309" t="n">
-        <v>-1.7371</v>
+        <v>-1.3572</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.92</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1256</v>
+        <v>-0.1068</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.6424</v>
+        <v>-3.0972</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.64</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4039</v>
+        <v>-0.3944</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.7131</v>
+        <v>-11.4376</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.85</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5042</v>
+        <v>1.536</v>
       </c>
       <c r="J312" t="n">
-        <v>31.5882</v>
+        <v>32.256</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.56</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1451</v>
+        <v>1.1612</v>
       </c>
       <c r="J313" t="n">
-        <v>24.0471</v>
+        <v>24.3852</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.49</v>
       </c>
       <c r="I314" t="n">
-        <v>1.0541</v>
+        <v>1.0661</v>
       </c>
       <c r="J314" t="n">
-        <v>22.1361</v>
+        <v>22.3881</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.17</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4447</v>
+        <v>0.4139</v>
       </c>
       <c r="J315" t="n">
-        <v>9.338699999999999</v>
+        <v>8.6919</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>1.1</v>
       </c>
       <c r="I316" t="n">
-        <v>0.2732</v>
+        <v>0.2406</v>
       </c>
       <c r="J316" t="n">
-        <v>5.7372</v>
+        <v>5.0526</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>0.96</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.0502</v>
+        <v>-0.0394</v>
       </c>
       <c r="J317" t="n">
-        <v>-1.0542</v>
+        <v>-0.8274</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>0.89</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.1395</v>
+        <v>-0.1241</v>
       </c>
       <c r="J318" t="n">
-        <v>-2.9295</v>
+        <v>-2.6061</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>0.75</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2802</v>
+        <v>-0.263</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.8842</v>
+        <v>-5.523</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3356</v>
+        <v>-0.32</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.0476</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.66</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3629</v>
+        <v>-0.3488</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.6209</v>
+        <v>-7.3248</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>2.11</v>
       </c>
       <c r="I322" t="n">
-        <v>1.8107</v>
+        <v>1.8711</v>
       </c>
       <c r="J322" t="n">
-        <v>38.0247</v>
+        <v>39.2931</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.69</v>
       </c>
       <c r="I323" t="n">
-        <v>1.3092</v>
+        <v>1.3298</v>
       </c>
       <c r="J323" t="n">
-        <v>27.4932</v>
+        <v>27.9258</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.29</v>
       </c>
       <c r="I324" t="n">
-        <v>0.7029</v>
+        <v>0.6835</v>
       </c>
       <c r="J324" t="n">
-        <v>14.7609</v>
+        <v>14.3535</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.09</v>
       </c>
       <c r="I325" t="n">
-        <v>0.2469</v>
+        <v>0.2147</v>
       </c>
       <c r="J325" t="n">
-        <v>5.1849</v>
+        <v>4.5087</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.98</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.1719</v>
+        <v>-0.1493</v>
       </c>
       <c r="J326" t="n">
-        <v>-3.6099</v>
+        <v>-3.1353</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>0.78</v>
       </c>
       <c r="I327" t="n">
-        <v>-0.243</v>
+        <v>-0.2283</v>
       </c>
       <c r="J327" t="n">
-        <v>-5.103</v>
+        <v>-4.7943</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>0.77</v>
       </c>
       <c r="I328" t="n">
-        <v>-0.2529</v>
+        <v>-0.2384</v>
       </c>
       <c r="J328" t="n">
-        <v>-5.3109</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.75</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.2722</v>
+        <v>-0.258</v>
       </c>
       <c r="J329" t="n">
-        <v>-5.7162</v>
+        <v>-5.418</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.61</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.341200000000001</v>
+        <v>-8.1081</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.6</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.4061</v>
+        <v>-0.3956</v>
       </c>
       <c r="J331" t="n">
-        <v>-8.5281</v>
+        <v>-8.307600000000001</v>
       </c>
     </row>
   </sheetData>
